--- a/research/traditional_assets/database/data/finland/finland_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_packaging_container.xlsx
@@ -650,10 +650,10 @@
         <v>0.07982471097265423</v>
       </c>
       <c r="X2">
-        <v>0.08603337346917239</v>
+        <v>0.08601248359496314</v>
       </c>
       <c r="Y2">
-        <v>-0.006208662496518164</v>
+        <v>-0.006187772622308907</v>
       </c>
       <c r="Z2">
         <v>1.485215737443881</v>
@@ -662,10 +662,10 @@
         <v>0.06217889277425617</v>
       </c>
       <c r="AB2">
-        <v>0.07578500344961855</v>
+        <v>0.07577033969327435</v>
       </c>
       <c r="AC2">
-        <v>-0.01360611067536238</v>
+        <v>-0.01359144691901818</v>
       </c>
       <c r="AD2">
         <v>2410.5</v>
@@ -787,10 +787,10 @@
         <v>0.1398268617425201</v>
       </c>
       <c r="X3">
-        <v>0.08777010305584589</v>
+        <v>0.08774831144112935</v>
       </c>
       <c r="Y3">
-        <v>0.05205675868667424</v>
+        <v>0.05207855030139077</v>
       </c>
       <c r="Z3">
         <v>1.966039033617057</v>
@@ -799,10 +799,10 @@
         <v>0.1371131037335585</v>
       </c>
       <c r="AB3">
-        <v>0.07595582833590248</v>
+        <v>0.07594127586167787</v>
       </c>
       <c r="AC3">
-        <v>0.061157275397656</v>
+        <v>0.06117182787188061</v>
       </c>
       <c r="AD3">
         <v>1844.1</v>
@@ -924,10 +924,10 @@
         <v>0.01982256020278834</v>
       </c>
       <c r="X4">
-        <v>0.08429664388249891</v>
+        <v>0.08427665574879691</v>
       </c>
       <c r="Y4">
-        <v>-0.06447408367971057</v>
+        <v>-0.06445409554600856</v>
       </c>
       <c r="Z4">
         <v>0.9757686176269643</v>
@@ -936,10 +936,10 @@
         <v>-0.01275531818504615</v>
       </c>
       <c r="AB4">
-        <v>0.07561417856333462</v>
+        <v>0.07559940352487082</v>
       </c>
       <c r="AC4">
-        <v>-0.08836949674838077</v>
+        <v>-0.08835472170991697</v>
       </c>
       <c r="AD4">
         <v>566.4</v>
@@ -1276,49 +1276,49 @@
         <v>4.79909194097616</v>
       </c>
       <c r="F2">
-        <v>9.882045077900059</v>
+        <v>4.56937582809417</v>
       </c>
       <c r="G2">
         <v>2.8728773952329</v>
       </c>
       <c r="H2">
-        <v>1.2107306434024</v>
+        <v>2.50794204704783</v>
       </c>
       <c r="I2">
         <v>0.332198443579767</v>
       </c>
       <c r="J2">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="K2">
         <v>3707.1</v>
       </c>
       <c r="L2">
-        <v>4954.10281780292</v>
+        <v>4191.26991542441</v>
       </c>
       <c r="M2">
         <v>5096</v>
       </c>
       <c r="N2">
-        <v>5276.07081780292</v>
+        <v>5345.91791542441</v>
       </c>
       <c r="O2">
         <v>1844.1</v>
       </c>
       <c r="P2">
-        <v>777.168</v>
+        <v>1609.848</v>
       </c>
       <c r="Q2">
-        <v>0.0759558283359025</v>
+        <v>0.0759412758616779</v>
       </c>
       <c r="R2">
-        <v>0.07492661836934041</v>
+        <v>0.0745321923421108</v>
       </c>
       <c r="S2">
         <v>0.0522061955533515</v>
       </c>
       <c r="T2">
-        <v>0.0454061955533515</v>
+        <v>0.0474061955533515</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1327,20 +1327,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.0877701030558459</v>
+        <v>0.08774831144112941</v>
       </c>
       <c r="X2">
-        <v>0.079732268595199</v>
+        <v>0.0856118248332942</v>
       </c>
       <c r="Y2">
         <v>0.862501434592403</v>
       </c>
       <c r="Z2">
-        <v>0.697320907298973</v>
+        <v>0.818573021244196</v>
       </c>
       <c r="AA2">
         <v>1844.1</v>
@@ -1373,7 +1373,7 @@
         <v>3707.1</v>
       </c>
       <c r="AK2">
-        <v>0.0486609081127847</v>
+        <v>0.0486356425145578</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1561,13 +1561,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07582237756365343</v>
+        <v>0.07580678941787569</v>
       </c>
       <c r="C2">
-        <v>5573.8519413374</v>
+        <v>5574.039595002044</v>
       </c>
       <c r="D2">
-        <v>5118.6519413374</v>
+        <v>5118.839595002044</v>
       </c>
       <c r="E2">
         <v>-1844.1</v>
@@ -1612,19 +1612,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07582237756365343</v>
+        <v>0.07580678941787569</v>
       </c>
       <c r="T2">
         <v>0.6169711731246059</v>
       </c>
       <c r="U2">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1643,13 +1643,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07574959476405964</v>
+        <v>0.07572283779457345</v>
       </c>
       <c r="C3">
-        <v>5530.779168691614</v>
+        <v>5532.889030116401</v>
       </c>
       <c r="D3">
-        <v>5131.091168691614</v>
+        <v>5133.201030116401</v>
       </c>
       <c r="E3">
         <v>-1788.588</v>
@@ -1676,37 +1676,37 @@
         <v>435.9</v>
       </c>
       <c r="M3">
-        <v>3.089672709447061</v>
+        <v>3.011955909447062</v>
       </c>
       <c r="N3">
-        <v>432.8103272905529</v>
+        <v>432.888044090553</v>
       </c>
       <c r="O3">
-        <v>86.5620654581106</v>
+        <v>86.5776088181106</v>
       </c>
       <c r="P3">
-        <v>346.2482618324424</v>
+        <v>346.3104352724424</v>
       </c>
       <c r="Q3">
-        <v>565.3482618324424</v>
+        <v>565.4104352724423</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07606498263487488</v>
+        <v>0.07604926852428276</v>
       </c>
       <c r="T3">
         <v>0.6219567987660169</v>
       </c>
       <c r="U3">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>141.0829045637038</v>
+        <v>144.7232340396454</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1725,13 +1725,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07567681196446585</v>
+        <v>0.07563888617127121</v>
       </c>
       <c r="C4">
-        <v>5487.76700236438</v>
+        <v>5491.819276946308</v>
       </c>
       <c r="D4">
-        <v>5143.59100236438</v>
+        <v>5147.643276946309</v>
       </c>
       <c r="E4">
         <v>-1733.076</v>
@@ -1758,37 +1758,37 @@
         <v>435.9</v>
       </c>
       <c r="M4">
-        <v>6.179345418894123</v>
+        <v>6.023911818894123</v>
       </c>
       <c r="N4">
-        <v>429.7206545811059</v>
+        <v>429.8760881811059</v>
       </c>
       <c r="O4">
-        <v>85.94413091622118</v>
+        <v>85.97521763622119</v>
       </c>
       <c r="P4">
-        <v>343.7765236648847</v>
+        <v>343.9008705448847</v>
       </c>
       <c r="Q4">
-        <v>562.8765236648846</v>
+        <v>563.0008705448847</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07631253882999879</v>
+        <v>0.07629669618388182</v>
       </c>
       <c r="T4">
         <v>0.6270441718694975</v>
       </c>
       <c r="U4">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>70.54145228185193</v>
+        <v>72.36161701982269</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1807,13 +1807,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07560402916487205</v>
+        <v>0.07555493454796895</v>
       </c>
       <c r="C5">
-        <v>5444.81588636589</v>
+        <v>5450.831019506854</v>
       </c>
       <c r="D5">
-        <v>5156.15188636589</v>
+        <v>5162.167019506855</v>
       </c>
       <c r="E5">
         <v>-1677.564</v>
@@ -1840,37 +1840,37 @@
         <v>435.9</v>
       </c>
       <c r="M5">
-        <v>9.269018128341184</v>
+        <v>9.035867728341184</v>
       </c>
       <c r="N5">
-        <v>426.6309818716588</v>
+        <v>426.8641322716588</v>
       </c>
       <c r="O5">
-        <v>85.32619637433177</v>
+        <v>85.37282645433177</v>
       </c>
       <c r="P5">
-        <v>341.3047854973271</v>
+        <v>341.4913058173271</v>
       </c>
       <c r="Q5">
-        <v>560.4047854973271</v>
+        <v>560.5913058173271</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07656519927656856</v>
+        <v>0.07654922544470971</v>
       </c>
       <c r="T5">
         <v>0.6322364392637714</v>
       </c>
       <c r="U5">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.02763485456795</v>
+        <v>48.24107801321512</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1889,13 +1889,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07553124636527828</v>
+        <v>0.07547098292466674</v>
       </c>
       <c r="C6">
-        <v>5401.926269054115</v>
+        <v>5409.924949554575</v>
       </c>
       <c r="D6">
-        <v>5168.774269054114</v>
+        <v>5176.772949554575</v>
       </c>
       <c r="E6">
         <v>-1622.052</v>
@@ -1922,37 +1922,37 @@
         <v>435.9</v>
       </c>
       <c r="M6">
-        <v>12.35869083778825</v>
+        <v>12.04782363778825</v>
       </c>
       <c r="N6">
-        <v>423.5413091622118</v>
+        <v>423.8521763622118</v>
       </c>
       <c r="O6">
-        <v>84.70826183244236</v>
+        <v>84.77043527244236</v>
       </c>
       <c r="P6">
-        <v>338.8330473297694</v>
+        <v>339.0817410897694</v>
       </c>
       <c r="Q6">
-        <v>557.9330473297694</v>
+        <v>558.1817410897694</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07682312348244189</v>
+        <v>0.07680701573180487</v>
       </c>
       <c r="T6">
         <v>0.6375368788954262</v>
       </c>
       <c r="U6">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.27072614092597</v>
+        <v>36.18080850991134</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1971,13 +1971,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07545846356568447</v>
+        <v>0.0753870313013645</v>
       </c>
       <c r="C7">
-        <v>5359.09860318818</v>
+        <v>5369.101766697313</v>
       </c>
       <c r="D7">
-        <v>5181.458603188181</v>
+        <v>5191.461766697314</v>
       </c>
       <c r="E7">
         <v>-1566.54</v>
@@ -2004,37 +2004,37 @@
         <v>435.9</v>
       </c>
       <c r="M7">
-        <v>15.44836354723531</v>
+        <v>15.05977954723531</v>
       </c>
       <c r="N7">
-        <v>420.4516364527647</v>
+        <v>420.8402204527648</v>
       </c>
       <c r="O7">
-        <v>84.09032729055295</v>
+        <v>84.16804409055295</v>
       </c>
       <c r="P7">
-        <v>336.3613091622118</v>
+        <v>336.6721763622118</v>
       </c>
       <c r="Q7">
-        <v>555.4613091622118</v>
+        <v>555.7721763622118</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07708647767159674</v>
+        <v>0.07707023318283887</v>
       </c>
       <c r="T7">
         <v>0.6429489067298524</v>
       </c>
       <c r="U7">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.21658091274077</v>
+        <v>28.94464680792908</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2053,13 +2053,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07538568076609069</v>
+        <v>0.07530307967806227</v>
       </c>
       <c r="C8">
-        <v>5316.333345982471</v>
+        <v>5328.362178505893</v>
       </c>
       <c r="D8">
-        <v>5194.205345982471</v>
+        <v>5206.234178505893</v>
       </c>
       <c r="E8">
         <v>-1511.028</v>
@@ -2086,37 +2086,37 @@
         <v>435.9</v>
       </c>
       <c r="M8">
-        <v>18.53803625668237</v>
+        <v>18.07173545668237</v>
       </c>
       <c r="N8">
-        <v>417.3619637433177</v>
+        <v>417.8282645433177</v>
       </c>
       <c r="O8">
-        <v>83.47239274866354</v>
+        <v>83.56565290866354</v>
       </c>
       <c r="P8">
-        <v>333.8895709946542</v>
+        <v>334.2626116346541</v>
       </c>
       <c r="Q8">
-        <v>552.9895709946541</v>
+        <v>553.3626116346541</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07735543514137191</v>
+        <v>0.07733905100517147</v>
       </c>
       <c r="T8">
         <v>0.648476084092671</v>
       </c>
       <c r="U8">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.51381742728397</v>
+        <v>24.12053900660757</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2135,13 +2135,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.0753128979664969</v>
+        <v>0.07521912805476003</v>
       </c>
       <c r="C9">
-        <v>5273.63095916159</v>
+        <v>5287.706900627761</v>
       </c>
       <c r="D9">
-        <v>5207.01495916159</v>
+        <v>5221.090900627761</v>
       </c>
       <c r="E9">
         <v>-1455.516</v>
@@ -2168,37 +2168,37 @@
         <v>435.9</v>
       </c>
       <c r="M9">
-        <v>21.62770896612943</v>
+        <v>21.08369136612943</v>
       </c>
       <c r="N9">
-        <v>414.2722910338706</v>
+        <v>414.8163086338706</v>
       </c>
       <c r="O9">
-        <v>82.85445820677413</v>
+        <v>82.96326172677414</v>
       </c>
       <c r="P9">
-        <v>331.4178328270965</v>
+        <v>331.8530469070965</v>
       </c>
       <c r="Q9">
-        <v>550.5178328270965</v>
+        <v>550.9530469070965</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07763017664275515</v>
+        <v>0.07761364985594132</v>
       </c>
       <c r="T9">
         <v>0.6541221254847973</v>
       </c>
       <c r="U9">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.15470065195769</v>
+        <v>20.67474771994934</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2217,13 +2217,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07524011516690311</v>
+        <v>0.0751351764314578</v>
       </c>
       <c r="C10">
-        <v>5230.991909016098</v>
+        <v>5247.136656902529</v>
       </c>
       <c r="D10">
-        <v>5219.887909016098</v>
+        <v>5236.032656902529</v>
       </c>
       <c r="E10">
         <v>-1400.004</v>
@@ -2250,37 +2250,37 @@
         <v>435.9</v>
       </c>
       <c r="M10">
-        <v>24.71738167557649</v>
+        <v>24.09564727557649</v>
       </c>
       <c r="N10">
-        <v>411.1826183244235</v>
+        <v>411.8043527244236</v>
       </c>
       <c r="O10">
-        <v>82.23652366488471</v>
+        <v>82.36087054488472</v>
       </c>
       <c r="P10">
-        <v>328.9460946595388</v>
+        <v>329.4434821795388</v>
       </c>
       <c r="Q10">
-        <v>548.0460946595388</v>
+        <v>548.5434821795388</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07791089078547281</v>
+        <v>0.0778942182469453</v>
       </c>
       <c r="T10">
         <v>0.6598909069071872</v>
       </c>
       <c r="U10">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.63536307046298</v>
+        <v>18.09040425495567</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2299,13 +2299,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07516733236730931</v>
+        <v>0.07505122480815556</v>
       </c>
       <c r="C11">
-        <v>5188.416666459105</v>
+        <v>5206.652179479565</v>
       </c>
       <c r="D11">
-        <v>5232.824666459105</v>
+        <v>5251.060179479566</v>
       </c>
       <c r="E11">
         <v>-1344.492</v>
@@ -2332,37 +2332,37 @@
         <v>435.9</v>
       </c>
       <c r="M11">
-        <v>27.80705438502355</v>
+        <v>27.10760318502355</v>
       </c>
       <c r="N11">
-        <v>408.0929456149765</v>
+        <v>408.7923968149765</v>
       </c>
       <c r="O11">
-        <v>81.6185891229953</v>
+        <v>81.7584793629953</v>
       </c>
       <c r="P11">
-        <v>326.4743564919812</v>
+        <v>327.0339174519812</v>
       </c>
       <c r="Q11">
-        <v>545.5743564919812</v>
+        <v>546.1339174519812</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07819777446978865</v>
+        <v>0.07818095297621311</v>
       </c>
       <c r="T11">
         <v>0.6657864747344648</v>
       </c>
       <c r="U11">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.67587828485599</v>
+        <v>16.08035933773838</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2381,13 +2381,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07509454956771552</v>
+        <v>0.07496727318485334</v>
       </c>
       <c r="C12">
-        <v>5145.905707083673</v>
+        <v>5166.254208937549</v>
       </c>
       <c r="D12">
-        <v>5245.825707083673</v>
+        <v>5266.174208937549</v>
       </c>
       <c r="E12">
         <v>-1288.98</v>
@@ -2414,37 +2414,37 @@
         <v>435.9</v>
       </c>
       <c r="M12">
-        <v>30.89672709447061</v>
+        <v>30.11955909447061</v>
       </c>
       <c r="N12">
-        <v>405.0032729055294</v>
+        <v>405.7804409055294</v>
       </c>
       <c r="O12">
-        <v>81.00065458110589</v>
+        <v>81.15608818110589</v>
       </c>
       <c r="P12">
-        <v>324.0026183244235</v>
+        <v>324.6243527244235</v>
       </c>
       <c r="Q12">
-        <v>543.1026183244235</v>
+        <v>543.7243527244235</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07849103334708929</v>
+        <v>0.07847405958835353</v>
       </c>
       <c r="T12">
         <v>0.6718130551801266</v>
       </c>
       <c r="U12">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.10829045637038</v>
+        <v>14.47232340396454</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2463,13 +2463,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07502176676812172</v>
+        <v>0.07488332156155109</v>
       </c>
       <c r="C13">
-        <v>5103.459511221129</v>
+        <v>5125.943494406168</v>
       </c>
       <c r="D13">
-        <v>5258.891511221129</v>
+        <v>5281.375494406167</v>
       </c>
       <c r="E13">
         <v>-1233.468</v>
@@ -2496,37 +2496,37 @@
         <v>435.9</v>
       </c>
       <c r="M13">
-        <v>33.98639980391767</v>
+        <v>33.13151500391767</v>
       </c>
       <c r="N13">
-        <v>401.9136001960824</v>
+        <v>402.7684849960823</v>
       </c>
       <c r="O13">
-        <v>80.38272003921648</v>
+        <v>80.55369699921647</v>
       </c>
       <c r="P13">
-        <v>321.5308801568659</v>
+        <v>322.2147879968659</v>
       </c>
       <c r="Q13">
-        <v>540.6308801568659</v>
+        <v>541.3147879968658</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07879088231152029</v>
+        <v>0.0787737528659353</v>
       </c>
       <c r="T13">
         <v>0.6779750643998478</v>
       </c>
       <c r="U13">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.82571859670035</v>
+        <v>13.15665763996776</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2545,13 +2545,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07505458396852795</v>
+        <v>0.07494336993824885</v>
       </c>
       <c r="C14">
-        <v>5042.048193123698</v>
+        <v>5059.549498746695</v>
       </c>
       <c r="D14">
-        <v>5252.992193123699</v>
+        <v>5270.493498746695</v>
       </c>
       <c r="E14">
         <v>-1177.956</v>
@@ -2578,37 +2578,37 @@
         <v>435.9</v>
       </c>
       <c r="M14">
-        <v>37.80883091336474</v>
+        <v>37.14268691336473</v>
       </c>
       <c r="N14">
-        <v>398.0911690866353</v>
+        <v>398.7573130866353</v>
       </c>
       <c r="O14">
-        <v>79.61823381732707</v>
+        <v>79.75146261732706</v>
       </c>
       <c r="P14">
-        <v>318.4729352693083</v>
+        <v>319.0058504693083</v>
       </c>
       <c r="Q14">
-        <v>537.5729352693082</v>
+        <v>538.1058504693083</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07909754602514291</v>
+        <v>0.07908025735437121</v>
       </c>
       <c r="T14">
         <v>0.6842771192836539</v>
       </c>
       <c r="U14">
-        <v>0.05675774444168939</v>
+        <v>0.05575774444168938</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04540619555335151</v>
+        <v>0.04460619555335151</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.5290525908834</v>
+        <v>11.73582301723987</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2627,13 +2627,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07499060116893413</v>
+        <v>0.07487141831494661</v>
       </c>
       <c r="C15">
-        <v>4998.050212475865</v>
+        <v>5017.081945313781</v>
       </c>
       <c r="D15">
-        <v>5264.506212475865</v>
+        <v>5283.537945313781</v>
       </c>
       <c r="E15">
         <v>-1122.444</v>
@@ -2660,37 +2660,37 @@
         <v>435.9</v>
       </c>
       <c r="M15">
-        <v>40.95956682281179</v>
+        <v>40.23791082281179</v>
       </c>
       <c r="N15">
-        <v>394.9404331771883</v>
+        <v>395.6620891771882</v>
       </c>
       <c r="O15">
-        <v>78.98808663543765</v>
+        <v>79.13241783543765</v>
       </c>
       <c r="P15">
-        <v>315.9523465417506</v>
+        <v>316.5296713417506</v>
       </c>
       <c r="Q15">
-        <v>535.0523465417506</v>
+        <v>535.6296713417505</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07941125947930855</v>
+        <v>0.07939380792300105</v>
       </c>
       <c r="T15">
         <v>0.6907240489923748</v>
       </c>
       <c r="U15">
-        <v>0.05675774444168939</v>
+        <v>0.05575774444168938</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04540619555335151</v>
+        <v>0.04460619555335151</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.64220239158468</v>
+        <v>10.83306740052911</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2709,13 +2709,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07492661836934035</v>
+        <v>0.07479946669164438</v>
       </c>
       <c r="C16">
-        <v>4954.102817802917</v>
+        <v>4974.679121975082</v>
       </c>
       <c r="D16">
-        <v>5276.070817802917</v>
+        <v>5296.647121975082</v>
       </c>
       <c r="E16">
         <v>-1066.932</v>
@@ -2742,37 +2742,37 @@
         <v>435.9</v>
       </c>
       <c r="M16">
-        <v>44.11030273225886</v>
+        <v>43.33313473225886</v>
       </c>
       <c r="N16">
-        <v>391.7896972677412</v>
+        <v>392.5668652677412</v>
       </c>
       <c r="O16">
-        <v>78.35793945354824</v>
+        <v>78.51337305354824</v>
       </c>
       <c r="P16">
-        <v>313.431757814193</v>
+        <v>314.0534922141929</v>
       </c>
       <c r="Q16">
-        <v>532.5317578141929</v>
+        <v>533.153492214193</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.079732268595199</v>
+        <v>0.07971465036531997</v>
       </c>
       <c r="T16">
         <v>0.6973209072989732</v>
       </c>
       <c r="U16">
-        <v>0.05675774444168939</v>
+        <v>0.05575774444168938</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04540619555335151</v>
+        <v>0.04460619555335151</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.882045077900056</v>
+        <v>10.05927687191989</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2791,13 +2791,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07512663556974655</v>
+        <v>0.07493151506834214</v>
       </c>
       <c r="C17">
-        <v>4862.606297464333</v>
+        <v>4895.158289864671</v>
       </c>
       <c r="D17">
-        <v>5240.086297464333</v>
+        <v>5272.638289864672</v>
       </c>
       <c r="E17">
         <v>-1011.42</v>
@@ -2824,37 +2824,37 @@
         <v>435.9</v>
       </c>
       <c r="M17">
-        <v>49.09293464170592</v>
+        <v>47.84391464170591</v>
       </c>
       <c r="N17">
-        <v>386.8070653582941</v>
+        <v>388.0560853582941</v>
       </c>
       <c r="O17">
-        <v>77.36141307165883</v>
+        <v>77.61121707165883</v>
       </c>
       <c r="P17">
-        <v>309.4456522866353</v>
+        <v>310.4448682866353</v>
       </c>
       <c r="Q17">
-        <v>528.5456522866352</v>
+        <v>529.5448682866353</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08006083086675744</v>
+        <v>0.08004304204157578</v>
       </c>
       <c r="T17">
         <v>0.7040729858010208</v>
       </c>
       <c r="U17">
-        <v>0.05895774444168939</v>
+        <v>0.05745774444168938</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04716619555335151</v>
+        <v>0.04596619555335151</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.879078082850846</v>
+        <v>9.110876550641251</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2873,13 +2873,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07508025277015276</v>
+        <v>0.0748731634450399</v>
       </c>
       <c r="C18">
-        <v>4815.395109431271</v>
+        <v>4850.228798502948</v>
       </c>
       <c r="D18">
-        <v>5248.387109431271</v>
+        <v>5283.220798502948</v>
       </c>
       <c r="E18">
         <v>-955.9079999999999</v>
@@ -2906,37 +2906,37 @@
         <v>435.9</v>
       </c>
       <c r="M18">
-        <v>52.36579695115298</v>
+        <v>51.03350895115298</v>
       </c>
       <c r="N18">
-        <v>383.5342030488471</v>
+        <v>384.866491048847</v>
       </c>
       <c r="O18">
-        <v>76.70684060976942</v>
+        <v>76.97329820976941</v>
       </c>
       <c r="P18">
-        <v>306.8273624390777</v>
+        <v>307.8931928390776</v>
       </c>
       <c r="Q18">
-        <v>525.9273624390776</v>
+        <v>526.9931928390777</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08039721604954347</v>
+        <v>0.08037925256726626</v>
       </c>
       <c r="T18">
         <v>0.7109858280769268</v>
       </c>
       <c r="U18">
-        <v>0.05895774444168939</v>
+        <v>0.05745774444168938</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04716619555335151</v>
+        <v>0.04596619555335151</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.324135702672667</v>
+        <v>8.541446766226171</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2955,13 +2955,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07503386997055896</v>
+        <v>0.07481481182173766</v>
       </c>
       <c r="C19">
-        <v>4768.210261728678</v>
+        <v>4805.341872060236</v>
       </c>
       <c r="D19">
-        <v>5256.714261728678</v>
+        <v>5293.845872060236</v>
       </c>
       <c r="E19">
         <v>-900.3959999999998</v>
@@ -2988,37 +2988,37 @@
         <v>435.9</v>
       </c>
       <c r="M19">
-        <v>55.63865926060004</v>
+        <v>54.22310326060004</v>
       </c>
       <c r="N19">
-        <v>380.2613407394</v>
+        <v>381.6768967394</v>
       </c>
       <c r="O19">
-        <v>76.05226814788</v>
+        <v>76.33537934787999</v>
       </c>
       <c r="P19">
-        <v>304.20907259152</v>
+        <v>305.34151739152</v>
       </c>
       <c r="Q19">
-        <v>523.3090725915199</v>
+        <v>524.4415173915199</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08074170689938459</v>
+        <v>0.08072356455140711</v>
       </c>
       <c r="T19">
         <v>0.7180652448655052</v>
       </c>
       <c r="U19">
-        <v>0.05895774444168939</v>
+        <v>0.05745774444168938</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04716619555335151</v>
+        <v>0.04596619555335151</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.834480661338981</v>
+        <v>8.039008721154044</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3037,13 +3037,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07520348717096519</v>
+        <v>0.07487166019843543</v>
       </c>
       <c r="C20">
-        <v>4682.374336160748</v>
+        <v>4739.477984955727</v>
       </c>
       <c r="D20">
-        <v>5226.390336160749</v>
+        <v>5283.493984955728</v>
       </c>
       <c r="E20">
         <v>-844.884</v>
@@ -3070,37 +3070,37 @@
         <v>435.9</v>
       </c>
       <c r="M20">
-        <v>60.4103455700471</v>
+        <v>58.21207037004709</v>
       </c>
       <c r="N20">
-        <v>375.4896544299529</v>
+        <v>377.6879296299529</v>
       </c>
       <c r="O20">
-        <v>75.09793088599058</v>
+        <v>75.53758592599058</v>
       </c>
       <c r="P20">
-        <v>300.3917235439623</v>
+        <v>302.1503437039623</v>
       </c>
       <c r="Q20">
-        <v>519.4917235439623</v>
+        <v>521.2503437039622</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.0810945999650755</v>
+        <v>0.0810762743888197</v>
       </c>
       <c r="T20">
         <v>0.725317330356244</v>
       </c>
       <c r="U20">
-        <v>0.06045774444168939</v>
+        <v>0.05825774444168939</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04836619555335151</v>
+        <v>0.04660619555335151</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.215651489603955</v>
+        <v>7.488137721765201</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3119,13 +3119,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07516910437137139</v>
+        <v>0.0748197085751332</v>
       </c>
       <c r="C21">
-        <v>4632.980940570842</v>
+        <v>4693.424594387154</v>
       </c>
       <c r="D21">
-        <v>5232.508940570842</v>
+        <v>5292.952594387154</v>
       </c>
       <c r="E21">
         <v>-789.3719999999998</v>
@@ -3152,37 +3152,37 @@
         <v>435.9</v>
       </c>
       <c r="M21">
-        <v>63.76647587949417</v>
+        <v>61.44607427949417</v>
       </c>
       <c r="N21">
-        <v>372.1335241205059</v>
+        <v>374.4539257205059</v>
       </c>
       <c r="O21">
-        <v>74.42670482410118</v>
+        <v>74.89078514410117</v>
       </c>
       <c r="P21">
-        <v>297.7068192964047</v>
+        <v>299.5631405764047</v>
       </c>
       <c r="Q21">
-        <v>516.8068192964047</v>
+        <v>518.6631405764047</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08145620643979581</v>
+        <v>0.08143769311110668</v>
       </c>
       <c r="T21">
         <v>0.7327484796862604</v>
       </c>
       <c r="U21">
-        <v>0.06045774444168939</v>
+        <v>0.05825774444168939</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04836619555335151</v>
+        <v>0.04660619555335151</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.835880358572167</v>
+        <v>7.094025210093347</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3201,13 +3201,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07513472157177761</v>
+        <v>0.07476775695183097</v>
       </c>
       <c r="C22">
-        <v>4583.60188803503</v>
+        <v>4647.405130512662</v>
       </c>
       <c r="D22">
-        <v>5238.64188803503</v>
+        <v>5302.445130512662</v>
       </c>
       <c r="E22">
         <v>-733.8599999999999</v>
@@ -3234,37 +3234,37 @@
         <v>435.9</v>
       </c>
       <c r="M22">
-        <v>67.12260618894122</v>
+        <v>64.68007818894122</v>
       </c>
       <c r="N22">
-        <v>368.7773938110588</v>
+        <v>371.2199218110588</v>
       </c>
       <c r="O22">
-        <v>73.75547876221177</v>
+        <v>74.24398436221178</v>
       </c>
       <c r="P22">
-        <v>295.0219150488471</v>
+        <v>296.975937448847</v>
       </c>
       <c r="Q22">
-        <v>514.1219150488471</v>
+        <v>516.0759374488471</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08182685307638413</v>
+        <v>0.08180814730145082</v>
       </c>
       <c r="T22">
         <v>0.7403654077495271</v>
       </c>
       <c r="U22">
-        <v>0.06045774444168939</v>
+        <v>0.05825774444168939</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04836619555335151</v>
+        <v>0.04660619555335151</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.49408634064356</v>
+        <v>6.739323949588681</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3283,13 +3283,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07510033877218381</v>
+        <v>0.07471580532852871</v>
       </c>
       <c r="C23">
-        <v>4534.237229046357</v>
+        <v>4601.419776195586</v>
       </c>
       <c r="D23">
-        <v>5244.789229046358</v>
+        <v>5311.971776195585</v>
       </c>
       <c r="E23">
         <v>-678.348</v>
@@ -3316,37 +3316,37 @@
         <v>435.9</v>
       </c>
       <c r="M23">
-        <v>70.47873649838829</v>
+        <v>67.91408209838828</v>
       </c>
       <c r="N23">
-        <v>365.4212635016117</v>
+        <v>367.9859179016117</v>
       </c>
       <c r="O23">
-        <v>73.08425270032235</v>
+        <v>73.59718358032235</v>
       </c>
       <c r="P23">
-        <v>292.3370108012894</v>
+        <v>294.3887343212894</v>
       </c>
       <c r="Q23">
-        <v>511.4370108012894</v>
+        <v>513.4887343212894</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08220688317212657</v>
+        <v>0.08218798007889228</v>
       </c>
       <c r="T23">
         <v>0.7481751694346487</v>
       </c>
       <c r="U23">
-        <v>0.06045774444168939</v>
+        <v>0.05825774444168939</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04836619555335151</v>
+        <v>0.04660619555335151</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.184844133946247</v>
+        <v>6.418403761513029</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07531235597259002</v>
+        <v>0.0746638537052265</v>
       </c>
       <c r="C24">
-        <v>4441.046585901234</v>
+        <v>4555.468715615774</v>
       </c>
       <c r="D24">
-        <v>5207.110585901234</v>
+        <v>5321.532715615775</v>
       </c>
       <c r="E24">
         <v>-622.836</v>
@@ -3398,45 +3398,45 @@
         <v>435.9</v>
       </c>
       <c r="M24">
-        <v>75.54463640783534</v>
+        <v>71.14808600783535</v>
       </c>
       <c r="N24">
-        <v>360.3553635921647</v>
+        <v>364.7519139921647</v>
       </c>
       <c r="O24">
-        <v>72.07107271843294</v>
+        <v>72.95038279843294</v>
       </c>
       <c r="P24">
-        <v>288.2842908737317</v>
+        <v>291.8015311937318</v>
       </c>
       <c r="Q24">
-        <v>507.3842908737317</v>
+        <v>510.9015311937317</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08259665762929831</v>
+        <v>0.08257755215831944</v>
       </c>
       <c r="T24">
         <v>0.7561851814193888</v>
       </c>
       <c r="U24">
-        <v>0.06185774444168939</v>
+        <v>0.05825774444168939</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04948619555335151</v>
+        <v>0.04660619555335151</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>5.77009858974964</v>
+        <v>6.12665813598971</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3447,13 +3447,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07528917317299622</v>
+        <v>0.07479590208192424</v>
       </c>
       <c r="C25">
-        <v>4389.628135776897</v>
+        <v>4475.722265014596</v>
       </c>
       <c r="D25">
-        <v>5211.204135776897</v>
+        <v>5297.298265014596</v>
       </c>
       <c r="E25">
         <v>-567.3239999999998</v>
@@ -3480,37 +3480,37 @@
         <v>435.9</v>
       </c>
       <c r="M25">
-        <v>78.97848351728241</v>
+        <v>75.65886591728241</v>
       </c>
       <c r="N25">
-        <v>356.9215164827176</v>
+        <v>360.2411340827176</v>
       </c>
       <c r="O25">
-        <v>71.38430329654352</v>
+        <v>72.04822681654353</v>
       </c>
       <c r="P25">
-        <v>285.5372131861741</v>
+        <v>288.1929072661741</v>
       </c>
       <c r="Q25">
-        <v>504.6372131861741</v>
+        <v>507.292907266174</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08299655609834464</v>
+        <v>0.08297724299305637</v>
       </c>
       <c r="T25">
         <v>0.7644032456634728</v>
       </c>
       <c r="U25">
-        <v>0.06185774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04948619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.519224738021394</v>
+        <v>5.761386913683957</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3529,13 +3529,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07526599037340242</v>
+        <v>0.07475195045862201</v>
       </c>
       <c r="C26">
-        <v>4338.216126973226</v>
+        <v>4428.25203263907</v>
       </c>
       <c r="D26">
-        <v>5215.304126973226</v>
+        <v>5305.340032639069</v>
       </c>
       <c r="E26">
         <v>-511.8119999999999</v>
@@ -3562,37 +3562,37 @@
         <v>435.9</v>
       </c>
       <c r="M26">
-        <v>82.41233062672947</v>
+        <v>78.94838182672947</v>
       </c>
       <c r="N26">
-        <v>353.4876693732706</v>
+        <v>356.9516181732706</v>
       </c>
       <c r="O26">
-        <v>70.69753387465413</v>
+        <v>71.39032363465411</v>
       </c>
       <c r="P26">
-        <v>282.7901354986165</v>
+        <v>285.5612945386164</v>
       </c>
       <c r="Q26">
-        <v>501.8901354986164</v>
+        <v>504.6612945386164</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08340697821131324</v>
+        <v>0.08338745200765479</v>
       </c>
       <c r="T26">
         <v>0.7728375747560853</v>
       </c>
       <c r="U26">
-        <v>0.06185774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04948619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.289257040603837</v>
+        <v>5.521329125613792</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3611,13 +3611,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07524280757380863</v>
+        <v>0.07470799883531977</v>
       </c>
       <c r="C27">
-        <v>4286.810574705602</v>
+        <v>4380.806253615941</v>
       </c>
       <c r="D27">
-        <v>5219.410574705603</v>
+        <v>5313.406253615942</v>
       </c>
       <c r="E27">
         <v>-456.3</v>
@@ -3644,37 +3644,37 @@
         <v>435.9</v>
       </c>
       <c r="M27">
-        <v>85.84617773617653</v>
+        <v>82.23789773617654</v>
       </c>
       <c r="N27">
-        <v>350.0538222638235</v>
+        <v>353.6621022638235</v>
       </c>
       <c r="O27">
-        <v>70.0107644527647</v>
+        <v>70.7324204527647</v>
       </c>
       <c r="P27">
-        <v>280.0430578110588</v>
+        <v>282.9296818110588</v>
       </c>
       <c r="Q27">
-        <v>499.1430578110588</v>
+        <v>502.0296818110588</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08382834491396102</v>
+        <v>0.0838085999293092</v>
       </c>
       <c r="T27">
         <v>0.7814968192911674</v>
       </c>
       <c r="U27">
-        <v>0.06185774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04948619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.077686758979683</v>
+        <v>5.300475960589241</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3693,13 +3693,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07521962477421484</v>
+        <v>0.07466404721201754</v>
       </c>
       <c r="C28">
-        <v>4235.411494237371</v>
+        <v>4333.385039651429</v>
       </c>
       <c r="D28">
-        <v>5223.523494237371</v>
+        <v>5321.497039651429</v>
       </c>
       <c r="E28">
         <v>-400.788</v>
@@ -3726,37 +3726,37 @@
         <v>435.9</v>
       </c>
       <c r="M28">
-        <v>89.28002484562359</v>
+        <v>85.52741364562358</v>
       </c>
       <c r="N28">
-        <v>346.6199751543764</v>
+        <v>350.3725863543764</v>
       </c>
       <c r="O28">
-        <v>69.3239950308753</v>
+        <v>70.07451727087529</v>
       </c>
       <c r="P28">
-        <v>277.2959801235012</v>
+        <v>280.2980690835012</v>
       </c>
       <c r="Q28">
-        <v>496.3959801235011</v>
+        <v>499.3980690835011</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08426109990586952</v>
+        <v>0.08424113022722453</v>
       </c>
       <c r="T28">
         <v>0.790390097462333</v>
       </c>
       <c r="U28">
-        <v>0.06185774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04948619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.882391114403542</v>
+        <v>5.096611500566578</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3775,13 +3775,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07519644197462105</v>
+        <v>0.07462009558871531</v>
       </c>
       <c r="C29">
-        <v>4184.018900880013</v>
+        <v>4285.988503133176</v>
       </c>
       <c r="D29">
-        <v>5227.642900880014</v>
+        <v>5329.612503133177</v>
       </c>
       <c r="E29">
         <v>-345.2759999999998</v>
@@ -3808,37 +3808,37 @@
         <v>435.9</v>
       </c>
       <c r="M29">
-        <v>92.71387195507066</v>
+        <v>88.81692955507066</v>
       </c>
       <c r="N29">
-        <v>343.1861280449294</v>
+        <v>347.0830704449294</v>
       </c>
       <c r="O29">
-        <v>68.63722560898587</v>
+        <v>69.41661408898588</v>
       </c>
       <c r="P29">
-        <v>274.5489024359435</v>
+        <v>277.6664563559435</v>
       </c>
       <c r="Q29">
-        <v>493.6489024359435</v>
+        <v>496.7664563559435</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08470571119892623</v>
+        <v>0.08468551067028822</v>
       </c>
       <c r="T29">
         <v>0.7995270270902428</v>
       </c>
       <c r="U29">
-        <v>0.06185774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.04948619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.701561813870077</v>
+        <v>4.907848111656704</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3857,13 +3857,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07517325917502726</v>
+        <v>0.07457614396541307</v>
       </c>
       <c r="C30">
-        <v>4132.632809993363</v>
+        <v>4238.616757135456</v>
       </c>
       <c r="D30">
-        <v>5231.768809993363</v>
+        <v>5337.752757135457</v>
       </c>
       <c r="E30">
         <v>-289.7639999999999</v>
@@ -3890,37 +3890,37 @@
         <v>435.9</v>
       </c>
       <c r="M30">
-        <v>96.14771906451772</v>
+        <v>92.10644546451772</v>
       </c>
       <c r="N30">
-        <v>339.7522809354823</v>
+        <v>343.7935545354823</v>
       </c>
       <c r="O30">
-        <v>67.95045618709646</v>
+        <v>68.75871090709647</v>
       </c>
       <c r="P30">
-        <v>271.8018247483859</v>
+        <v>275.0348436283858</v>
       </c>
       <c r="Q30">
-        <v>490.9018247483858</v>
+        <v>494.1348436283858</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08516267280567894</v>
+        <v>0.08514223501454812</v>
       </c>
       <c r="T30">
         <v>0.8089177603189278</v>
       </c>
       <c r="U30">
-        <v>0.06185774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04948619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.533648891946145</v>
+        <v>4.732567821954679</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3939,13 +3939,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07575327637543347</v>
+        <v>0.07453219234211084</v>
       </c>
       <c r="C31">
-        <v>3975.812496995802</v>
+        <v>4191.269915424412</v>
       </c>
       <c r="D31">
-        <v>5130.460496995802</v>
+        <v>5345.917915424412</v>
       </c>
       <c r="E31">
         <v>-234.2520000000002</v>
@@ -3972,45 +3972,45 @@
         <v>435.9</v>
       </c>
       <c r="M31">
-        <v>103.7671709739648</v>
+        <v>95.39596137396477</v>
       </c>
       <c r="N31">
-        <v>332.1328290260353</v>
+        <v>340.5040386260353</v>
       </c>
       <c r="O31">
-        <v>66.42656580520706</v>
+        <v>68.10080772520705</v>
       </c>
       <c r="P31">
-        <v>265.7062632208282</v>
+        <v>272.4032309008282</v>
       </c>
       <c r="Q31">
-        <v>484.8062632208282</v>
+        <v>491.5032309008282</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08563250657036836</v>
+        <v>0.08561182483329421</v>
       </c>
       <c r="T31">
         <v>0.8185730212441955</v>
       </c>
       <c r="U31">
-        <v>0.06445774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.05156619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.200750544788077</v>
+        <v>4.569375828094174</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4021,13 +4021,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07575089357583967</v>
+        <v>0.0750882407188086</v>
       </c>
       <c r="C32">
-        <v>3920.708660416947</v>
+        <v>4034.263632877007</v>
       </c>
       <c r="D32">
-        <v>5130.868660416947</v>
+        <v>5244.423632877007</v>
       </c>
       <c r="E32">
         <v>-178.74</v>
@@ -4054,37 +4054,37 @@
         <v>435.9</v>
       </c>
       <c r="M32">
-        <v>107.3453492834118</v>
+        <v>102.8488772834118</v>
       </c>
       <c r="N32">
-        <v>328.5546507165882</v>
+        <v>333.0511227165882</v>
       </c>
       <c r="O32">
-        <v>65.71093014331764</v>
+        <v>66.61022454331764</v>
       </c>
       <c r="P32">
-        <v>262.8437205732706</v>
+        <v>266.4408981732706</v>
       </c>
       <c r="Q32">
-        <v>481.9437205732705</v>
+        <v>485.5408981732705</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08611576415690603</v>
+        <v>0.08609483150400449</v>
       </c>
       <c r="T32">
         <v>0.828504146767328</v>
       </c>
       <c r="U32">
-        <v>0.06445774444168939</v>
+        <v>0.06175774444168938</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335151</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.060725526628474</v>
+        <v>4.238257251937013</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4103,13 +4103,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07641811077624588</v>
+        <v>0.07506428909550636</v>
       </c>
       <c r="C33">
-        <v>3753.386893698377</v>
+        <v>3983.043979049573</v>
       </c>
       <c r="D33">
-        <v>5019.058893698377</v>
+        <v>5248.715979049573</v>
       </c>
       <c r="E33">
         <v>-123.2280000000001</v>
@@ -4136,45 +4136,45 @@
         <v>435.9</v>
       </c>
       <c r="M33">
-        <v>115.5698819928589</v>
+        <v>106.2771731928589</v>
       </c>
       <c r="N33">
-        <v>320.3301180071412</v>
+        <v>329.6228268071412</v>
       </c>
       <c r="O33">
-        <v>64.06602360142823</v>
+        <v>65.92456536142824</v>
       </c>
       <c r="P33">
-        <v>256.2640944057129</v>
+        <v>263.6982614457129</v>
       </c>
       <c r="Q33">
-        <v>475.3640944057129</v>
+        <v>482.7982614457129</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08661302920972017</v>
+        <v>0.08659183836806869</v>
       </c>
       <c r="T33">
         <v>0.8387231310012758</v>
       </c>
       <c r="U33">
-        <v>0.06715774444168938</v>
+        <v>0.06175774444168938</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.05372619555335151</v>
+        <v>0.04940619555335151</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.771743922235159</v>
+        <v>4.101539276068078</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4185,13 +4185,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07643732797665209</v>
+        <v>0.07593633747220412</v>
       </c>
       <c r="C34">
-        <v>3694.726699420982</v>
+        <v>3775.651072701899</v>
       </c>
       <c r="D34">
-        <v>5015.910699420982</v>
+        <v>5096.8350727019</v>
       </c>
       <c r="E34">
         <v>-67.71599999999989</v>
@@ -4218,37 +4218,37 @@
         <v>435.9</v>
       </c>
       <c r="M34">
-        <v>119.297942702306</v>
+        <v>115.922813102306</v>
       </c>
       <c r="N34">
-        <v>316.602057297694</v>
+        <v>319.9771868976941</v>
       </c>
       <c r="O34">
-        <v>63.32041145953881</v>
+        <v>63.99543737953882</v>
       </c>
       <c r="P34">
-        <v>253.2816458381552</v>
+        <v>255.9817495181553</v>
       </c>
       <c r="Q34">
-        <v>472.3816458381552</v>
+        <v>475.0817495181552</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08712491970526413</v>
+        <v>0.08710346308107594</v>
       </c>
       <c r="T34">
         <v>0.8492426735950458</v>
       </c>
       <c r="U34">
-        <v>0.06715774444168938</v>
+        <v>0.06525774444168939</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.05372619555335151</v>
+        <v>0.05220619555335151</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.65387692466531</v>
+        <v>3.760260714302222</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.0764565451770583</v>
+        <v>0.07594038584890188</v>
       </c>
       <c r="C35">
-        <v>3636.070452064547</v>
+        <v>3719.454479331261</v>
       </c>
       <c r="D35">
-        <v>5012.766452064547</v>
+        <v>5096.150479331261</v>
       </c>
       <c r="E35">
         <v>-12.20399999999995</v>
@@ -4300,37 +4300,37 @@
         <v>435.9</v>
       </c>
       <c r="M35">
-        <v>123.026003411753</v>
+        <v>119.545401011753</v>
       </c>
       <c r="N35">
-        <v>312.873996588247</v>
+        <v>316.354598988247</v>
       </c>
       <c r="O35">
-        <v>62.5747993176494</v>
+        <v>63.27091979764941</v>
       </c>
       <c r="P35">
-        <v>250.2991972705976</v>
+        <v>253.0836791905976</v>
       </c>
       <c r="Q35">
-        <v>469.3991972705976</v>
+        <v>472.1836791905976</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08765209051410791</v>
+        <v>0.08763036017357595</v>
       </c>
       <c r="T35">
         <v>0.8600762323856447</v>
       </c>
       <c r="U35">
-        <v>0.06715774444168938</v>
+        <v>0.06525774444168939</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05372619555335151</v>
+        <v>0.05220619555335151</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.543153381493634</v>
+        <v>3.646313419929428</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4349,13 +4349,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07775416237746449</v>
+        <v>0.07594443422559966</v>
       </c>
       <c r="C36">
-        <v>3376.996490621756</v>
+        <v>3663.258069841451</v>
       </c>
       <c r="D36">
-        <v>4809.204490621757</v>
+        <v>5095.466069841452</v>
       </c>
       <c r="E36">
         <v>43.30800000000022</v>
@@ -4382,45 +4382,45 @@
         <v>435.9</v>
       </c>
       <c r="M36">
-        <v>135.6248817212001</v>
+        <v>123.1679889212001</v>
       </c>
       <c r="N36">
-        <v>300.2751182787999</v>
+        <v>312.7320110787999</v>
       </c>
       <c r="O36">
-        <v>60.05502365575999</v>
+        <v>62.54640221575999</v>
       </c>
       <c r="P36">
-        <v>240.22009462304</v>
+        <v>250.1856088630399</v>
       </c>
       <c r="Q36">
-        <v>459.3200946230399</v>
+        <v>469.2856088630399</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08819523619594696</v>
+        <v>0.08817322384463658</v>
       </c>
       <c r="T36">
         <v>0.8712380808365647</v>
       </c>
       <c r="U36">
-        <v>0.07185774444168938</v>
+        <v>0.06525774444168939</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.05748619555335151</v>
+        <v>0.05220619555335151</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.214012019535371</v>
+        <v>3.539068907578562</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4431,13 +4431,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07781097957787073</v>
+        <v>0.07673248260229741</v>
       </c>
       <c r="C37">
-        <v>3312.948496442837</v>
+        <v>3477.931925387401</v>
       </c>
       <c r="D37">
-        <v>4800.668496442837</v>
+        <v>4965.651925387401</v>
       </c>
       <c r="E37">
         <v>98.82000000000016</v>
@@ -4464,37 +4464,37 @@
         <v>435.9</v>
       </c>
       <c r="M37">
-        <v>139.6138488306471</v>
+        <v>132.2307528306471</v>
       </c>
       <c r="N37">
-        <v>296.2861511693529</v>
+        <v>303.6692471693529</v>
       </c>
       <c r="O37">
-        <v>59.25723023387059</v>
+        <v>60.73384943387058</v>
       </c>
       <c r="P37">
-        <v>237.0289209354823</v>
+        <v>242.9353977354823</v>
       </c>
       <c r="Q37">
-        <v>456.1289209354823</v>
+        <v>462.0353977354823</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08875509405261184</v>
+        <v>0.08873279101326828</v>
       </c>
       <c r="T37">
         <v>0.8827433707782824</v>
       </c>
       <c r="U37">
-        <v>0.07185774444168938</v>
+        <v>0.06805774444168938</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.05748619555335151</v>
+        <v>0.05444619555335151</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.122183104691503</v>
+        <v>3.296510007458503</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4513,13 +4513,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07786779677827693</v>
+        <v>0.07675893097899517</v>
       </c>
       <c r="C38">
-        <v>3248.930750135035</v>
+        <v>3418.177742969614</v>
       </c>
       <c r="D38">
-        <v>4792.162750135035</v>
+        <v>4961.409742969614</v>
       </c>
       <c r="E38">
         <v>154.3319999999999</v>
@@ -4546,37 +4546,37 @@
         <v>435.9</v>
       </c>
       <c r="M38">
-        <v>143.6028159400942</v>
+        <v>136.0087743400942</v>
       </c>
       <c r="N38">
-        <v>292.2971840599058</v>
+        <v>299.8912256599058</v>
       </c>
       <c r="O38">
-        <v>58.45943681198116</v>
+        <v>59.97824513198117</v>
       </c>
       <c r="P38">
-        <v>233.8377472479247</v>
+        <v>239.9129805279247</v>
       </c>
       <c r="Q38">
-        <v>452.9377472479246</v>
+        <v>459.0129805279246</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08933244746729747</v>
+        <v>0.08930984465591973</v>
       </c>
       <c r="T38">
         <v>0.8946082010306785</v>
       </c>
       <c r="U38">
-        <v>0.07185774444168938</v>
+        <v>0.06805774444168938</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05748619555335151</v>
+        <v>0.05444619555335151</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.03545579622785</v>
+        <v>3.2049402850291</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4595,13 +4595,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08067741397868314</v>
+        <v>0.07678537935569293</v>
       </c>
       <c r="C39">
-        <v>2807.376857861872</v>
+        <v>3358.430802602168</v>
       </c>
       <c r="D39">
-        <v>4406.120857861873</v>
+        <v>4957.174802602168</v>
       </c>
       <c r="E39">
         <v>209.8440000000001</v>
@@ -4628,45 +4628,45 @@
         <v>435.9</v>
       </c>
       <c r="M39">
-        <v>166.6934622495413</v>
+        <v>139.7867958495412</v>
       </c>
       <c r="N39">
-        <v>269.2065377504588</v>
+        <v>296.1132041504588</v>
       </c>
       <c r="O39">
-        <v>53.84130755009176</v>
+        <v>59.22264083009176</v>
       </c>
       <c r="P39">
-        <v>215.365230200367</v>
+        <v>236.890563320367</v>
       </c>
       <c r="Q39">
-        <v>434.465230200367</v>
+        <v>455.990563320367</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08992812956181441</v>
+        <v>0.08990521746182997</v>
       </c>
       <c r="T39">
         <v>0.9068496925609287</v>
       </c>
       <c r="U39">
-        <v>0.08115774444168938</v>
+        <v>0.06805774444168938</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.06492619555335151</v>
+        <v>0.05444619555335151</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.614979580587598</v>
+        <v>3.118320277325611</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4677,13 +4677,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08080863117908935</v>
+        <v>0.0768118277323907</v>
       </c>
       <c r="C40">
-        <v>2735.350106380662</v>
+        <v>3298.691085755961</v>
       </c>
       <c r="D40">
-        <v>4389.606106380662</v>
+        <v>4952.947085755961</v>
       </c>
       <c r="E40">
         <v>265.3560000000002</v>
@@ -4710,45 +4710,45 @@
         <v>435.9</v>
       </c>
       <c r="M40">
-        <v>171.1986909589883</v>
+        <v>143.5648173589883</v>
       </c>
       <c r="N40">
-        <v>264.7013090410117</v>
+        <v>292.3351826410117</v>
       </c>
       <c r="O40">
-        <v>52.94026180820234</v>
+        <v>58.46703652820234</v>
       </c>
       <c r="P40">
-        <v>211.7610472328094</v>
+        <v>233.8681461128093</v>
       </c>
       <c r="Q40">
-        <v>430.8610472328094</v>
+        <v>452.9681461128093</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09054302720776737</v>
+        <v>0.09051979584212441</v>
       </c>
       <c r="T40">
         <v>0.9194860709147352</v>
       </c>
       <c r="U40">
-        <v>0.08115774444168938</v>
+        <v>0.06805774444168938</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.06492619555335151</v>
+        <v>0.05444619555335151</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.546164328466872</v>
+        <v>3.036259217395989</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4759,13 +4759,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08240624837949556</v>
+        <v>0.07927187610908847</v>
       </c>
       <c r="C41">
-        <v>2488.26124371341</v>
+        <v>2879.157379937223</v>
       </c>
       <c r="D41">
-        <v>4198.02924371341</v>
+        <v>4588.925379937223</v>
       </c>
       <c r="E41">
         <v>320.8679999999999</v>
@@ -4792,45 +4792,45 @@
         <v>435.9</v>
       </c>
       <c r="M41">
-        <v>185.8792692684354</v>
+        <v>164.2295892684354</v>
       </c>
       <c r="N41">
-        <v>250.0207307315646</v>
+        <v>271.6704107315646</v>
       </c>
       <c r="O41">
-        <v>50.00414614631293</v>
+        <v>54.33408214631293</v>
       </c>
       <c r="P41">
-        <v>200.0165845852517</v>
+        <v>217.3363285852517</v>
       </c>
       <c r="Q41">
-        <v>419.1165845852516</v>
+        <v>436.4363285852517</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09117808543227618</v>
+        <v>0.09115452433324817</v>
       </c>
       <c r="T41">
         <v>0.9325367567555519</v>
       </c>
       <c r="U41">
-        <v>0.08585774444168939</v>
+        <v>0.07585774444168938</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.06868619555335152</v>
+        <v>0.06068619555335151</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.345070548832964</v>
+        <v>2.654211107399872</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4841,13 +4841,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08257506557990177</v>
+        <v>0.07936072448578624</v>
       </c>
       <c r="C42">
-        <v>2413.478046423299</v>
+        <v>2811.496697897676</v>
       </c>
       <c r="D42">
-        <v>4178.758046423299</v>
+        <v>4576.776697897676</v>
       </c>
       <c r="E42">
         <v>376.3800000000001</v>
@@ -4874,45 +4874,45 @@
         <v>435.9</v>
       </c>
       <c r="M42">
-        <v>190.6454043778825</v>
+        <v>168.4406043778824</v>
       </c>
       <c r="N42">
-        <v>245.2545956221176</v>
+        <v>267.4593956221176</v>
       </c>
       <c r="O42">
-        <v>49.05091912442352</v>
+        <v>53.49187912442352</v>
       </c>
       <c r="P42">
-        <v>196.2036764976941</v>
+        <v>213.9675164976941</v>
       </c>
       <c r="Q42">
-        <v>415.303676497694</v>
+        <v>433.067516497694</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09183431226426861</v>
+        <v>0.09181041044074273</v>
       </c>
       <c r="T42">
         <v>0.9460224654577292</v>
       </c>
       <c r="U42">
-        <v>0.08585774444168939</v>
+        <v>0.07585774444168938</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.06868619555335152</v>
+        <v>0.06068619555335151</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.28644378511214</v>
+        <v>2.587855829714876</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4923,13 +4923,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08274388278030798</v>
+        <v>0.079449572862484</v>
       </c>
       <c r="C43">
-        <v>2338.87097082534</v>
+        <v>2743.900170650387</v>
       </c>
       <c r="D43">
-        <v>4159.66297082534</v>
+        <v>4564.692170650387</v>
       </c>
       <c r="E43">
         <v>431.8920000000003</v>
@@ -4956,45 +4956,45 @@
         <v>435.9</v>
       </c>
       <c r="M43">
-        <v>195.4115394873295</v>
+        <v>172.6516194873295</v>
       </c>
       <c r="N43">
-        <v>240.4884605126705</v>
+        <v>263.2483805126705</v>
       </c>
       <c r="O43">
-        <v>48.0976921025341</v>
+        <v>52.6496761025341</v>
       </c>
       <c r="P43">
-        <v>192.3907684101364</v>
+        <v>210.5987044101364</v>
       </c>
       <c r="Q43">
-        <v>411.4907684101364</v>
+        <v>429.6987044101364</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.0925127840736167</v>
+        <v>0.09248852997560997</v>
       </c>
       <c r="T43">
         <v>0.9599653168277767</v>
       </c>
       <c r="U43">
-        <v>0.08585774444168939</v>
+        <v>0.07585774444168938</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.06868619555335152</v>
+        <v>0.06068619555335151</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.230676863524038</v>
+        <v>2.524737394843781</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5005,13 +5005,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08291269998071418</v>
+        <v>0.08084882123918176</v>
       </c>
       <c r="C44">
-        <v>2264.437613507414</v>
+        <v>2506.152709254407</v>
       </c>
       <c r="D44">
-        <v>4140.741613507414</v>
+        <v>4382.456709254407</v>
       </c>
       <c r="E44">
         <v>487.404</v>
@@ -5038,37 +5038,37 @@
         <v>435.9</v>
       </c>
       <c r="M44">
-        <v>200.1776745967766</v>
+        <v>185.9555001967766</v>
       </c>
       <c r="N44">
-        <v>235.7223254032235</v>
+        <v>249.9444998032235</v>
       </c>
       <c r="O44">
-        <v>47.14446508064469</v>
+        <v>49.98889996064469</v>
       </c>
       <c r="P44">
-        <v>188.5778603225788</v>
+        <v>199.9555998425788</v>
       </c>
       <c r="Q44">
-        <v>407.6778603225787</v>
+        <v>419.0555998425788</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.09321465146259748</v>
+        <v>0.093190032942714</v>
       </c>
       <c r="T44">
         <v>0.9743889561761017</v>
       </c>
       <c r="U44">
-        <v>0.08585774444168939</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.06868619555335152</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.177565509630609</v>
+        <v>2.344109206443123</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5087,13 +5087,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08308151718112039</v>
+        <v>0.08096886961587953</v>
       </c>
       <c r="C45">
-        <v>2190.175614589671</v>
+        <v>2435.681263027089</v>
       </c>
       <c r="D45">
-        <v>4121.991614589671</v>
+        <v>4367.49726302709</v>
       </c>
       <c r="E45">
         <v>542.9160000000002</v>
@@ -5120,37 +5120,37 @@
         <v>435.9</v>
       </c>
       <c r="M45">
-        <v>204.9438097062236</v>
+        <v>190.3830121062236</v>
       </c>
       <c r="N45">
-        <v>230.9561902937764</v>
+        <v>245.5169878937764</v>
       </c>
       <c r="O45">
-        <v>46.19123805875528</v>
+        <v>49.10339757875528</v>
       </c>
       <c r="P45">
-        <v>184.7649522350211</v>
+        <v>196.4135903150211</v>
       </c>
       <c r="Q45">
-        <v>403.8649522350211</v>
+        <v>415.5135903150211</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.09394114577750742</v>
+        <v>0.09391615004901468</v>
       </c>
       <c r="T45">
         <v>0.9893186881331401</v>
       </c>
       <c r="U45">
-        <v>0.08585774444168939</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.06868619555335152</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.126924451267107</v>
+        <v>2.289595038851423</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5169,13 +5169,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.0832503343815266</v>
+        <v>0.08108891799257729</v>
       </c>
       <c r="C46">
-        <v>2116.082656743374</v>
+        <v>2365.311597037767</v>
       </c>
       <c r="D46">
-        <v>4103.410656743374</v>
+        <v>4352.639597037767</v>
       </c>
       <c r="E46">
         <v>598.4279999999999</v>
@@ -5202,37 +5202,37 @@
         <v>435.9</v>
       </c>
       <c r="M46">
-        <v>209.7099448156707</v>
+        <v>194.8105240156707</v>
       </c>
       <c r="N46">
-        <v>226.1900551843293</v>
+        <v>241.0894759843294</v>
       </c>
       <c r="O46">
-        <v>45.23801103686587</v>
+        <v>48.21789519686588</v>
       </c>
       <c r="P46">
-        <v>180.9520441474635</v>
+        <v>192.8715807874635</v>
       </c>
       <c r="Q46">
-        <v>400.0520441474634</v>
+        <v>411.9715807874635</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09469358631794987</v>
+        <v>0.09466819990911182</v>
       </c>
       <c r="T46">
         <v>1.00478162480293</v>
       </c>
       <c r="U46">
-        <v>0.08585774444168939</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.06868619555335152</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.078585259192854</v>
+        <v>2.237558787968436</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5251,13 +5251,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08341915158193282</v>
+        <v>0.08120896636927505</v>
       </c>
       <c r="C47">
-        <v>2042.156464236142</v>
+        <v>2295.042676078104</v>
       </c>
       <c r="D47">
-        <v>4084.996464236141</v>
+        <v>4337.882676078104</v>
       </c>
       <c r="E47">
         <v>653.9400000000001</v>
@@ -5284,37 +5284,37 @@
         <v>435.9</v>
       </c>
       <c r="M47">
-        <v>214.4760799251178</v>
+        <v>199.2380359251177</v>
       </c>
       <c r="N47">
-        <v>221.4239200748823</v>
+        <v>236.6619640748823</v>
       </c>
       <c r="O47">
-        <v>44.28478401497645</v>
+        <v>47.33239281497646</v>
       </c>
       <c r="P47">
-        <v>177.1391360599058</v>
+        <v>189.3295712599058</v>
       </c>
       <c r="Q47">
-        <v>396.2391360599058</v>
+        <v>408.4295712599058</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09547338833259023</v>
+        <v>0.09544759703684885</v>
       </c>
       <c r="T47">
         <v>1.020806850078893</v>
       </c>
       <c r="U47">
-        <v>0.08585774444168939</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.06868619555335152</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.032394475655235</v>
+        <v>2.187835259346915</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5333,13 +5333,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08958636878233901</v>
+        <v>0.08132901474597282</v>
       </c>
       <c r="C48">
-        <v>1411.281373885587</v>
+        <v>2224.873478931155</v>
       </c>
       <c r="D48">
-        <v>3509.633373885587</v>
+        <v>4323.225478931156</v>
       </c>
       <c r="E48">
         <v>709.4520000000002</v>
@@ -5366,45 +5366,45 @@
         <v>435.9</v>
       </c>
       <c r="M48">
-        <v>260.8651126345648</v>
+        <v>203.6655478345648</v>
       </c>
       <c r="N48">
-        <v>175.0348873654352</v>
+        <v>232.2344521654352</v>
       </c>
       <c r="O48">
-        <v>35.00697747308705</v>
+        <v>46.44689043308705</v>
       </c>
       <c r="P48">
-        <v>140.0279098923482</v>
+        <v>185.7875617323482</v>
       </c>
       <c r="Q48">
-        <v>359.1279098923482</v>
+        <v>404.8875617323481</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09628207190332835</v>
+        <v>0.09625586072487244</v>
       </c>
       <c r="T48">
         <v>1.03742560221693</v>
       </c>
       <c r="U48">
-        <v>0.1021577444416894</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.08172619555335152</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.670978520652681</v>
+        <v>2.140273623274156</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5415,13 +5415,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08988558598274522</v>
+        <v>0.08144906312267058</v>
       </c>
       <c r="C49">
-        <v>1331.948829161576</v>
+        <v>2154.802998135792</v>
       </c>
       <c r="D49">
-        <v>3485.812829161576</v>
+        <v>4308.666998135792</v>
       </c>
       <c r="E49">
         <v>764.9639999999999</v>
@@ -5448,45 +5448,45 @@
         <v>435.9</v>
       </c>
       <c r="M49">
-        <v>266.5360933440119</v>
+        <v>208.0930597440119</v>
       </c>
       <c r="N49">
-        <v>169.3639066559882</v>
+        <v>227.8069402559882</v>
       </c>
       <c r="O49">
-        <v>33.87278133119764</v>
+        <v>45.56138805119764</v>
       </c>
       <c r="P49">
-        <v>135.4911253247905</v>
+        <v>182.2455522047905</v>
       </c>
       <c r="Q49">
-        <v>354.5911253247905</v>
+        <v>401.3455522047905</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09712127183522642</v>
+        <v>0.09709462492942522</v>
       </c>
       <c r="T49">
         <v>1.054671477077157</v>
       </c>
       <c r="U49">
-        <v>0.1021577444416894</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.08172619555335152</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.635425786170709</v>
+        <v>2.094735886608749</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5497,13 +5497,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09018480318315143</v>
+        <v>0.08156911149936835</v>
       </c>
       <c r="C50">
-        <v>1252.937453675379</v>
+        <v>2084.830239755854</v>
       </c>
       <c r="D50">
-        <v>3462.313453675379</v>
+        <v>4294.206239755854</v>
       </c>
       <c r="E50">
         <v>820.4760000000001</v>
@@ -5530,45 +5530,45 @@
         <v>435.9</v>
       </c>
       <c r="M50">
-        <v>272.2070740534589</v>
+        <v>212.5205716534589</v>
       </c>
       <c r="N50">
-        <v>163.6929259465411</v>
+        <v>223.3794283465411</v>
       </c>
       <c r="O50">
-        <v>32.73858518930822</v>
+        <v>44.67588566930822</v>
       </c>
       <c r="P50">
-        <v>130.9543407572329</v>
+        <v>178.7035426772329</v>
       </c>
       <c r="Q50">
-        <v>350.0543407572328</v>
+        <v>397.8035426772328</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09799274868758212</v>
+        <v>0.09796564929569157</v>
       </c>
       <c r="T50">
         <v>1.072580654816623</v>
       </c>
       <c r="U50">
-        <v>0.1021577444416894</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.08172619555335152</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.601354415625486</v>
+        <v>2.051095555637733</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5579,13 +5579,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09048402038355764</v>
+        <v>0.08168915987606611</v>
       </c>
       <c r="C51">
-        <v>1174.240795499037</v>
+        <v>2014.954223153954</v>
       </c>
       <c r="D51">
-        <v>3439.128795499037</v>
+        <v>4279.842223153953</v>
       </c>
       <c r="E51">
         <v>875.9879999999998</v>
@@ -5612,45 +5612,45 @@
         <v>435.9</v>
       </c>
       <c r="M51">
-        <v>277.878054762906</v>
+        <v>216.948083562906</v>
       </c>
       <c r="N51">
-        <v>158.021945237094</v>
+        <v>218.9519164370941</v>
       </c>
       <c r="O51">
-        <v>31.60438904741881</v>
+        <v>43.79038328741882</v>
       </c>
       <c r="P51">
-        <v>126.4175561896752</v>
+        <v>175.1615331496753</v>
       </c>
       <c r="Q51">
-        <v>345.5175561896752</v>
+        <v>394.2615331496752</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09889840110277529</v>
+        <v>0.09887083148024287</v>
       </c>
       <c r="T51">
         <v>1.091192153251754</v>
       </c>
       <c r="U51">
-        <v>0.1021577444416894</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.08172619555335152</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.568673713265782</v>
+        <v>2.009236462665535</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5661,13 +5661,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09078323758396384</v>
+        <v>0.08748920825276388</v>
       </c>
       <c r="C52">
-        <v>1095.852574371005</v>
+        <v>1364.005346818435</v>
       </c>
       <c r="D52">
-        <v>3416.252574371005</v>
+        <v>3684.405346818434</v>
       </c>
       <c r="E52">
         <v>931.5</v>
@@ -5694,37 +5694,37 @@
         <v>435.9</v>
       </c>
       <c r="M52">
-        <v>283.5490354723531</v>
+        <v>260.789115472353</v>
       </c>
       <c r="N52">
-        <v>152.350964527647</v>
+        <v>175.110884527647</v>
       </c>
       <c r="O52">
-        <v>30.47019290552939</v>
+        <v>35.0221769055294</v>
       </c>
       <c r="P52">
-        <v>121.8807716221176</v>
+        <v>140.0887076221176</v>
       </c>
       <c r="Q52">
-        <v>340.9807716221176</v>
+        <v>359.1887076221176</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09984027961457617</v>
+        <v>0.09981222095217623</v>
       </c>
       <c r="T52">
         <v>1.110548111624291</v>
       </c>
       <c r="U52">
-        <v>0.1021577444416894</v>
+        <v>0.09395774444168939</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.08172619555335152</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.537300239000466</v>
+        <v>1.671465464386726</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5743,13 +5743,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09108245478437005</v>
+        <v>0.08772285662946164</v>
       </c>
       <c r="C53">
-        <v>1017.766676024473</v>
+        <v>1287.959075120553</v>
       </c>
       <c r="D53">
-        <v>3393.678676024474</v>
+        <v>3663.871075120554</v>
       </c>
       <c r="E53">
         <v>987.0120000000002</v>
@@ -5776,37 +5776,37 @@
         <v>435.9</v>
       </c>
       <c r="M53">
-        <v>289.2200161818001</v>
+        <v>266.0048977818001</v>
       </c>
       <c r="N53">
-        <v>146.6799838181999</v>
+        <v>169.8951022181999</v>
       </c>
       <c r="O53">
-        <v>29.33599676363998</v>
+        <v>33.97902044363998</v>
       </c>
       <c r="P53">
-        <v>117.3439870545599</v>
+        <v>135.9160817745599</v>
       </c>
       <c r="Q53">
-        <v>336.4439870545599</v>
+        <v>355.0160817745599</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1008206021472669</v>
+        <v>0.1007920344841885</v>
       </c>
       <c r="T53">
         <v>1.130694109114074</v>
       </c>
       <c r="U53">
-        <v>0.1021577444416894</v>
+        <v>0.09395774444168939</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.08172619555335152</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.50715709705928</v>
+        <v>1.638691631751692</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5825,13 +5825,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1206177798190752</v>
+        <v>0.08795650500615941</v>
       </c>
       <c r="C54">
-        <v>-377.4456332083814</v>
+        <v>1212.140421876724</v>
       </c>
       <c r="D54">
-        <v>2053.978366791619</v>
+        <v>3643.564421876724</v>
       </c>
       <c r="E54">
         <v>1042.524</v>
@@ -5858,45 +5858,45 @@
         <v>435.9</v>
       </c>
       <c r="M54">
-        <v>483.6762064912472</v>
+        <v>271.2206800912472</v>
       </c>
       <c r="N54">
-        <v>-47.77620649124714</v>
+        <v>164.6793199087529</v>
       </c>
       <c r="O54">
-        <v>-9.555241298249427</v>
+        <v>32.93586398175057</v>
       </c>
       <c r="P54">
-        <v>-38.22096519299771</v>
+        <v>131.7434559270023</v>
       </c>
       <c r="Q54">
-        <v>180.8790348070023</v>
+        <v>350.8434559270023</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1024843025083177</v>
+        <v>0.1018126735800346</v>
       </c>
       <c r="T54">
-        <v>1.164883778513476</v>
+        <v>1.151679523165931</v>
       </c>
       <c r="U54">
-        <v>0.1675577444416894</v>
+        <v>0.09395774444168939</v>
       </c>
       <c r="V54">
-        <v>0.1802445496180877</v>
+        <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.1373563742597745</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.9012227480904382</v>
+        <v>1.607178331141082</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5907,13 +5907,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1218353572634921</v>
+        <v>0.08819015338285717</v>
       </c>
       <c r="C55">
-        <v>-465.848617360125</v>
+        <v>1136.545623287241</v>
       </c>
       <c r="D55">
-        <v>2021.087382639875</v>
+        <v>3623.481623287241</v>
       </c>
       <c r="E55">
         <v>1098.036</v>
@@ -5940,45 +5940,45 @@
         <v>435.9</v>
       </c>
       <c r="M55">
-        <v>492.9776720006943</v>
+        <v>276.4364624006943</v>
       </c>
       <c r="N55">
-        <v>-57.07767200069424</v>
+        <v>159.4635375993058</v>
       </c>
       <c r="O55">
-        <v>-11.41553440013885</v>
+        <v>31.89270751986115</v>
       </c>
       <c r="P55">
-        <v>-45.66213760055539</v>
+        <v>127.5708300794446</v>
       </c>
       <c r="Q55">
-        <v>173.4378623994446</v>
+        <v>346.6708300794446</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1036903514978564</v>
+        <v>0.1028767441267678</v>
       </c>
       <c r="T55">
-        <v>1.189668539758443</v>
+        <v>1.173557933560421</v>
       </c>
       <c r="U55">
-        <v>0.1675577444416894</v>
+        <v>0.09395774444168939</v>
       </c>
       <c r="V55">
-        <v>0.1768437090592558</v>
+        <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.1379262114330181</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.884218545296279</v>
+        <v>1.57685421168559</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5989,13 +5989,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.123052934707909</v>
+        <v>0.08842380175955494</v>
       </c>
       <c r="C56">
-        <v>-553.2148170692012</v>
+        <v>1061.170998079589</v>
       </c>
       <c r="D56">
-        <v>1989.233182930799</v>
+        <v>3603.61899807959</v>
       </c>
       <c r="E56">
         <v>1153.548</v>
@@ -6022,45 +6022,45 @@
         <v>435.9</v>
       </c>
       <c r="M56">
-        <v>502.2791375101413</v>
+        <v>281.6522447101413</v>
       </c>
       <c r="N56">
-        <v>-66.37913751014128</v>
+        <v>154.2477552898587</v>
       </c>
       <c r="O56">
-        <v>-13.27582750202826</v>
+        <v>30.84955105797175</v>
       </c>
       <c r="P56">
-        <v>-53.10331000811302</v>
+        <v>123.398204231887</v>
       </c>
       <c r="Q56">
-        <v>165.9966899918869</v>
+        <v>342.4982042318869</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1049488373999837</v>
+        <v>0.1039870786103155</v>
       </c>
       <c r="T56">
-        <v>1.21553089931841</v>
+        <v>1.196387579189453</v>
       </c>
       <c r="U56">
-        <v>0.1675577444416894</v>
+        <v>0.09395774444168939</v>
       </c>
       <c r="V56">
-        <v>0.1735688255581585</v>
+        <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.1384749435257713</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.8678441277907923</v>
+        <v>1.547653207765487</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6071,13 +6071,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1242705121523259</v>
+        <v>0.0886574501362527</v>
       </c>
       <c r="C57">
-        <v>-639.5924937264472</v>
+        <v>986.0129452588617</v>
       </c>
       <c r="D57">
-        <v>1958.367506273553</v>
+        <v>3583.972945258862</v>
       </c>
       <c r="E57">
         <v>1209.06</v>
@@ -6104,45 +6104,45 @@
         <v>435.9</v>
       </c>
       <c r="M57">
-        <v>511.5806030195884</v>
+        <v>286.8680270195884</v>
       </c>
       <c r="N57">
-        <v>-75.68060301958837</v>
+        <v>149.0319729804116</v>
       </c>
       <c r="O57">
-        <v>-15.13612060391767</v>
+        <v>29.80639459608233</v>
       </c>
       <c r="P57">
-        <v>-60.5444824156707</v>
+        <v>119.2255783843293</v>
       </c>
       <c r="Q57">
-        <v>158.5555175843293</v>
+        <v>338.3255783843293</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1062632560088722</v>
+        <v>0.1051467612931319</v>
       </c>
       <c r="T57">
-        <v>1.242542697081041</v>
+        <v>1.220231875735332</v>
       </c>
       <c r="U57">
-        <v>0.1675577444416894</v>
+        <v>0.09395774444168939</v>
       </c>
       <c r="V57">
-        <v>0.1704130287298283</v>
+        <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.1390037217242426</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8520651436491415</v>
+        <v>1.519514058533387</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6153,13 +6153,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1254880895967428</v>
+        <v>0.1157525511729299</v>
       </c>
       <c r="C58">
-        <v>-725.0269591235233</v>
+        <v>-457.6987334697255</v>
       </c>
       <c r="D58">
-        <v>1928.445040876477</v>
+        <v>2195.773266530275</v>
       </c>
       <c r="E58">
         <v>1264.572</v>
@@ -6186,37 +6186,37 @@
         <v>435.9</v>
       </c>
       <c r="M58">
-        <v>520.8820685290355</v>
+        <v>468.6563789290355</v>
       </c>
       <c r="N58">
-        <v>-84.98206852903542</v>
+        <v>-32.75637892903546</v>
       </c>
       <c r="O58">
-        <v>-16.99641370580708</v>
+        <v>-6.551275785807093</v>
       </c>
       <c r="P58">
-        <v>-67.98565482322833</v>
+        <v>-26.20510314322837</v>
       </c>
       <c r="Q58">
-        <v>151.1143451767716</v>
+        <v>192.8948968567716</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1076374209181648</v>
+        <v>0.106893015409499</v>
       </c>
       <c r="T58">
-        <v>1.270782303832882</v>
+        <v>1.256136698332143</v>
       </c>
       <c r="U58">
-        <v>0.1675577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V58">
-        <v>0.1673699389310814</v>
+        <v>0.1860211530657538</v>
       </c>
       <c r="W58">
-        <v>0.1395136149870541</v>
+        <v>0.1227136149870541</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8368496946554069</v>
+        <v>0.9301057653287688</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6235,13 +6235,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1267056670411597</v>
+        <v>0.1168021286173468</v>
       </c>
       <c r="C59">
-        <v>-809.5607974006157</v>
+        <v>-545.6693954631455</v>
       </c>
       <c r="D59">
-        <v>1899.423202599385</v>
+        <v>2163.314604536855</v>
       </c>
       <c r="E59">
         <v>1320.084</v>
@@ -6268,37 +6268,37 @@
         <v>435.9</v>
       </c>
       <c r="M59">
-        <v>530.1835340384825</v>
+        <v>477.0252428384826</v>
       </c>
       <c r="N59">
-        <v>-94.28353403848251</v>
+        <v>-41.12524283848256</v>
       </c>
       <c r="O59">
-        <v>-18.8567068076965</v>
+        <v>-8.225048567696513</v>
       </c>
       <c r="P59">
-        <v>-75.42682723078602</v>
+        <v>-32.90019427078605</v>
       </c>
       <c r="Q59">
-        <v>143.6731727692139</v>
+        <v>186.1998057292139</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1090755004744011</v>
+        <v>0.1083137832097199</v>
       </c>
       <c r="T59">
-        <v>1.300335380666205</v>
+        <v>1.285349179688704</v>
       </c>
       <c r="U59">
-        <v>0.1675577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V59">
-        <v>0.1644336242129922</v>
+        <v>0.1827576240646002</v>
       </c>
       <c r="W59">
-        <v>0.1400056172581881</v>
+        <v>0.1232056172581881</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8221681210649611</v>
+        <v>0.9137881203230008</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6317,13 +6317,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1279232444855766</v>
+        <v>0.1178517060617637</v>
       </c>
       <c r="C60">
-        <v>-893.2340672502646</v>
+        <v>-632.6944065798166</v>
       </c>
       <c r="D60">
-        <v>1871.261932749735</v>
+        <v>2131.801593420183</v>
       </c>
       <c r="E60">
         <v>1375.596</v>
@@ -6350,37 +6350,37 @@
         <v>435.9</v>
       </c>
       <c r="M60">
-        <v>539.4849995479294</v>
+        <v>485.3941067479295</v>
       </c>
       <c r="N60">
-        <v>-103.5849995479294</v>
+        <v>-49.49410674792949</v>
       </c>
       <c r="O60">
-        <v>-20.71699990958588</v>
+        <v>-9.8988213495859</v>
       </c>
       <c r="P60">
-        <v>-82.86799963834351</v>
+        <v>-39.59528539834359</v>
       </c>
       <c r="Q60">
-        <v>136.2320003616564</v>
+        <v>179.5047146016564</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1105820600095059</v>
+        <v>0.1098022066194752</v>
       </c>
       <c r="T60">
-        <v>1.331295746872543</v>
+        <v>1.315952731586054</v>
       </c>
       <c r="U60">
-        <v>0.1675577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V60">
-        <v>0.1615985617265614</v>
+        <v>0.179606630546245</v>
       </c>
       <c r="W60">
-        <v>0.1404806539337657</v>
+        <v>0.1236806539337657</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8079928086328069</v>
+        <v>0.8980331527312252</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6399,13 +6399,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1606072226070548</v>
+        <v>0.1189012835061806</v>
       </c>
       <c r="C61">
-        <v>-1481.46763894857</v>
+        <v>-718.814499367088</v>
       </c>
       <c r="D61">
-        <v>1338.54036105143</v>
+        <v>2101.193500632912</v>
       </c>
       <c r="E61">
         <v>1431.108</v>
@@ -6432,45 +6432,45 @@
         <v>435.9</v>
       </c>
       <c r="M61">
-        <v>719.7523226573766</v>
+        <v>493.7629706573766</v>
       </c>
       <c r="N61">
-        <v>-283.8523226573765</v>
+        <v>-57.86297065737659</v>
       </c>
       <c r="O61">
-        <v>-56.77046453147531</v>
+        <v>-11.57259413147532</v>
       </c>
       <c r="P61">
-        <v>-227.0818581259012</v>
+        <v>-46.29037652590127</v>
       </c>
       <c r="Q61">
-        <v>-7.981858125901255</v>
+        <v>172.8096234740987</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1137923558074484</v>
+        <v>0.1113632360492185</v>
       </c>
       <c r="T61">
-        <v>1.397268535347879</v>
+        <v>1.348049139673519</v>
       </c>
       <c r="U61">
-        <v>0.2197577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V61">
-        <v>0.121124999886246</v>
+        <v>0.1765624503674951</v>
       </c>
       <c r="W61">
-        <v>0.1931395876711881</v>
+        <v>0.1241395876711881</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.6056249994312298</v>
+        <v>0.8828122518374756</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6481,13 +6481,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1623468000514717</v>
+        <v>0.1199508609505974</v>
       </c>
       <c r="C62">
-        <v>-1556.95869130778</v>
+        <v>-804.0681001569833</v>
       </c>
       <c r="D62">
-        <v>1318.561308692219</v>
+        <v>2071.451899843017</v>
       </c>
       <c r="E62">
         <v>1486.62</v>
@@ -6514,45 +6514,45 @@
         <v>435.9</v>
       </c>
       <c r="M62">
-        <v>731.9515145668237</v>
+        <v>502.1318345668237</v>
       </c>
       <c r="N62">
-        <v>-296.0515145668236</v>
+        <v>-66.23183456682369</v>
       </c>
       <c r="O62">
-        <v>-59.21030291336473</v>
+        <v>-13.24636691336474</v>
       </c>
       <c r="P62">
-        <v>-236.8412116534589</v>
+        <v>-52.98546765345895</v>
       </c>
       <c r="Q62">
-        <v>-17.74121165345895</v>
+        <v>166.114532346541</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1154921647026346</v>
+        <v>0.1130023169504489</v>
       </c>
       <c r="T62">
-        <v>1.432200248731576</v>
+        <v>1.381750368165356</v>
       </c>
       <c r="U62">
-        <v>0.2197577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V62">
-        <v>0.1191062498881419</v>
+        <v>0.1736197428613702</v>
       </c>
       <c r="W62">
-        <v>0.1935832236173631</v>
+        <v>0.1245832236173631</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.5955312494407092</v>
+        <v>0.8680987143068509</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6563,13 +6563,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1640863774958886</v>
+        <v>0.1210004383950143</v>
       </c>
       <c r="C63">
-        <v>-1631.86210019391</v>
+        <v>-888.491490006194</v>
       </c>
       <c r="D63">
-        <v>1299.16989980609</v>
+        <v>2042.540509993806</v>
       </c>
       <c r="E63">
         <v>1542.132</v>
@@ -6596,45 +6596,45 @@
         <v>435.9</v>
       </c>
       <c r="M63">
-        <v>744.1507064762708</v>
+        <v>510.5006984762708</v>
       </c>
       <c r="N63">
-        <v>-308.2507064762708</v>
+        <v>-74.60069847627074</v>
       </c>
       <c r="O63">
-        <v>-61.65014129525415</v>
+        <v>-14.92013969525415</v>
       </c>
       <c r="P63">
-        <v>-246.6005651810166</v>
+        <v>-59.68055878101659</v>
       </c>
       <c r="Q63">
-        <v>-27.50056518101664</v>
+        <v>159.4194412189834</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1172791432847534</v>
+        <v>0.1147254532825117</v>
       </c>
       <c r="T63">
-        <v>1.468923332032386</v>
+        <v>1.417179864784981</v>
       </c>
       <c r="U63">
-        <v>0.2197577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V63">
-        <v>0.1171536884145657</v>
+        <v>0.1707735175685609</v>
       </c>
       <c r="W63">
-        <v>0.19401231412268</v>
+        <v>0.12501231412268</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.5857684420728289</v>
+        <v>0.8538675878428041</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6645,13 +6645,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1658259549403055</v>
+        <v>0.1220500158394312</v>
       </c>
       <c r="C64">
-        <v>-1706.203416363833</v>
+        <v>-972.1189523440867</v>
       </c>
       <c r="D64">
-        <v>1280.340583636167</v>
+        <v>2014.425047655913</v>
       </c>
       <c r="E64">
         <v>1597.644</v>
@@ -6678,45 +6678,45 @@
         <v>435.9</v>
       </c>
       <c r="M64">
-        <v>756.3498983857178</v>
+        <v>518.8695623857178</v>
       </c>
       <c r="N64">
-        <v>-320.4498983857177</v>
+        <v>-82.96956238571778</v>
       </c>
       <c r="O64">
-        <v>-64.08997967714355</v>
+        <v>-16.59391247714356</v>
       </c>
       <c r="P64">
-        <v>-256.3599187085742</v>
+        <v>-66.37564990857422</v>
       </c>
       <c r="Q64">
-        <v>-37.25991870857422</v>
+        <v>152.7243500914257</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1191601733711943</v>
+        <v>0.1165392810004726</v>
       </c>
       <c r="T64">
-        <v>1.507579209191132</v>
+        <v>1.454474071753007</v>
       </c>
       <c r="U64">
-        <v>0.2197577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V64">
-        <v>0.115264112794976</v>
+        <v>0.1680191059948744</v>
       </c>
       <c r="W64">
-        <v>0.194427562998793</v>
+        <v>0.125427562998793</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.57632056397488</v>
+        <v>0.8400955299743719</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6727,13 +6727,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1675655323847224</v>
+        <v>0.1230995932838481</v>
       </c>
       <c r="C65">
-        <v>-1780.006730472558</v>
+        <v>-1054.982908592087</v>
       </c>
       <c r="D65">
-        <v>1262.049269527442</v>
+        <v>1987.073091407913</v>
       </c>
       <c r="E65">
         <v>1653.156</v>
@@ -6760,45 +6760,45 @@
         <v>435.9</v>
       </c>
       <c r="M65">
-        <v>768.5490902951649</v>
+        <v>527.2384262951649</v>
       </c>
       <c r="N65">
-        <v>-332.6490902951649</v>
+        <v>-91.33842629516488</v>
       </c>
       <c r="O65">
-        <v>-66.52981805903298</v>
+        <v>-18.26768525903298</v>
       </c>
       <c r="P65">
-        <v>-266.1192722361319</v>
+        <v>-73.07074103613191</v>
       </c>
       <c r="Q65">
-        <v>-47.01927223613194</v>
+        <v>146.0292589638681</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.121142880759605</v>
+        <v>0.1184511534599448</v>
       </c>
       <c r="T65">
-        <v>1.548324593223325</v>
+        <v>1.493784181800386</v>
       </c>
       <c r="U65">
-        <v>0.2197577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V65">
-        <v>0.1134345237029923</v>
+        <v>0.1653521360584478</v>
       </c>
       <c r="W65">
-        <v>0.1948296293709025</v>
+        <v>0.1258296293709025</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.5671726185149613</v>
+        <v>0.8267606802922389</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6809,13 +6809,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1693051098291393</v>
+        <v>0.124149170728265</v>
       </c>
       <c r="C66">
-        <v>-1853.294775901367</v>
+        <v>-1137.11404288239</v>
       </c>
       <c r="D66">
-        <v>1244.273224098633</v>
+        <v>1960.45395711761</v>
       </c>
       <c r="E66">
         <v>1708.668</v>
@@ -6842,45 +6842,45 @@
         <v>435.9</v>
       </c>
       <c r="M66">
-        <v>780.748282204612</v>
+        <v>535.607290204612</v>
       </c>
       <c r="N66">
-        <v>-344.848282204612</v>
+        <v>-99.70729020461198</v>
       </c>
       <c r="O66">
-        <v>-68.96965644092239</v>
+        <v>-19.9414580409224</v>
       </c>
       <c r="P66">
-        <v>-275.8786257636896</v>
+        <v>-79.76583216368958</v>
       </c>
       <c r="Q66">
-        <v>-56.7786257636896</v>
+        <v>139.3341678363104</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1232357385584829</v>
+        <v>0.1204692410560544</v>
       </c>
       <c r="T66">
-        <v>1.591333609701751</v>
+        <v>1.535278186850396</v>
       </c>
       <c r="U66">
-        <v>0.2197577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V66">
-        <v>0.111662109270133</v>
+        <v>0.1627685089325346</v>
       </c>
       <c r="W66">
-        <v>0.1952191311688835</v>
+        <v>0.1262191311688835</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.5583105463506649</v>
+        <v>0.8138425446626727</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6891,13 +6891,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1710446872735562</v>
+        <v>0.1251987481726819</v>
       </c>
       <c r="C67">
-        <v>-1926.089023016617</v>
+        <v>-1218.541416884677</v>
       </c>
       <c r="D67">
-        <v>1226.990976983383</v>
+        <v>1934.538583115323</v>
       </c>
       <c r="E67">
         <v>1764.18</v>
@@ -6924,45 +6924,45 @@
         <v>435.9</v>
       </c>
       <c r="M67">
-        <v>792.9474741140591</v>
+        <v>543.9761541140591</v>
       </c>
       <c r="N67">
-        <v>-357.0474741140591</v>
+        <v>-108.0761541140591</v>
       </c>
       <c r="O67">
-        <v>-71.40949482281182</v>
+        <v>-21.61523082281182</v>
       </c>
       <c r="P67">
-        <v>-285.6379792912472</v>
+        <v>-86.46092329124727</v>
       </c>
       <c r="Q67">
-        <v>-66.53797929124727</v>
+        <v>132.6390767087527</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1254481882315824</v>
+        <v>0.1226026479433702</v>
       </c>
       <c r="T67">
-        <v>1.636800284264658</v>
+        <v>1.579143277903265</v>
       </c>
       <c r="U67">
-        <v>0.2197577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V67">
-        <v>0.1099442306659771</v>
+        <v>0.1602643780258801</v>
       </c>
       <c r="W67">
-        <v>0.1955966482961574</v>
+        <v>0.1265966482961575</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5497211533298854</v>
+        <v>0.8013218901294007</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6973,13 +6973,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1727842647179731</v>
+        <v>0.1627126977691551</v>
       </c>
       <c r="C68">
-        <v>-1998.409765680945</v>
+        <v>-1894.791662466138</v>
       </c>
       <c r="D68">
-        <v>1210.182234319055</v>
+        <v>1313.800337533862</v>
       </c>
       <c r="E68">
         <v>1819.692</v>
@@ -7006,37 +7006,37 @@
         <v>435.9</v>
       </c>
       <c r="M68">
-        <v>805.1466660235061</v>
+        <v>750.189786023506</v>
       </c>
       <c r="N68">
-        <v>-369.2466660235061</v>
+        <v>-314.289786023506</v>
       </c>
       <c r="O68">
-        <v>-73.84933320470121</v>
+        <v>-62.8579572047012</v>
       </c>
       <c r="P68">
-        <v>-295.3973328188048</v>
+        <v>-251.4318288188048</v>
       </c>
       <c r="Q68">
-        <v>-76.29733281880488</v>
+        <v>-32.33182881880484</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1277907820030995</v>
+        <v>0.1272861733301055</v>
       </c>
       <c r="T68">
-        <v>1.684941469095972</v>
+        <v>1.675441489350424</v>
       </c>
       <c r="U68">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V68">
-        <v>0.1082784089892199</v>
+        <v>0.1162105931381854</v>
       </c>
       <c r="W68">
-        <v>0.1959627255104837</v>
+        <v>0.1809627255104837</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5413920449460994</v>
+        <v>0.5810529656909269</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7055,13 +7055,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.17452384216239</v>
+        <v>0.164302275213572</v>
       </c>
       <c r="C69">
-        <v>-2070.276200749778</v>
+        <v>-1967.926846318493</v>
       </c>
       <c r="D69">
-        <v>1193.827799250222</v>
+        <v>1296.177153681507</v>
       </c>
       <c r="E69">
         <v>1875.204</v>
@@ -7088,37 +7088,37 @@
         <v>435.9</v>
       </c>
       <c r="M69">
-        <v>817.3458579329532</v>
+        <v>761.5562979329532</v>
       </c>
       <c r="N69">
-        <v>-381.4458579329532</v>
+        <v>-325.6562979329531</v>
       </c>
       <c r="O69">
-        <v>-76.28917158659064</v>
+        <v>-65.13125958659063</v>
       </c>
       <c r="P69">
-        <v>-305.1566863463626</v>
+        <v>-260.5250383463625</v>
       </c>
       <c r="Q69">
-        <v>-86.0566863463626</v>
+        <v>-41.42503834636256</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1302753511547086</v>
+        <v>0.1297554513098057</v>
       </c>
       <c r="T69">
-        <v>1.736000301492819</v>
+        <v>1.726212443573164</v>
       </c>
       <c r="U69">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V69">
-        <v>0.1066623133326643</v>
+        <v>0.1144761066734363</v>
       </c>
       <c r="W69">
-        <v>0.1963178750467704</v>
+        <v>0.1813178750467704</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5333115666633217</v>
+        <v>0.5723805333671816</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7137,13 +7137,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1762634196068069</v>
+        <v>0.1658918526579889</v>
       </c>
       <c r="C70">
-        <v>-2141.706501207887</v>
+        <v>-2040.59549701426</v>
       </c>
       <c r="D70">
-        <v>1177.909498792113</v>
+        <v>1279.02050298574</v>
       </c>
       <c r="E70">
         <v>1930.716</v>
@@ -7170,37 +7170,37 @@
         <v>435.9</v>
       </c>
       <c r="M70">
-        <v>829.5450498424003</v>
+        <v>772.9228098424003</v>
       </c>
       <c r="N70">
-        <v>-393.6450498424003</v>
+        <v>-337.0228098424002</v>
       </c>
       <c r="O70">
-        <v>-78.72900996848006</v>
+        <v>-67.40456196848005</v>
       </c>
       <c r="P70">
-        <v>-314.9160398739202</v>
+        <v>-269.6182478739202</v>
       </c>
       <c r="Q70">
-        <v>-95.81603987392026</v>
+        <v>-50.51824787392025</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1329152058782933</v>
+        <v>0.1323790591632371</v>
       </c>
       <c r="T70">
-        <v>1.79025031091447</v>
+        <v>1.780156582434826</v>
       </c>
       <c r="U70">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V70">
-        <v>0.1050937499013016</v>
+        <v>0.112792634516474</v>
       </c>
       <c r="W70">
-        <v>0.1966625790084603</v>
+        <v>0.1816625790084603</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5254687495065081</v>
+        <v>0.5639631725823702</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7219,13 +7219,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1780029970512238</v>
+        <v>0.1674814301024058</v>
       </c>
       <c r="C71">
-        <v>-2212.717883531793</v>
+        <v>-2112.815898130041</v>
       </c>
       <c r="D71">
-        <v>1162.410116468207</v>
+        <v>1262.312101869959</v>
       </c>
       <c r="E71">
         <v>1986.228</v>
@@ -7252,37 +7252,37 @@
         <v>435.9</v>
       </c>
       <c r="M71">
-        <v>841.7442417518473</v>
+        <v>784.2893217518473</v>
       </c>
       <c r="N71">
-        <v>-405.8442417518473</v>
+        <v>-348.3893217518473</v>
       </c>
       <c r="O71">
-        <v>-81.16884835036946</v>
+        <v>-69.67786435036946</v>
       </c>
       <c r="P71">
-        <v>-324.6753934014778</v>
+        <v>-278.7114574014778</v>
       </c>
       <c r="Q71">
-        <v>-105.5753934014779</v>
+        <v>-59.61145740147782</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1357253738098511</v>
+        <v>0.1351719320394706</v>
       </c>
       <c r="T71">
-        <v>1.848000320943969</v>
+        <v>1.83758098831982</v>
       </c>
       <c r="U71">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V71">
-        <v>0.1035706520766451</v>
+        <v>0.1111579586539164</v>
       </c>
       <c r="W71">
-        <v>0.1969972915509709</v>
+        <v>0.1819972915509709</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5178532603832254</v>
+        <v>0.5557897932695821</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7301,13 +7301,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1797425744956407</v>
+        <v>0.1690710075468227</v>
       </c>
       <c r="C72">
-        <v>-2283.326669802957</v>
+        <v>-2184.605390176862</v>
       </c>
       <c r="D72">
-        <v>1147.313330197043</v>
+        <v>1246.034609823138</v>
       </c>
       <c r="E72">
         <v>2041.74</v>
@@ -7334,37 +7334,37 @@
         <v>435.9</v>
       </c>
       <c r="M72">
-        <v>853.9434336612944</v>
+        <v>795.6558336612943</v>
       </c>
       <c r="N72">
-        <v>-418.0434336612944</v>
+        <v>-359.7558336612943</v>
       </c>
       <c r="O72">
-        <v>-83.60868673225889</v>
+        <v>-71.95116673225886</v>
       </c>
       <c r="P72">
-        <v>-334.4347469290355</v>
+        <v>-287.8046669290354</v>
       </c>
       <c r="Q72">
-        <v>-115.3347469290355</v>
+        <v>-68.70466692903545</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1387228862701795</v>
+        <v>0.1381509964407862</v>
       </c>
       <c r="T72">
-        <v>1.909600331642101</v>
+        <v>1.89883368793048</v>
       </c>
       <c r="U72">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V72">
-        <v>0.102091071332693</v>
+        <v>0.1095699878160034</v>
       </c>
       <c r="W72">
-        <v>0.1973224408779812</v>
+        <v>0.1823224408779812</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5104553566634651</v>
+        <v>0.5478499390800168</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7383,13 +7383,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1814821519400576</v>
+        <v>0.1706605849912396</v>
       </c>
       <c r="C73">
-        <v>-2353.548345042861</v>
+        <v>-2255.980430630152</v>
       </c>
       <c r="D73">
-        <v>1132.603654957138</v>
+        <v>1230.171569369848</v>
       </c>
       <c r="E73">
         <v>2097.252</v>
@@ -7416,37 +7416,37 @@
         <v>435.9</v>
       </c>
       <c r="M73">
-        <v>866.1426255707414</v>
+        <v>807.0223455707413</v>
       </c>
       <c r="N73">
-        <v>-430.2426255707414</v>
+        <v>-371.1223455707413</v>
       </c>
       <c r="O73">
-        <v>-86.04852511414828</v>
+        <v>-74.22446911414826</v>
       </c>
       <c r="P73">
-        <v>-344.1941004565931</v>
+        <v>-296.8978764565931</v>
       </c>
       <c r="Q73">
-        <v>-125.0941004565931</v>
+        <v>-77.79787645659309</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1419271237277719</v>
+        <v>0.141335513559434</v>
       </c>
       <c r="T73">
-        <v>1.975448618940105</v>
+        <v>1.964310711652221</v>
       </c>
       <c r="U73">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V73">
-        <v>0.1006531689195565</v>
+        <v>0.1080267485509892</v>
       </c>
       <c r="W73">
-        <v>0.1976384310690193</v>
+        <v>0.1826384310690193</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5032658445977825</v>
+        <v>0.5401337427549462</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7465,13 +7465,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2050794405142009</v>
+        <v>0.1722501624356564</v>
       </c>
       <c r="C74">
-        <v>-2576.855857130752</v>
+        <v>-2326.956649431992</v>
       </c>
       <c r="D74">
-        <v>964.8081428692477</v>
+        <v>1214.707350568008</v>
       </c>
       <c r="E74">
         <v>2152.764</v>
@@ -7498,45 +7498,45 @@
         <v>435.9</v>
       </c>
       <c r="M74">
-        <v>998.2477374801884</v>
+        <v>818.3888574801883</v>
       </c>
       <c r="N74">
-        <v>-562.3477374801885</v>
+        <v>-382.4888574801883</v>
       </c>
       <c r="O74">
-        <v>-112.4695474960377</v>
+        <v>-76.49777149603766</v>
       </c>
       <c r="P74">
-        <v>-449.8781899841508</v>
+        <v>-305.9910859841506</v>
       </c>
       <c r="Q74">
-        <v>-230.7781899841508</v>
+        <v>-86.89108598415066</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.146280632181358</v>
+        <v>0.1447474961865567</v>
       </c>
       <c r="T74">
-        <v>2.064914858318452</v>
+        <v>2.0344646656398</v>
       </c>
       <c r="U74">
-        <v>0.2497577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V74">
-        <v>0.08733303039590432</v>
+        <v>0.1065263770433366</v>
       </c>
       <c r="W74">
-        <v>0.2279456437547508</v>
+        <v>0.1829456437547508</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.4366651519795215</v>
+        <v>0.532631885216683</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7547,13 +7547,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2071190179586178</v>
+        <v>0.1738397398800734</v>
       </c>
       <c r="C75">
-        <v>-2644.566052676988</v>
+        <v>-2397.548900359079</v>
       </c>
       <c r="D75">
-        <v>952.6099473230123</v>
+        <v>1199.627099640921</v>
       </c>
       <c r="E75">
         <v>2208.276</v>
@@ -7580,45 +7580,45 @@
         <v>435.9</v>
       </c>
       <c r="M75">
-        <v>1012.112289389636</v>
+        <v>829.7553693896355</v>
       </c>
       <c r="N75">
-        <v>-576.2122893896355</v>
+        <v>-393.8553693896354</v>
       </c>
       <c r="O75">
-        <v>-115.2424578779271</v>
+        <v>-78.77107387792709</v>
       </c>
       <c r="P75">
-        <v>-460.9698315117084</v>
+        <v>-315.0842955117083</v>
       </c>
       <c r="Q75">
-        <v>-241.8698315117085</v>
+        <v>-95.98429551170835</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1500021370769639</v>
+        <v>0.1484122182675403</v>
       </c>
       <c r="T75">
-        <v>2.14139318640432</v>
+        <v>2.109815208811644</v>
       </c>
       <c r="U75">
-        <v>0.2497577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V75">
-        <v>0.08613668751376864</v>
+        <v>0.1050671116043868</v>
       </c>
       <c r="W75">
-        <v>0.2282444396545719</v>
+        <v>0.1832444396545719</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.4306834375688431</v>
+        <v>0.5253355580219339</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7629,13 +7629,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2091585954030347</v>
+        <v>0.1754293173244902</v>
       </c>
       <c r="C76">
-        <v>-2711.971652503147</v>
+        <v>-2467.771308611304</v>
       </c>
       <c r="D76">
-        <v>940.7163474968531</v>
+        <v>1184.916691388697</v>
       </c>
       <c r="E76">
         <v>2263.788</v>
@@ -7662,45 +7662,45 @@
         <v>435.9</v>
       </c>
       <c r="M76">
-        <v>1025.976841299083</v>
+        <v>841.1218812990826</v>
       </c>
       <c r="N76">
-        <v>-590.0768412990826</v>
+        <v>-405.2218812990826</v>
       </c>
       <c r="O76">
-        <v>-118.0153682598165</v>
+        <v>-81.04437625981652</v>
       </c>
       <c r="P76">
-        <v>-472.0614730392661</v>
+        <v>-324.1775050392661</v>
       </c>
       <c r="Q76">
-        <v>-252.9614730392661</v>
+        <v>-105.0775050392661</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.154009911579924</v>
+        <v>0.152358842047061</v>
       </c>
       <c r="T76">
-        <v>2.223754462804487</v>
+        <v>2.190961947612093</v>
       </c>
       <c r="U76">
-        <v>0.2497577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V76">
-        <v>0.08497267822304203</v>
+        <v>0.1036472857718951</v>
       </c>
       <c r="W76">
-        <v>0.228535159989533</v>
+        <v>0.183535159989533</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.4248633911152102</v>
+        <v>0.5182364288594753</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7711,13 +7711,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2111981728474515</v>
+        <v>0.1770188947689071</v>
       </c>
       <c r="C77">
-        <v>-2779.083924809168</v>
+        <v>-2537.637314941426</v>
       </c>
       <c r="D77">
-        <v>929.1160751908317</v>
+        <v>1170.562685058574</v>
       </c>
       <c r="E77">
         <v>2319.3</v>
@@ -7744,45 +7744,45 @@
         <v>435.9</v>
       </c>
       <c r="M77">
-        <v>1039.84139320853</v>
+        <v>852.4883932085296</v>
       </c>
       <c r="N77">
-        <v>-603.9413932085295</v>
+        <v>-416.5883932085296</v>
       </c>
       <c r="O77">
-        <v>-120.7882786417059</v>
+        <v>-83.31767864170592</v>
       </c>
       <c r="P77">
-        <v>-483.1531145668235</v>
+        <v>-333.2707145668236</v>
       </c>
       <c r="Q77">
-        <v>-264.0531145668236</v>
+        <v>-114.1707145668237</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.158338308043121</v>
+        <v>0.1566211957289435</v>
       </c>
       <c r="T77">
-        <v>2.312704641316667</v>
+        <v>2.278600425516576</v>
       </c>
       <c r="U77">
-        <v>0.2497577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V77">
-        <v>0.08383970918006815</v>
+        <v>0.1022653219616032</v>
       </c>
       <c r="W77">
-        <v>0.2288181277822284</v>
+        <v>0.1838181277822284</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4191985459003408</v>
+        <v>0.5113266098080156</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7793,13 +7793,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2132377502918684</v>
+        <v>0.178608472213324</v>
       </c>
       <c r="C78">
-        <v>-2845.913588758314</v>
+        <v>-2607.159716615624</v>
       </c>
       <c r="D78">
-        <v>917.7984112416859</v>
+        <v>1156.552283384376</v>
       </c>
       <c r="E78">
         <v>2374.812</v>
@@ -7826,45 +7826,45 @@
         <v>435.9</v>
       </c>
       <c r="M78">
-        <v>1053.705945117977</v>
+        <v>863.8549051179767</v>
       </c>
       <c r="N78">
-        <v>-617.8059451179768</v>
+        <v>-427.9549051179767</v>
       </c>
       <c r="O78">
-        <v>-123.5611890235954</v>
+        <v>-85.59098102359535</v>
       </c>
       <c r="P78">
-        <v>-494.2447560943814</v>
+        <v>-342.3639240943813</v>
       </c>
       <c r="Q78">
-        <v>-275.1447560943814</v>
+        <v>-123.2639240943814</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1630274042115844</v>
+        <v>0.1612387455509828</v>
       </c>
       <c r="T78">
-        <v>2.409067334704861</v>
+        <v>2.3735421099131</v>
       </c>
       <c r="U78">
-        <v>0.2497577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V78">
-        <v>0.08273655511190935</v>
+        <v>0.1009197256200031</v>
       </c>
       <c r="W78">
-        <v>0.2290936490540634</v>
+        <v>0.1840936490540634</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.4136827755595467</v>
+        <v>0.5045986281000154</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7875,13 +7875,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2152773277362854</v>
+        <v>0.207484022817586</v>
       </c>
       <c r="C79">
-        <v>-2912.470847514122</v>
+        <v>-2869.223257104062</v>
       </c>
       <c r="D79">
-        <v>906.7531524858773</v>
+        <v>950.0007428959376</v>
       </c>
       <c r="E79">
         <v>2430.324</v>
@@ -7908,37 +7908,37 @@
         <v>435.9</v>
       </c>
       <c r="M79">
-        <v>1067.570497027424</v>
+        <v>1024.826257027424</v>
       </c>
       <c r="N79">
-        <v>-631.6704970274238</v>
+        <v>-588.9262570274236</v>
       </c>
       <c r="O79">
-        <v>-126.3340994054848</v>
+        <v>-117.7852514054847</v>
       </c>
       <c r="P79">
-        <v>-505.3363976219391</v>
+        <v>-471.1410056219389</v>
       </c>
       <c r="Q79">
-        <v>-286.2363976219391</v>
+        <v>-252.041005621939</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1681242478729576</v>
+        <v>0.1677185743133953</v>
       </c>
       <c r="T79">
-        <v>2.513809392735507</v>
+        <v>2.506774209406243</v>
       </c>
       <c r="U79">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V79">
-        <v>0.08166205439617026</v>
+        <v>0.08506807802999833</v>
       </c>
       <c r="W79">
-        <v>0.2293620139292274</v>
+        <v>0.2193620139292274</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4083102719808513</v>
+        <v>0.4253403901499917</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7957,13 +7957,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2173169051807022</v>
+        <v>0.2094236002620029</v>
       </c>
       <c r="C80">
-        <v>-2978.765418920221</v>
+        <v>-2935.99646887394</v>
       </c>
       <c r="D80">
-        <v>895.9705810797782</v>
+        <v>938.7395311260598</v>
       </c>
       <c r="E80">
         <v>2485.836</v>
@@ -7990,37 +7990,37 @@
         <v>435.9</v>
       </c>
       <c r="M80">
-        <v>1081.435048936871</v>
+        <v>1038.135688936871</v>
       </c>
       <c r="N80">
-        <v>-645.5350489368707</v>
+        <v>-602.2356889368707</v>
       </c>
       <c r="O80">
-        <v>-129.1070097873742</v>
+        <v>-120.4471377873741</v>
       </c>
       <c r="P80">
-        <v>-516.4280391494965</v>
+        <v>-481.7885511494966</v>
       </c>
       <c r="Q80">
-        <v>-297.3280391494965</v>
+        <v>-262.6885511494966</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.173684440958092</v>
+        <v>0.1732603276912769</v>
       </c>
       <c r="T80">
-        <v>2.628073456041666</v>
+        <v>2.620718491651981</v>
       </c>
       <c r="U80">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V80">
-        <v>0.08061510498083475</v>
+        <v>0.08397746164499836</v>
       </c>
       <c r="W80">
-        <v>0.2296234976537461</v>
+        <v>0.2196234976537461</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4030755249041739</v>
+        <v>0.4198873082249918</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8039,13 +8039,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2193564826251191</v>
+        <v>0.2113631777064198</v>
       </c>
       <c r="C81">
-        <v>-3044.806564016914</v>
+        <v>-3002.505829796689</v>
       </c>
       <c r="D81">
-        <v>885.4414359830862</v>
+        <v>927.7421702033113</v>
       </c>
       <c r="E81">
         <v>2541.348</v>
@@ -8072,37 +8072,37 @@
         <v>435.9</v>
       </c>
       <c r="M81">
-        <v>1095.299600846318</v>
+        <v>1051.445120846318</v>
       </c>
       <c r="N81">
-        <v>-659.399600846318</v>
+        <v>-615.5451208463178</v>
       </c>
       <c r="O81">
-        <v>-131.8799201692636</v>
+        <v>-123.1090241692636</v>
       </c>
       <c r="P81">
-        <v>-527.5196806770543</v>
+        <v>-492.4360966770543</v>
       </c>
       <c r="Q81">
-        <v>-308.4196806770544</v>
+        <v>-273.3360966770543</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1797741762418108</v>
+        <v>0.1793298671051472</v>
       </c>
       <c r="T81">
-        <v>2.75321981109127</v>
+        <v>2.745514610302075</v>
       </c>
       <c r="U81">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V81">
-        <v>0.07959466061398873</v>
+        <v>0.08291445580139079</v>
       </c>
       <c r="W81">
-        <v>0.2298783615371378</v>
+        <v>0.2198783615371378</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3979733030699437</v>
+        <v>0.4145722790069539</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8121,13 +8121,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.221396060069536</v>
+        <v>0.2133027551508367</v>
       </c>
       <c r="C82">
-        <v>-3110.603113570407</v>
+        <v>-3068.760505557098</v>
       </c>
       <c r="D82">
-        <v>875.1568864295934</v>
+        <v>916.9994944429021</v>
       </c>
       <c r="E82">
         <v>2596.86</v>
@@ -8154,37 +8154,37 @@
         <v>435.9</v>
       </c>
       <c r="M82">
-        <v>1109.164152755765</v>
+        <v>1064.754552755765</v>
       </c>
       <c r="N82">
-        <v>-673.2641527557648</v>
+        <v>-628.8545527557649</v>
       </c>
       <c r="O82">
-        <v>-134.652830551153</v>
+        <v>-125.770910551153</v>
       </c>
       <c r="P82">
-        <v>-538.6113222046118</v>
+        <v>-503.0836422046119</v>
       </c>
       <c r="Q82">
-        <v>-319.5113222046119</v>
+        <v>-283.983642204612</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1864728850539013</v>
+        <v>0.1860063604604046</v>
       </c>
       <c r="T82">
-        <v>2.890880801645833</v>
+        <v>2.882790340817179</v>
       </c>
       <c r="U82">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V82">
-        <v>0.07859972735631389</v>
+        <v>0.08187802510387339</v>
       </c>
       <c r="W82">
-        <v>0.2301268538234447</v>
+        <v>0.2201268538234447</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3929986367815694</v>
+        <v>0.409390125519367</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8203,13 +8203,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2234356375139529</v>
+        <v>0.2152423325952535</v>
       </c>
       <c r="C83">
-        <v>-3176.163492774426</v>
+        <v>-3134.769242167846</v>
       </c>
       <c r="D83">
-        <v>865.108507225574</v>
+        <v>906.502757832154</v>
       </c>
       <c r="E83">
         <v>2652.372</v>
@@ -8236,37 +8236,37 @@
         <v>435.9</v>
       </c>
       <c r="M83">
-        <v>1123.028704665212</v>
+        <v>1078.063984665212</v>
       </c>
       <c r="N83">
-        <v>-687.1287046652119</v>
+        <v>-642.163984665212</v>
       </c>
       <c r="O83">
-        <v>-137.4257409330424</v>
+        <v>-128.4327969330424</v>
       </c>
       <c r="P83">
-        <v>-549.7029637321696</v>
+        <v>-513.7311877321696</v>
       </c>
       <c r="Q83">
-        <v>-330.6029637321696</v>
+        <v>-294.6311877321696</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1938767211093698</v>
+        <v>0.1933856425898996</v>
       </c>
       <c r="T83">
-        <v>3.043032422785088</v>
+        <v>3.03451614822861</v>
       </c>
       <c r="U83">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V83">
-        <v>0.07762936035191495</v>
+        <v>0.0808671852877762</v>
       </c>
       <c r="W83">
-        <v>0.230369210497744</v>
+        <v>0.220369210497744</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3881468017595748</v>
+        <v>0.4043359264388809</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8285,13 +8285,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2254752149583698</v>
+        <v>0.2171819100396705</v>
       </c>
       <c r="C84">
-        <v>-3241.495744269432</v>
+        <v>-3200.540389717235</v>
       </c>
       <c r="D84">
-        <v>855.2882557305683</v>
+        <v>896.2436102827653</v>
       </c>
       <c r="E84">
         <v>2707.884</v>
@@ -8318,37 +8318,37 @@
         <v>435.9</v>
       </c>
       <c r="M84">
-        <v>1136.893256574659</v>
+        <v>1091.373416574659</v>
       </c>
       <c r="N84">
-        <v>-700.9932565746592</v>
+        <v>-655.473416574659</v>
       </c>
       <c r="O84">
-        <v>-140.1986513149319</v>
+        <v>-131.0946833149318</v>
       </c>
       <c r="P84">
-        <v>-560.7946052597274</v>
+        <v>-524.3787332597273</v>
       </c>
       <c r="Q84">
-        <v>-341.6946052597274</v>
+        <v>-305.2787332597273</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2021032056154459</v>
+        <v>0.2015848449560051</v>
       </c>
       <c r="T84">
-        <v>3.212089779606482</v>
+        <v>3.203100378685755</v>
       </c>
       <c r="U84">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V84">
-        <v>0.07668266083542817</v>
+        <v>0.0798810001013399</v>
       </c>
       <c r="W84">
-        <v>0.2306056560336458</v>
+        <v>0.2206056560336458</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3834133041771408</v>
+        <v>0.3994050005066995</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8367,13 +8367,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2275147924027867</v>
+        <v>0.2191214874840874</v>
       </c>
       <c r="C85">
-        <v>-3306.60754961162</v>
+        <v>-3266.081924522415</v>
       </c>
       <c r="D85">
-        <v>845.6884503883805</v>
+        <v>886.2140754775857</v>
       </c>
       <c r="E85">
         <v>2763.396</v>
@@ -8400,37 +8400,37 @@
         <v>435.9</v>
       </c>
       <c r="M85">
-        <v>1150.757808484106</v>
+        <v>1104.682848484106</v>
       </c>
       <c r="N85">
-        <v>-714.857808484106</v>
+        <v>-668.7828484841061</v>
       </c>
       <c r="O85">
-        <v>-142.9715616968212</v>
+        <v>-133.7565696968212</v>
       </c>
       <c r="P85">
-        <v>-571.8862467872848</v>
+        <v>-535.0262787872849</v>
       </c>
       <c r="Q85">
-        <v>-352.7862467872848</v>
+        <v>-315.926278787285</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2112975118281192</v>
+        <v>0.2107486593651819</v>
       </c>
       <c r="T85">
-        <v>3.401036237230393</v>
+        <v>3.391518048020212</v>
       </c>
       <c r="U85">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V85">
-        <v>0.07575877335548326</v>
+        <v>0.07891857841337194</v>
       </c>
       <c r="W85">
-        <v>0.2308364040867548</v>
+        <v>0.2208364040867548</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3787938667774163</v>
+        <v>0.3945928920668598</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8449,13 +8449,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2295543698472036</v>
+        <v>0.2210610649285042</v>
       </c>
       <c r="C86">
-        <v>-3371.50624931215</v>
+        <v>-3331.401469811622</v>
       </c>
       <c r="D86">
-        <v>836.3017506878498</v>
+        <v>876.4065301883778</v>
       </c>
       <c r="E86">
         <v>2818.908</v>
@@ -8482,37 +8482,37 @@
         <v>435.9</v>
       </c>
       <c r="M86">
-        <v>1164.622360393553</v>
+        <v>1117.992280393553</v>
       </c>
       <c r="N86">
-        <v>-728.7223603935531</v>
+        <v>-682.092280393553</v>
       </c>
       <c r="O86">
-        <v>-145.7444720787106</v>
+        <v>-136.4184560787106</v>
       </c>
       <c r="P86">
-        <v>-582.9778883148425</v>
+        <v>-545.6738243148424</v>
       </c>
       <c r="Q86">
-        <v>-363.8778883148426</v>
+        <v>-326.5738243148424</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2216411063173765</v>
+        <v>0.2210579505755056</v>
       </c>
       <c r="T86">
-        <v>3.613601002057291</v>
+        <v>3.603487926021473</v>
       </c>
       <c r="U86">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V86">
-        <v>0.07485688319648941</v>
+        <v>0.07797907152749849</v>
       </c>
       <c r="W86">
-        <v>0.2310616581385992</v>
+        <v>0.2210616581385992</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3742844159824471</v>
+        <v>0.3898953576374924</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8531,13 +8531,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2315939472916205</v>
+        <v>0.2230006423729211</v>
       </c>
       <c r="C87">
-        <v>-3436.198861556488</v>
+        <v>-3396.506315048129</v>
       </c>
       <c r="D87">
-        <v>827.1211384435118</v>
+        <v>866.8136849518709</v>
       </c>
       <c r="E87">
         <v>2874.42</v>
@@ -8564,37 +8564,37 @@
         <v>435.9</v>
       </c>
       <c r="M87">
-        <v>1178.486912303</v>
+        <v>1131.301712303</v>
       </c>
       <c r="N87">
-        <v>-742.5869123030002</v>
+        <v>-695.4017123030001</v>
       </c>
       <c r="O87">
-        <v>-148.5173824606</v>
+        <v>-139.0803424606</v>
       </c>
       <c r="P87">
-        <v>-594.0695298424001</v>
+        <v>-556.3213698424</v>
       </c>
       <c r="Q87">
-        <v>-374.9695298424002</v>
+        <v>-337.2213698424001</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.233363846738535</v>
+        <v>0.232741813947206</v>
       </c>
       <c r="T87">
-        <v>3.854507735527777</v>
+        <v>3.843720454422904</v>
       </c>
       <c r="U87">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V87">
-        <v>0.07397621398241307</v>
+        <v>0.07706167068599851</v>
       </c>
       <c r="W87">
-        <v>0.2312816120951062</v>
+        <v>0.2212816120951061</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3698810699120654</v>
+        <v>0.3853083534299925</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8613,13 +8613,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2336335247360374</v>
+        <v>0.224940219817338</v>
       </c>
       <c r="C88">
-        <v>-3500.692099704154</v>
+        <v>-3461.403433998853</v>
       </c>
       <c r="D88">
-        <v>818.1399002958461</v>
+        <v>857.4285660011468</v>
       </c>
       <c r="E88">
         <v>2929.932</v>
@@ -8646,37 +8646,37 @@
         <v>435.9</v>
       </c>
       <c r="M88">
-        <v>1192.351464212447</v>
+        <v>1144.611144212447</v>
       </c>
       <c r="N88">
-        <v>-756.4514642124473</v>
+        <v>-708.7111442124474</v>
       </c>
       <c r="O88">
-        <v>-151.2902928424895</v>
+        <v>-141.7422288424895</v>
       </c>
       <c r="P88">
-        <v>-605.1611713699579</v>
+        <v>-566.9689153699579</v>
       </c>
       <c r="Q88">
-        <v>-386.0611713699579</v>
+        <v>-347.868915369958</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2467612643627161</v>
+        <v>0.2460948006577208</v>
       </c>
       <c r="T88">
-        <v>4.129829716636904</v>
+        <v>4.118271915453112</v>
       </c>
       <c r="U88">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V88">
-        <v>0.07311602544773385</v>
+        <v>0.0761656047477892</v>
       </c>
       <c r="W88">
-        <v>0.2314964508433222</v>
+        <v>0.2214964508433222</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3655801272386693</v>
+        <v>0.380828023738946</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8695,13 +8695,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2356731021804543</v>
+        <v>0.2268797972617549</v>
       </c>
       <c r="C89">
-        <v>-3564.992388660611</v>
+        <v>-3526.099501641752</v>
       </c>
       <c r="D89">
-        <v>809.3516113393886</v>
+        <v>848.2444983582475</v>
       </c>
       <c r="E89">
         <v>2985.444</v>
@@ -8728,37 +8728,37 @@
         <v>435.9</v>
       </c>
       <c r="M89">
-        <v>1206.216016121894</v>
+        <v>1157.920576121894</v>
       </c>
       <c r="N89">
-        <v>-770.3160161218943</v>
+        <v>-722.0205761218942</v>
       </c>
       <c r="O89">
-        <v>-154.0632032243789</v>
+        <v>-144.4041152243788</v>
       </c>
       <c r="P89">
-        <v>-616.2528128975155</v>
+        <v>-577.6164608975154</v>
       </c>
       <c r="Q89">
-        <v>-397.1528128975155</v>
+        <v>-358.5164608975154</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.262219823159848</v>
+        <v>0.261502093016007</v>
       </c>
       <c r="T89">
-        <v>4.447508925608973</v>
+        <v>4.43506206279566</v>
       </c>
       <c r="U89">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V89">
-        <v>0.07227561136212771</v>
+        <v>0.07529013802655025</v>
       </c>
       <c r="W89">
-        <v>0.2317063507697402</v>
+        <v>0.2217063507697402</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3613780568106386</v>
+        <v>0.3764506901327513</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8777,13 +8777,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2377126796248711</v>
+        <v>0.2288193747061718</v>
       </c>
       <c r="C90">
-        <v>-3629.105880205188</v>
+        <v>-3590.60090999815</v>
       </c>
       <c r="D90">
-        <v>800.7501197948121</v>
+        <v>839.2550900018493</v>
       </c>
       <c r="E90">
         <v>3040.956</v>
@@ -8810,37 +8810,37 @@
         <v>435.9</v>
       </c>
       <c r="M90">
-        <v>1220.080568031341</v>
+        <v>1171.230008031341</v>
       </c>
       <c r="N90">
-        <v>-784.1805680313414</v>
+        <v>-735.3300080313413</v>
       </c>
       <c r="O90">
-        <v>-156.8361136062683</v>
+        <v>-147.0660016062683</v>
       </c>
       <c r="P90">
-        <v>-627.3444544250731</v>
+        <v>-588.264006425073</v>
       </c>
       <c r="Q90">
-        <v>-408.2444544250731</v>
+        <v>-369.1640064250731</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2802548084231687</v>
+        <v>0.2794772674340076</v>
       </c>
       <c r="T90">
-        <v>4.818134669409722</v>
+        <v>4.804650568028632</v>
       </c>
       <c r="U90">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V90">
-        <v>0.07145429759664898</v>
+        <v>0.07443456827624854</v>
       </c>
       <c r="W90">
-        <v>0.2319114802432851</v>
+        <v>0.2219114802432851</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3572714879832449</v>
+        <v>0.3721728413812427</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8859,13 +8859,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2397522570692881</v>
+        <v>0.2307589521505887</v>
       </c>
       <c r="C91">
-        <v>-3693.03846735187</v>
+        <v>-3654.913782968897</v>
       </c>
       <c r="D91">
-        <v>792.3295326481301</v>
+        <v>830.454217031103</v>
       </c>
       <c r="E91">
         <v>3096.468</v>
@@ -8892,37 +8892,37 @@
         <v>435.9</v>
       </c>
       <c r="M91">
-        <v>1233.945119940789</v>
+        <v>1184.539439940788</v>
       </c>
       <c r="N91">
-        <v>-798.0451199407885</v>
+        <v>-748.6394399407884</v>
       </c>
       <c r="O91">
-        <v>-159.6090239881577</v>
+        <v>-149.7278879881577</v>
       </c>
       <c r="P91">
-        <v>-638.4360959526308</v>
+        <v>-598.9115519526307</v>
       </c>
       <c r="Q91">
-        <v>-419.3360959526308</v>
+        <v>-379.8115519526307</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3015688819161841</v>
+        <v>0.3007206553825538</v>
       </c>
       <c r="T91">
-        <v>5.256146912083333</v>
+        <v>5.241436983303962</v>
       </c>
       <c r="U91">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V91">
-        <v>0.07065144032028213</v>
+        <v>0.07359822481247046</v>
       </c>
       <c r="W91">
-        <v>0.2321120000657391</v>
+        <v>0.2221120000657391</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3532572016014107</v>
+        <v>0.3679911240623523</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8941,13 +8941,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.241791834513705</v>
+        <v>0.2326985295950056</v>
       </c>
       <c r="C92">
-        <v>-3756.795797813438</v>
+        <v>-3719.043990246743</v>
       </c>
       <c r="D92">
-        <v>784.0842021865619</v>
+        <v>821.8360097532568</v>
       </c>
       <c r="E92">
         <v>3151.98</v>
@@ -8974,37 +8974,37 @@
         <v>435.9</v>
       </c>
       <c r="M92">
-        <v>1247.809671850236</v>
+        <v>1197.848871850236</v>
       </c>
       <c r="N92">
-        <v>-811.9096718502356</v>
+        <v>-761.9488718502355</v>
       </c>
       <c r="O92">
-        <v>-162.3819343700471</v>
+        <v>-152.3897743700471</v>
       </c>
       <c r="P92">
-        <v>-649.5277374801884</v>
+        <v>-609.5590974801884</v>
       </c>
       <c r="Q92">
-        <v>-430.4277374801885</v>
+        <v>-390.4590974801884</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3271457701078025</v>
+        <v>0.3262127209208092</v>
       </c>
       <c r="T92">
-        <v>5.781761603291667</v>
+        <v>5.765580681634359</v>
       </c>
       <c r="U92">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V92">
-        <v>0.06986642431672345</v>
+        <v>0.07278046675899856</v>
       </c>
       <c r="W92">
-        <v>0.2323080638921386</v>
+        <v>0.2223080638921386</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3493321215836173</v>
+        <v>0.3639023337949929</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9023,13 +9023,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2438314119581219</v>
+        <v>0.2346381070394225</v>
       </c>
       <c r="C93">
-        <v>-3820.383286633573</v>
+        <v>-3782.997160371342</v>
       </c>
       <c r="D93">
-        <v>776.0087133664268</v>
+        <v>813.3948396286579</v>
       </c>
       <c r="E93">
         <v>3207.492</v>
@@ -9056,37 +9056,37 @@
         <v>435.9</v>
       </c>
       <c r="M93">
-        <v>1261.674223759683</v>
+        <v>1211.158303759683</v>
       </c>
       <c r="N93">
-        <v>-825.7742237596826</v>
+        <v>-775.2583037596826</v>
       </c>
       <c r="O93">
-        <v>-165.1548447519365</v>
+        <v>-155.0516607519365</v>
       </c>
       <c r="P93">
-        <v>-660.6193790077461</v>
+        <v>-620.206643007746</v>
       </c>
       <c r="Q93">
-        <v>-441.5193790077462</v>
+        <v>-401.1066430077461</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3584064112308917</v>
+        <v>0.3573696899120102</v>
       </c>
       <c r="T93">
-        <v>6.424179559212964</v>
+        <v>6.406200757371511</v>
       </c>
       <c r="U93">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V93">
-        <v>0.06909866141214407</v>
+        <v>0.07198068140999858</v>
       </c>
       <c r="W93">
-        <v>0.2324998186234523</v>
+        <v>0.2224998186234523</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3454933070607203</v>
+        <v>0.3599034070499929</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9105,13 +9105,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2458709894025388</v>
+        <v>0.2365776844838394</v>
       </c>
       <c r="C94">
-        <v>-3883.806128046312</v>
+        <v>-3846.778692987891</v>
       </c>
       <c r="D94">
-        <v>768.0978719536884</v>
+        <v>805.1253070121089</v>
       </c>
       <c r="E94">
         <v>3263.004</v>
@@ -9138,37 +9138,37 @@
         <v>435.9</v>
       </c>
       <c r="M94">
-        <v>1275.53877566913</v>
+        <v>1224.46773566913</v>
       </c>
       <c r="N94">
-        <v>-839.6387756691297</v>
+        <v>-788.5677356691297</v>
       </c>
       <c r="O94">
-        <v>-167.9277551338259</v>
+        <v>-157.713547133826</v>
       </c>
       <c r="P94">
-        <v>-671.7110205353038</v>
+        <v>-630.8541885353037</v>
       </c>
       <c r="Q94">
-        <v>-452.6110205353038</v>
+        <v>-411.7541885353037</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3974822126347534</v>
+        <v>0.3963159011510116</v>
       </c>
       <c r="T94">
-        <v>7.227202004114587</v>
+        <v>7.206975852042952</v>
       </c>
       <c r="U94">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V94">
-        <v>0.06834758900549033</v>
+        <v>0.07119828269902033</v>
       </c>
       <c r="W94">
-        <v>0.2326874047736505</v>
+        <v>0.2226874047736505</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3417379450274517</v>
+        <v>0.3559914134951018</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9187,13 +9187,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2479105668469556</v>
+        <v>0.2385172619282563</v>
       </c>
       <c r="C95">
-        <v>-3947.069306617433</v>
+        <v>-3910.393770365523</v>
       </c>
       <c r="D95">
-        <v>760.3466933825672</v>
+        <v>797.0222296344772</v>
       </c>
       <c r="E95">
         <v>3318.516</v>
@@ -9220,37 +9220,37 @@
         <v>435.9</v>
       </c>
       <c r="M95">
-        <v>1289.403327578577</v>
+        <v>1237.777167578577</v>
       </c>
       <c r="N95">
-        <v>-853.5033275785768</v>
+        <v>-801.8771675785767</v>
       </c>
       <c r="O95">
-        <v>-170.7006655157154</v>
+        <v>-160.3754335157154</v>
       </c>
       <c r="P95">
-        <v>-682.8026620628614</v>
+        <v>-641.5017340628614</v>
       </c>
       <c r="Q95">
-        <v>-463.7026620628614</v>
+        <v>-422.4017340628614</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4477225287254324</v>
+        <v>0.4463896013154418</v>
       </c>
       <c r="T95">
-        <v>8.259659433273814</v>
+        <v>8.23654383090623</v>
       </c>
       <c r="U95">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V95">
-        <v>0.06761266869360333</v>
+        <v>0.07043270976677281</v>
       </c>
       <c r="W95">
-        <v>0.2328709568130918</v>
+        <v>0.2228709568130918</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3380633434680167</v>
+        <v>0.352163548833864</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9269,13 +9269,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2499501442913725</v>
+        <v>0.2404568393726732</v>
       </c>
       <c r="C96">
-        <v>-4010.177607717993</v>
+        <v>-3973.847368227071</v>
       </c>
       <c r="D96">
-        <v>752.7503922820069</v>
+        <v>789.0806317729281</v>
       </c>
       <c r="E96">
         <v>3374.028</v>
@@ -9302,37 +9302,37 @@
         <v>435.9</v>
       </c>
       <c r="M96">
-        <v>1303.267879488024</v>
+        <v>1251.086599488024</v>
       </c>
       <c r="N96">
-        <v>-867.3678794880236</v>
+        <v>-815.1865994880236</v>
       </c>
       <c r="O96">
-        <v>-173.4735758976047</v>
+        <v>-163.0373198976047</v>
       </c>
       <c r="P96">
-        <v>-693.8943035904189</v>
+        <v>-652.1492795904189</v>
       </c>
       <c r="Q96">
-        <v>-474.7943035904189</v>
+        <v>-433.049279590419</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5147096168463379</v>
+        <v>0.5131545348680155</v>
       </c>
       <c r="T96">
-        <v>9.636269338819451</v>
+        <v>9.609301136057271</v>
       </c>
       <c r="U96">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V96">
-        <v>0.06689338498409693</v>
+        <v>0.06968342562031779</v>
       </c>
       <c r="W96">
-        <v>0.2330506034899918</v>
+        <v>0.2230506034899918</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3344669249204847</v>
+        <v>0.348417128101589</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9351,13 +9351,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2519897217357894</v>
+        <v>0.2423964168170901</v>
       </c>
       <c r="C97">
-        <v>-4073.135627376246</v>
+        <v>-4037.144265937781</v>
       </c>
       <c r="D97">
-        <v>745.3043726237541</v>
+        <v>781.2957340622191</v>
       </c>
       <c r="E97">
         <v>3429.54</v>
@@ -9384,37 +9384,37 @@
         <v>435.9</v>
       </c>
       <c r="M97">
-        <v>1317.132431397471</v>
+        <v>1264.396031397471</v>
       </c>
       <c r="N97">
-        <v>-881.2324313974709</v>
+        <v>-828.4960313974709</v>
       </c>
       <c r="O97">
-        <v>-176.2464862794942</v>
+        <v>-165.6992062794942</v>
       </c>
       <c r="P97">
-        <v>-704.9859451179767</v>
+        <v>-662.7968251179767</v>
       </c>
       <c r="Q97">
-        <v>-485.8859451179767</v>
+        <v>-443.6968251179767</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6084915402156057</v>
+        <v>0.6066254418416189</v>
       </c>
       <c r="T97">
-        <v>11.56352320658335</v>
+        <v>11.53116136326873</v>
       </c>
       <c r="U97">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V97">
-        <v>0.06618924408952748</v>
+        <v>0.06894991587694602</v>
       </c>
       <c r="W97">
-        <v>0.2332264681315886</v>
+        <v>0.2232264681315886</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3309462204476374</v>
+        <v>0.3447495793847301</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9433,13 +9433,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2540292991802063</v>
+        <v>0.244335994261507</v>
       </c>
       <c r="C98">
-        <v>-4135.947781550578</v>
+        <v>-4100.289056096779</v>
       </c>
       <c r="D98">
-        <v>738.0042184494216</v>
+        <v>773.6629439032206</v>
       </c>
       <c r="E98">
         <v>3485.052</v>
@@ -9466,37 +9466,37 @@
         <v>435.9</v>
       </c>
       <c r="M98">
-        <v>1330.996983306918</v>
+        <v>1277.705463306918</v>
       </c>
       <c r="N98">
-        <v>-895.096983306918</v>
+        <v>-841.8054633069178</v>
       </c>
       <c r="O98">
-        <v>-179.0193966613836</v>
+        <v>-168.3610926613836</v>
       </c>
       <c r="P98">
-        <v>-716.0775866455344</v>
+        <v>-673.4443706455343</v>
       </c>
       <c r="Q98">
-        <v>-496.9775866455345</v>
+        <v>-454.3443706455343</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.7491644252695057</v>
+        <v>0.7468318023020221</v>
       </c>
       <c r="T98">
-        <v>14.45440400822915</v>
+        <v>14.41395170408588</v>
       </c>
       <c r="U98">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V98">
-        <v>0.06549977279692823</v>
+        <v>0.06823168758656116</v>
       </c>
       <c r="W98">
-        <v>0.2333986689264855</v>
+        <v>0.2233986689264855</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3274988639846412</v>
+        <v>0.3411584379328059</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9515,13 +9515,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2560688766246232</v>
+        <v>0.2462755717059238</v>
       </c>
       <c r="C99">
-        <v>-4198.618314862767</v>
+        <v>-4163.286153571782</v>
       </c>
       <c r="D99">
-        <v>730.8456851372325</v>
+        <v>766.1778464282173</v>
       </c>
       <c r="E99">
         <v>3540.564</v>
@@ -9548,37 +9548,37 @@
         <v>435.9</v>
       </c>
       <c r="M99">
-        <v>1344.861535216365</v>
+        <v>1291.014895216365</v>
       </c>
       <c r="N99">
-        <v>-908.9615352163648</v>
+        <v>-855.1148952163649</v>
       </c>
       <c r="O99">
-        <v>-181.792307043273</v>
+        <v>-171.022979043273</v>
       </c>
       <c r="P99">
-        <v>-727.1692281730918</v>
+        <v>-684.0919161730919</v>
       </c>
       <c r="Q99">
-        <v>-508.0692281730919</v>
+        <v>-464.991916173092</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.9836192336926742</v>
+        <v>0.9805090697360295</v>
       </c>
       <c r="T99">
-        <v>19.27253867763887</v>
+        <v>19.21860227211451</v>
       </c>
       <c r="U99">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V99">
-        <v>0.06482451740726919</v>
+        <v>0.06752826812690589</v>
       </c>
       <c r="W99">
-        <v>0.2335673191895288</v>
+        <v>0.2235673191895288</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.324122587036346</v>
+        <v>0.3376413406345296</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9597,13 +9597,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2581084540690401</v>
+        <v>0.2482151491503407</v>
       </c>
       <c r="C100">
-        <v>-4261.151308827853</v>
+        <v>-4226.13980401436</v>
       </c>
       <c r="D100">
-        <v>723.8246911721473</v>
+        <v>758.8361959856392</v>
       </c>
       <c r="E100">
         <v>3596.076</v>
@@ -9630,37 +9630,37 @@
         <v>435.9</v>
       </c>
       <c r="M100">
-        <v>1358.726087125812</v>
+        <v>1304.324327125812</v>
       </c>
       <c r="N100">
-        <v>-922.8260871258119</v>
+        <v>-868.4243271258119</v>
       </c>
       <c r="O100">
-        <v>-184.5652174251624</v>
+        <v>-173.6848654251624</v>
       </c>
       <c r="P100">
-        <v>-738.2608697006496</v>
+        <v>-694.7394617006496</v>
       </c>
       <c r="Q100">
-        <v>-519.1608697006495</v>
+        <v>-475.6394617006496</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.452528850539011</v>
+        <v>1.447863604604044</v>
       </c>
       <c r="T100">
-        <v>28.90880801645831</v>
+        <v>28.82790340817176</v>
       </c>
       <c r="U100">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V100">
-        <v>0.06416304273984806</v>
+        <v>0.06683920416642726</v>
       </c>
       <c r="W100">
-        <v>0.2337325276104693</v>
+        <v>0.2237325276104692</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3208152136992404</v>
+        <v>0.3341960208321363</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9679,13 +9679,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.260148031513457</v>
+        <v>0.2501547265947576</v>
       </c>
       <c r="C101">
-        <v>-4323.550689614151</v>
+        <v>-4288.854091890284</v>
       </c>
       <c r="D101">
-        <v>716.9373103858487</v>
+        <v>751.6339081097168</v>
       </c>
       <c r="E101">
         <v>3651.588</v>
@@ -9712,37 +9712,37 @@
         <v>435.9</v>
       </c>
       <c r="M101">
-        <v>1372.590639035259</v>
+        <v>1317.633759035259</v>
       </c>
       <c r="N101">
-        <v>-936.6906390352592</v>
+        <v>-881.733759035259</v>
       </c>
       <c r="O101">
-        <v>-187.3381278070518</v>
+        <v>-176.3467518070518</v>
       </c>
       <c r="P101">
-        <v>-749.3525112282074</v>
+        <v>-705.3870072282073</v>
       </c>
       <c r="Q101">
-        <v>-530.2525112282074</v>
+        <v>-486.2870072282073</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.859257701078023</v>
+        <v>2.849927209208088</v>
       </c>
       <c r="T101">
-        <v>57.81761603291661</v>
+        <v>57.65580681634353</v>
       </c>
       <c r="U101">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V101">
-        <v>0.06351493119702131</v>
+        <v>0.06616406068999871</v>
       </c>
       <c r="W101">
-        <v>0.2338943984875523</v>
+        <v>0.2238943984875523</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3175746559851066</v>
+        <v>0.3308203034499936</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/finland/finland_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_packaging_container.xlsx
@@ -1421,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1558,22 +1558,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07580678941787569</v>
+        <v>0.07572283779457345</v>
       </c>
       <c r="C2">
-        <v>5574.039595002044</v>
+        <v>5532.889030116401</v>
       </c>
       <c r="D2">
-        <v>5118.839595002044</v>
+        <v>5133.201030116401</v>
       </c>
       <c r="E2">
-        <v>-1844.1</v>
+        <v>-1788.588</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>55.512</v>
       </c>
       <c r="G2">
         <v>455.2</v>
@@ -1594,28 +1594,28 @@
         <v>435.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.011955909447062</v>
       </c>
       <c r="N2">
-        <v>435.9</v>
+        <v>432.888044090553</v>
       </c>
       <c r="O2">
-        <v>87.18000000000001</v>
+        <v>86.5776088181106</v>
       </c>
       <c r="P2">
-        <v>348.72</v>
+        <v>346.3104352724424</v>
       </c>
       <c r="Q2">
-        <v>567.8199999999999</v>
+        <v>565.4104352724423</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07580678941787569</v>
+        <v>0.07604926852428276</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.6219567987660169</v>
       </c>
       <c r="U2">
         <v>0.05425774444168939</v>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>144.7232340396454</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1640,22 +1640,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07572283779457345</v>
+        <v>0.07563888617127121</v>
       </c>
       <c r="C3">
-        <v>5532.889030116401</v>
+        <v>5491.819276946308</v>
       </c>
       <c r="D3">
-        <v>5133.201030116401</v>
+        <v>5147.643276946309</v>
       </c>
       <c r="E3">
-        <v>-1788.588</v>
+        <v>-1733.076</v>
       </c>
       <c r="F3">
-        <v>55.512</v>
+        <v>111.024</v>
       </c>
       <c r="G3">
         <v>455.2</v>
@@ -1676,28 +1676,28 @@
         <v>435.9</v>
       </c>
       <c r="M3">
-        <v>3.011955909447062</v>
+        <v>6.023911818894123</v>
       </c>
       <c r="N3">
-        <v>432.888044090553</v>
+        <v>429.8760881811059</v>
       </c>
       <c r="O3">
-        <v>86.5776088181106</v>
+        <v>85.97521763622119</v>
       </c>
       <c r="P3">
-        <v>346.3104352724424</v>
+        <v>343.9008705448847</v>
       </c>
       <c r="Q3">
-        <v>565.4104352724423</v>
+        <v>563.0008705448847</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07604926852428276</v>
+        <v>0.07629669618388182</v>
       </c>
       <c r="T3">
-        <v>0.6219567987660169</v>
+        <v>0.6270441718694975</v>
       </c>
       <c r="U3">
         <v>0.05425774444168939</v>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>144.7232340396454</v>
+        <v>72.36161701982269</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1722,22 +1722,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07563888617127121</v>
+        <v>0.07555493454796895</v>
       </c>
       <c r="C4">
-        <v>5491.819276946308</v>
+        <v>5450.831019506854</v>
       </c>
       <c r="D4">
-        <v>5147.643276946309</v>
+        <v>5162.167019506855</v>
       </c>
       <c r="E4">
-        <v>-1733.076</v>
+        <v>-1677.564</v>
       </c>
       <c r="F4">
-        <v>111.024</v>
+        <v>166.536</v>
       </c>
       <c r="G4">
         <v>455.2</v>
@@ -1758,28 +1758,28 @@
         <v>435.9</v>
       </c>
       <c r="M4">
-        <v>6.023911818894123</v>
+        <v>9.035867728341184</v>
       </c>
       <c r="N4">
-        <v>429.8760881811059</v>
+        <v>426.8641322716588</v>
       </c>
       <c r="O4">
-        <v>85.97521763622119</v>
+        <v>85.37282645433177</v>
       </c>
       <c r="P4">
-        <v>343.9008705448847</v>
+        <v>341.4913058173271</v>
       </c>
       <c r="Q4">
-        <v>563.0008705448847</v>
+        <v>560.5913058173271</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07629669618388182</v>
+        <v>0.07654922544470971</v>
       </c>
       <c r="T4">
-        <v>0.6270441718694975</v>
+        <v>0.6322364392637714</v>
       </c>
       <c r="U4">
         <v>0.05425774444168939</v>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>72.36161701982269</v>
+        <v>48.24107801321512</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1804,22 +1804,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07555493454796895</v>
+        <v>0.07547098292466674</v>
       </c>
       <c r="C5">
-        <v>5450.831019506854</v>
+        <v>5409.924949554575</v>
       </c>
       <c r="D5">
-        <v>5162.167019506855</v>
+        <v>5176.772949554575</v>
       </c>
       <c r="E5">
-        <v>-1677.564</v>
+        <v>-1622.052</v>
       </c>
       <c r="F5">
-        <v>166.536</v>
+        <v>222.048</v>
       </c>
       <c r="G5">
         <v>455.2</v>
@@ -1840,28 +1840,28 @@
         <v>435.9</v>
       </c>
       <c r="M5">
-        <v>9.035867728341184</v>
+        <v>12.04782363778825</v>
       </c>
       <c r="N5">
-        <v>426.8641322716588</v>
+        <v>423.8521763622118</v>
       </c>
       <c r="O5">
-        <v>85.37282645433177</v>
+        <v>84.77043527244236</v>
       </c>
       <c r="P5">
-        <v>341.4913058173271</v>
+        <v>339.0817410897694</v>
       </c>
       <c r="Q5">
-        <v>560.5913058173271</v>
+        <v>558.1817410897694</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07654922544470971</v>
+        <v>0.07680701573180487</v>
       </c>
       <c r="T5">
-        <v>0.6322364392637714</v>
+        <v>0.6375368788954262</v>
       </c>
       <c r="U5">
         <v>0.05425774444168939</v>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.24107801321512</v>
+        <v>36.18080850991134</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1886,22 +1886,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07547098292466674</v>
+        <v>0.0753870313013645</v>
       </c>
       <c r="C6">
-        <v>5409.924949554575</v>
+        <v>5369.101766697313</v>
       </c>
       <c r="D6">
-        <v>5176.772949554575</v>
+        <v>5191.461766697314</v>
       </c>
       <c r="E6">
-        <v>-1622.052</v>
+        <v>-1566.54</v>
       </c>
       <c r="F6">
-        <v>222.048</v>
+        <v>277.56</v>
       </c>
       <c r="G6">
         <v>455.2</v>
@@ -1922,28 +1922,28 @@
         <v>435.9</v>
       </c>
       <c r="M6">
-        <v>12.04782363778825</v>
+        <v>15.05977954723531</v>
       </c>
       <c r="N6">
-        <v>423.8521763622118</v>
+        <v>420.8402204527648</v>
       </c>
       <c r="O6">
-        <v>84.77043527244236</v>
+        <v>84.16804409055295</v>
       </c>
       <c r="P6">
-        <v>339.0817410897694</v>
+        <v>336.6721763622118</v>
       </c>
       <c r="Q6">
-        <v>558.1817410897694</v>
+        <v>555.7721763622118</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07680701573180487</v>
+        <v>0.07707023318283887</v>
       </c>
       <c r="T6">
-        <v>0.6375368788954262</v>
+        <v>0.6429489067298524</v>
       </c>
       <c r="U6">
         <v>0.05425774444168939</v>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.18080850991134</v>
+        <v>28.94464680792908</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1968,22 +1968,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0753870313013645</v>
+        <v>0.07530307967806227</v>
       </c>
       <c r="C7">
-        <v>5369.101766697313</v>
+        <v>5328.362178505893</v>
       </c>
       <c r="D7">
-        <v>5191.461766697314</v>
+        <v>5206.234178505893</v>
       </c>
       <c r="E7">
-        <v>-1566.54</v>
+        <v>-1511.028</v>
       </c>
       <c r="F7">
-        <v>277.56</v>
+        <v>333.072</v>
       </c>
       <c r="G7">
         <v>455.2</v>
@@ -2004,28 +2004,28 @@
         <v>435.9</v>
       </c>
       <c r="M7">
-        <v>15.05977954723531</v>
+        <v>18.07173545668237</v>
       </c>
       <c r="N7">
-        <v>420.8402204527648</v>
+        <v>417.8282645433177</v>
       </c>
       <c r="O7">
-        <v>84.16804409055295</v>
+        <v>83.56565290866354</v>
       </c>
       <c r="P7">
-        <v>336.6721763622118</v>
+        <v>334.2626116346541</v>
       </c>
       <c r="Q7">
-        <v>555.7721763622118</v>
+        <v>553.3626116346541</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07707023318283887</v>
+        <v>0.07733905100517147</v>
       </c>
       <c r="T7">
-        <v>0.6429489067298524</v>
+        <v>0.648476084092671</v>
       </c>
       <c r="U7">
         <v>0.05425774444168939</v>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.94464680792908</v>
+        <v>24.12053900660757</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2050,22 +2050,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07530307967806227</v>
+        <v>0.07521912805476004</v>
       </c>
       <c r="C8">
-        <v>5328.362178505893</v>
+        <v>5287.706900627757</v>
       </c>
       <c r="D8">
-        <v>5206.234178505893</v>
+        <v>5221.090900627757</v>
       </c>
       <c r="E8">
-        <v>-1511.028</v>
+        <v>-1455.516</v>
       </c>
       <c r="F8">
-        <v>333.072</v>
+        <v>388.5839999999999</v>
       </c>
       <c r="G8">
         <v>455.2</v>
@@ -2086,28 +2086,28 @@
         <v>435.9</v>
       </c>
       <c r="M8">
-        <v>18.07173545668237</v>
+        <v>21.08369136612943</v>
       </c>
       <c r="N8">
-        <v>417.8282645433177</v>
+        <v>414.8163086338706</v>
       </c>
       <c r="O8">
-        <v>83.56565290866354</v>
+        <v>82.96326172677414</v>
       </c>
       <c r="P8">
-        <v>334.2626116346541</v>
+        <v>331.8530469070965</v>
       </c>
       <c r="Q8">
-        <v>553.3626116346541</v>
+        <v>550.9530469070965</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07733905100517147</v>
+        <v>0.07761364985594132</v>
       </c>
       <c r="T8">
-        <v>0.648476084092671</v>
+        <v>0.6541221254847973</v>
       </c>
       <c r="U8">
         <v>0.05425774444168939</v>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.12053900660757</v>
+        <v>20.67474771994934</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2132,22 +2132,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07521912805476003</v>
+        <v>0.0751351764314578</v>
       </c>
       <c r="C9">
-        <v>5287.706900627761</v>
+        <v>5247.136656902529</v>
       </c>
       <c r="D9">
-        <v>5221.090900627761</v>
+        <v>5236.032656902529</v>
       </c>
       <c r="E9">
-        <v>-1455.516</v>
+        <v>-1400.004</v>
       </c>
       <c r="F9">
-        <v>388.584</v>
+        <v>444.096</v>
       </c>
       <c r="G9">
         <v>455.2</v>
@@ -2168,28 +2168,28 @@
         <v>435.9</v>
       </c>
       <c r="M9">
-        <v>21.08369136612943</v>
+        <v>24.09564727557649</v>
       </c>
       <c r="N9">
-        <v>414.8163086338706</v>
+        <v>411.8043527244236</v>
       </c>
       <c r="O9">
-        <v>82.96326172677414</v>
+        <v>82.36087054488472</v>
       </c>
       <c r="P9">
-        <v>331.8530469070965</v>
+        <v>329.4434821795388</v>
       </c>
       <c r="Q9">
-        <v>550.9530469070965</v>
+        <v>548.5434821795388</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07761364985594132</v>
+        <v>0.0778942182469453</v>
       </c>
       <c r="T9">
-        <v>0.6541221254847973</v>
+        <v>0.6598909069071872</v>
       </c>
       <c r="U9">
         <v>0.05425774444168939</v>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.67474771994934</v>
+        <v>18.09040425495567</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2214,22 +2214,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0751351764314578</v>
+        <v>0.07505122480815556</v>
       </c>
       <c r="C10">
-        <v>5247.136656902529</v>
+        <v>5206.652179479565</v>
       </c>
       <c r="D10">
-        <v>5236.032656902529</v>
+        <v>5251.060179479566</v>
       </c>
       <c r="E10">
-        <v>-1400.004</v>
+        <v>-1344.492</v>
       </c>
       <c r="F10">
-        <v>444.096</v>
+        <v>499.6079999999999</v>
       </c>
       <c r="G10">
         <v>455.2</v>
@@ -2250,28 +2250,28 @@
         <v>435.9</v>
       </c>
       <c r="M10">
-        <v>24.09564727557649</v>
+        <v>27.10760318502355</v>
       </c>
       <c r="N10">
-        <v>411.8043527244236</v>
+        <v>408.7923968149765</v>
       </c>
       <c r="O10">
-        <v>82.36087054488472</v>
+        <v>81.7584793629953</v>
       </c>
       <c r="P10">
-        <v>329.4434821795388</v>
+        <v>327.0339174519812</v>
       </c>
       <c r="Q10">
-        <v>548.5434821795388</v>
+        <v>546.1339174519812</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0778942182469453</v>
+        <v>0.07818095297621311</v>
       </c>
       <c r="T10">
-        <v>0.6598909069071872</v>
+        <v>0.6657864747344648</v>
       </c>
       <c r="U10">
         <v>0.05425774444168939</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.09040425495567</v>
+        <v>16.08035933773838</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2296,22 +2296,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07505122480815556</v>
+        <v>0.07496727318485333</v>
       </c>
       <c r="C11">
-        <v>5206.652179479565</v>
+        <v>5166.254208937551</v>
       </c>
       <c r="D11">
-        <v>5251.060179479566</v>
+        <v>5266.174208937551</v>
       </c>
       <c r="E11">
-        <v>-1344.492</v>
+        <v>-1288.98</v>
       </c>
       <c r="F11">
-        <v>499.6079999999999</v>
+        <v>555.1199999999999</v>
       </c>
       <c r="G11">
         <v>455.2</v>
@@ -2332,28 +2332,28 @@
         <v>435.9</v>
       </c>
       <c r="M11">
-        <v>27.10760318502355</v>
+        <v>30.11955909447061</v>
       </c>
       <c r="N11">
-        <v>408.7923968149765</v>
+        <v>405.7804409055294</v>
       </c>
       <c r="O11">
-        <v>81.7584793629953</v>
+        <v>81.15608818110589</v>
       </c>
       <c r="P11">
-        <v>327.0339174519812</v>
+        <v>324.6243527244235</v>
       </c>
       <c r="Q11">
-        <v>546.1339174519812</v>
+        <v>543.7243527244235</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07818095297621311</v>
+        <v>0.07847405958835352</v>
       </c>
       <c r="T11">
-        <v>0.6657864747344648</v>
+        <v>0.6718130551801264</v>
       </c>
       <c r="U11">
         <v>0.05425774444168939</v>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.08035933773838</v>
+        <v>14.47232340396454</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2378,22 +2378,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07496727318485334</v>
+        <v>0.07488332156155109</v>
       </c>
       <c r="C12">
-        <v>5166.254208937549</v>
+        <v>5125.943494406168</v>
       </c>
       <c r="D12">
-        <v>5266.174208937549</v>
+        <v>5281.375494406167</v>
       </c>
       <c r="E12">
-        <v>-1288.98</v>
+        <v>-1233.468</v>
       </c>
       <c r="F12">
-        <v>555.12</v>
+        <v>610.6319999999999</v>
       </c>
       <c r="G12">
         <v>455.2</v>
@@ -2414,28 +2414,28 @@
         <v>435.9</v>
       </c>
       <c r="M12">
-        <v>30.11955909447061</v>
+        <v>33.13151500391767</v>
       </c>
       <c r="N12">
-        <v>405.7804409055294</v>
+        <v>402.7684849960823</v>
       </c>
       <c r="O12">
-        <v>81.15608818110589</v>
+        <v>80.55369699921647</v>
       </c>
       <c r="P12">
-        <v>324.6243527244235</v>
+        <v>322.2147879968659</v>
       </c>
       <c r="Q12">
-        <v>543.7243527244235</v>
+        <v>541.3147879968658</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07847405958835353</v>
+        <v>0.0787737528659353</v>
       </c>
       <c r="T12">
-        <v>0.6718130551801266</v>
+        <v>0.6779750643998478</v>
       </c>
       <c r="U12">
         <v>0.05425774444168939</v>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.47232340396454</v>
+        <v>13.15665763996776</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2460,22 +2460,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07488332156155109</v>
+        <v>0.07494336993824885</v>
       </c>
       <c r="C13">
-        <v>5125.943494406168</v>
+        <v>5059.549498746695</v>
       </c>
       <c r="D13">
-        <v>5281.375494406167</v>
+        <v>5270.493498746695</v>
       </c>
       <c r="E13">
-        <v>-1233.468</v>
+        <v>-1177.956</v>
       </c>
       <c r="F13">
-        <v>610.6319999999999</v>
+        <v>666.144</v>
       </c>
       <c r="G13">
         <v>455.2</v>
@@ -2496,45 +2496,45 @@
         <v>435.9</v>
       </c>
       <c r="M13">
-        <v>33.13151500391767</v>
+        <v>37.14268691336473</v>
       </c>
       <c r="N13">
-        <v>402.7684849960823</v>
+        <v>398.7573130866353</v>
       </c>
       <c r="O13">
-        <v>80.55369699921647</v>
+        <v>79.75146261732706</v>
       </c>
       <c r="P13">
-        <v>322.2147879968659</v>
+        <v>319.0058504693083</v>
       </c>
       <c r="Q13">
-        <v>541.3147879968658</v>
+        <v>538.1058504693083</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0787737528659353</v>
+        <v>0.07908025735437121</v>
       </c>
       <c r="T13">
-        <v>0.6779750643998478</v>
+        <v>0.6842771192836539</v>
       </c>
       <c r="U13">
-        <v>0.05425774444168939</v>
+        <v>0.05575774444168938</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04340619555335151</v>
+        <v>0.04460619555335151</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.15665763996776</v>
+        <v>11.73582301723987</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2542,22 +2542,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07494336993824885</v>
+        <v>0.07487141831494661</v>
       </c>
       <c r="C14">
-        <v>5059.549498746695</v>
+        <v>5017.081945313781</v>
       </c>
       <c r="D14">
-        <v>5270.493498746695</v>
+        <v>5283.537945313781</v>
       </c>
       <c r="E14">
-        <v>-1177.956</v>
+        <v>-1122.444</v>
       </c>
       <c r="F14">
-        <v>666.144</v>
+        <v>721.6559999999999</v>
       </c>
       <c r="G14">
         <v>455.2</v>
@@ -2578,28 +2578,28 @@
         <v>435.9</v>
       </c>
       <c r="M14">
-        <v>37.14268691336473</v>
+        <v>40.23791082281179</v>
       </c>
       <c r="N14">
-        <v>398.7573130866353</v>
+        <v>395.6620891771882</v>
       </c>
       <c r="O14">
-        <v>79.75146261732706</v>
+        <v>79.13241783543765</v>
       </c>
       <c r="P14">
-        <v>319.0058504693083</v>
+        <v>316.5296713417506</v>
       </c>
       <c r="Q14">
-        <v>538.1058504693083</v>
+        <v>535.6296713417505</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07908025735437121</v>
+        <v>0.07939380792300105</v>
       </c>
       <c r="T14">
-        <v>0.6842771192836539</v>
+        <v>0.6907240489923748</v>
       </c>
       <c r="U14">
         <v>0.05575774444168938</v>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.73582301723987</v>
+        <v>10.83306740052911</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2624,22 +2624,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07487141831494661</v>
+        <v>0.07479946669164438</v>
       </c>
       <c r="C15">
-        <v>5017.081945313781</v>
+        <v>4974.679121975082</v>
       </c>
       <c r="D15">
-        <v>5283.537945313781</v>
+        <v>5296.647121975082</v>
       </c>
       <c r="E15">
-        <v>-1122.444</v>
+        <v>-1066.932</v>
       </c>
       <c r="F15">
-        <v>721.6559999999999</v>
+        <v>777.168</v>
       </c>
       <c r="G15">
         <v>455.2</v>
@@ -2660,28 +2660,28 @@
         <v>435.9</v>
       </c>
       <c r="M15">
-        <v>40.23791082281179</v>
+        <v>43.33313473225886</v>
       </c>
       <c r="N15">
-        <v>395.6620891771882</v>
+        <v>392.5668652677412</v>
       </c>
       <c r="O15">
-        <v>79.13241783543765</v>
+        <v>78.51337305354824</v>
       </c>
       <c r="P15">
-        <v>316.5296713417506</v>
+        <v>314.0534922141929</v>
       </c>
       <c r="Q15">
-        <v>535.6296713417505</v>
+        <v>533.153492214193</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07939380792300105</v>
+        <v>0.07971465036531997</v>
       </c>
       <c r="T15">
-        <v>0.6907240489923748</v>
+        <v>0.6973209072989732</v>
       </c>
       <c r="U15">
         <v>0.05575774444168938</v>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.83306740052911</v>
+        <v>10.05927687191989</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2706,22 +2706,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07479946669164438</v>
+        <v>0.07493151506834214</v>
       </c>
       <c r="C16">
-        <v>4974.679121975082</v>
+        <v>4895.158289864671</v>
       </c>
       <c r="D16">
-        <v>5296.647121975082</v>
+        <v>5272.638289864672</v>
       </c>
       <c r="E16">
-        <v>-1066.932</v>
+        <v>-1011.42</v>
       </c>
       <c r="F16">
-        <v>777.168</v>
+        <v>832.6800000000001</v>
       </c>
       <c r="G16">
         <v>455.2</v>
@@ -2742,45 +2742,45 @@
         <v>435.9</v>
       </c>
       <c r="M16">
-        <v>43.33313473225886</v>
+        <v>47.84391464170592</v>
       </c>
       <c r="N16">
-        <v>392.5668652677412</v>
+        <v>388.0560853582941</v>
       </c>
       <c r="O16">
-        <v>78.51337305354824</v>
+        <v>77.61121707165883</v>
       </c>
       <c r="P16">
-        <v>314.0534922141929</v>
+        <v>310.4448682866353</v>
       </c>
       <c r="Q16">
-        <v>533.153492214193</v>
+        <v>529.5448682866353</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07971465036531997</v>
+        <v>0.08004304204157578</v>
       </c>
       <c r="T16">
-        <v>0.6973209072989732</v>
+        <v>0.7040729858010208</v>
       </c>
       <c r="U16">
-        <v>0.05575774444168938</v>
+        <v>0.05745774444168938</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04460619555335151</v>
+        <v>0.04596619555335151</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.05927687191989</v>
+        <v>9.110876550641249</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2788,22 +2788,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07493151506834214</v>
+        <v>0.0748731634450399</v>
       </c>
       <c r="C17">
-        <v>4895.158289864671</v>
+        <v>4850.228798502948</v>
       </c>
       <c r="D17">
-        <v>5272.638289864672</v>
+        <v>5283.220798502948</v>
       </c>
       <c r="E17">
-        <v>-1011.42</v>
+        <v>-955.9079999999999</v>
       </c>
       <c r="F17">
-        <v>832.6799999999999</v>
+        <v>888.192</v>
       </c>
       <c r="G17">
         <v>455.2</v>
@@ -2824,28 +2824,28 @@
         <v>435.9</v>
       </c>
       <c r="M17">
-        <v>47.84391464170591</v>
+        <v>51.03350895115298</v>
       </c>
       <c r="N17">
-        <v>388.0560853582941</v>
+        <v>384.866491048847</v>
       </c>
       <c r="O17">
-        <v>77.61121707165883</v>
+        <v>76.97329820976941</v>
       </c>
       <c r="P17">
-        <v>310.4448682866353</v>
+        <v>307.8931928390776</v>
       </c>
       <c r="Q17">
-        <v>529.5448682866353</v>
+        <v>526.9931928390777</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08004304204157578</v>
+        <v>0.08037925256726626</v>
       </c>
       <c r="T17">
-        <v>0.7040729858010208</v>
+        <v>0.7109858280769268</v>
       </c>
       <c r="U17">
         <v>0.05745774444168938</v>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.110876550641251</v>
+        <v>8.541446766226171</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2870,22 +2870,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0748731634450399</v>
+        <v>0.07481481182173766</v>
       </c>
       <c r="C18">
-        <v>4850.228798502948</v>
+        <v>4805.341872060236</v>
       </c>
       <c r="D18">
-        <v>5283.220798502948</v>
+        <v>5293.845872060236</v>
       </c>
       <c r="E18">
-        <v>-955.9079999999999</v>
+        <v>-900.3959999999998</v>
       </c>
       <c r="F18">
-        <v>888.192</v>
+        <v>943.7040000000001</v>
       </c>
       <c r="G18">
         <v>455.2</v>
@@ -2906,28 +2906,28 @@
         <v>435.9</v>
       </c>
       <c r="M18">
-        <v>51.03350895115298</v>
+        <v>54.22310326060004</v>
       </c>
       <c r="N18">
-        <v>384.866491048847</v>
+        <v>381.6768967394</v>
       </c>
       <c r="O18">
-        <v>76.97329820976941</v>
+        <v>76.33537934787999</v>
       </c>
       <c r="P18">
-        <v>307.8931928390776</v>
+        <v>305.34151739152</v>
       </c>
       <c r="Q18">
-        <v>526.9931928390777</v>
+        <v>524.4415173915199</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08037925256726626</v>
+        <v>0.08072356455140711</v>
       </c>
       <c r="T18">
-        <v>0.7109858280769268</v>
+        <v>0.7180652448655052</v>
       </c>
       <c r="U18">
         <v>0.05745774444168938</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.541446766226171</v>
+        <v>8.039008721154044</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2952,22 +2952,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07481481182173766</v>
+        <v>0.07487166019843541</v>
       </c>
       <c r="C19">
-        <v>4805.341872060236</v>
+        <v>4739.477984955731</v>
       </c>
       <c r="D19">
-        <v>5293.845872060236</v>
+        <v>5283.493984955731</v>
       </c>
       <c r="E19">
-        <v>-900.3959999999998</v>
+        <v>-844.8839999999998</v>
       </c>
       <c r="F19">
-        <v>943.7040000000001</v>
+        <v>999.2160000000001</v>
       </c>
       <c r="G19">
         <v>455.2</v>
@@ -2988,45 +2988,45 @@
         <v>435.9</v>
       </c>
       <c r="M19">
-        <v>54.22310326060004</v>
+        <v>58.21207037004711</v>
       </c>
       <c r="N19">
-        <v>381.6768967394</v>
+        <v>377.6879296299529</v>
       </c>
       <c r="O19">
-        <v>76.33537934787999</v>
+        <v>75.53758592599058</v>
       </c>
       <c r="P19">
-        <v>305.34151739152</v>
+        <v>302.1503437039623</v>
       </c>
       <c r="Q19">
-        <v>524.4415173915199</v>
+        <v>521.2503437039622</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08072356455140711</v>
+        <v>0.0810762743888197</v>
       </c>
       <c r="T19">
-        <v>0.7180652448655052</v>
+        <v>0.7253173303562441</v>
       </c>
       <c r="U19">
-        <v>0.05745774444168938</v>
+        <v>0.05825774444168939</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04596619555335151</v>
+        <v>0.04660619555335151</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>8.039008721154044</v>
+        <v>7.4881377217652</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3034,22 +3034,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07487166019843543</v>
+        <v>0.0748197085751332</v>
       </c>
       <c r="C20">
-        <v>4739.477984955727</v>
+        <v>4693.424594387154</v>
       </c>
       <c r="D20">
-        <v>5283.493984955728</v>
+        <v>5292.952594387154</v>
       </c>
       <c r="E20">
-        <v>-844.884</v>
+        <v>-789.3719999999998</v>
       </c>
       <c r="F20">
-        <v>999.2159999999999</v>
+        <v>1054.728</v>
       </c>
       <c r="G20">
         <v>455.2</v>
@@ -3070,28 +3070,28 @@
         <v>435.9</v>
       </c>
       <c r="M20">
-        <v>58.21207037004709</v>
+        <v>61.44607427949417</v>
       </c>
       <c r="N20">
-        <v>377.6879296299529</v>
+        <v>374.4539257205059</v>
       </c>
       <c r="O20">
-        <v>75.53758592599058</v>
+        <v>74.89078514410117</v>
       </c>
       <c r="P20">
-        <v>302.1503437039623</v>
+        <v>299.5631405764047</v>
       </c>
       <c r="Q20">
-        <v>521.2503437039622</v>
+        <v>518.6631405764047</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0810762743888197</v>
+        <v>0.08143769311110668</v>
       </c>
       <c r="T20">
-        <v>0.725317330356244</v>
+        <v>0.7327484796862604</v>
       </c>
       <c r="U20">
         <v>0.05825774444168939</v>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.488137721765201</v>
+        <v>7.094025210093347</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3116,22 +3116,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0748197085751332</v>
+        <v>0.07476775695183097</v>
       </c>
       <c r="C21">
-        <v>4693.424594387154</v>
+        <v>4647.405130512662</v>
       </c>
       <c r="D21">
-        <v>5292.952594387154</v>
+        <v>5302.445130512662</v>
       </c>
       <c r="E21">
-        <v>-789.3719999999998</v>
+        <v>-733.8599999999999</v>
       </c>
       <c r="F21">
-        <v>1054.728</v>
+        <v>1110.24</v>
       </c>
       <c r="G21">
         <v>455.2</v>
@@ -3152,28 +3152,28 @@
         <v>435.9</v>
       </c>
       <c r="M21">
-        <v>61.44607427949417</v>
+        <v>64.68007818894122</v>
       </c>
       <c r="N21">
-        <v>374.4539257205059</v>
+        <v>371.2199218110588</v>
       </c>
       <c r="O21">
-        <v>74.89078514410117</v>
+        <v>74.24398436221178</v>
       </c>
       <c r="P21">
-        <v>299.5631405764047</v>
+        <v>296.975937448847</v>
       </c>
       <c r="Q21">
-        <v>518.6631405764047</v>
+        <v>516.0759374488471</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08143769311110668</v>
+        <v>0.08180814730145082</v>
       </c>
       <c r="T21">
-        <v>0.7327484796862604</v>
+        <v>0.7403654077495271</v>
       </c>
       <c r="U21">
         <v>0.05825774444168939</v>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.094025210093347</v>
+        <v>6.739323949588681</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3198,22 +3198,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07476775695183097</v>
+        <v>0.07471580532852871</v>
       </c>
       <c r="C22">
-        <v>4647.405130512662</v>
+        <v>4601.419776195585</v>
       </c>
       <c r="D22">
-        <v>5302.445130512662</v>
+        <v>5311.971776195585</v>
       </c>
       <c r="E22">
-        <v>-733.8599999999999</v>
+        <v>-678.3479999999997</v>
       </c>
       <c r="F22">
-        <v>1110.24</v>
+        <v>1165.752</v>
       </c>
       <c r="G22">
         <v>455.2</v>
@@ -3234,28 +3234,28 @@
         <v>435.9</v>
       </c>
       <c r="M22">
-        <v>64.68007818894122</v>
+        <v>67.91408209838829</v>
       </c>
       <c r="N22">
-        <v>371.2199218110588</v>
+        <v>367.9859179016117</v>
       </c>
       <c r="O22">
-        <v>74.24398436221178</v>
+        <v>73.59718358032235</v>
       </c>
       <c r="P22">
-        <v>296.975937448847</v>
+        <v>294.3887343212894</v>
       </c>
       <c r="Q22">
-        <v>516.0759374488471</v>
+        <v>513.4887343212894</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08180814730145082</v>
+        <v>0.08218798007889228</v>
       </c>
       <c r="T22">
-        <v>0.7403654077495271</v>
+        <v>0.7481751694346487</v>
       </c>
       <c r="U22">
         <v>0.05825774444168939</v>
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.739323949588681</v>
+        <v>6.418403761513028</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3280,22 +3280,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07471580532852871</v>
+        <v>0.0746638537052265</v>
       </c>
       <c r="C23">
-        <v>4601.419776195586</v>
+        <v>4555.468715615774</v>
       </c>
       <c r="D23">
-        <v>5311.971776195585</v>
+        <v>5321.532715615775</v>
       </c>
       <c r="E23">
-        <v>-678.348</v>
+        <v>-622.836</v>
       </c>
       <c r="F23">
-        <v>1165.752</v>
+        <v>1221.264</v>
       </c>
       <c r="G23">
         <v>455.2</v>
@@ -3316,28 +3316,28 @@
         <v>435.9</v>
       </c>
       <c r="M23">
-        <v>67.91408209838828</v>
+        <v>71.14808600783535</v>
       </c>
       <c r="N23">
-        <v>367.9859179016117</v>
+        <v>364.7519139921647</v>
       </c>
       <c r="O23">
-        <v>73.59718358032235</v>
+        <v>72.95038279843294</v>
       </c>
       <c r="P23">
-        <v>294.3887343212894</v>
+        <v>291.8015311937318</v>
       </c>
       <c r="Q23">
-        <v>513.4887343212894</v>
+        <v>510.9015311937317</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08218798007889228</v>
+        <v>0.08257755215831944</v>
       </c>
       <c r="T23">
-        <v>0.7481751694346487</v>
+        <v>0.7561851814193888</v>
       </c>
       <c r="U23">
         <v>0.05825774444168939</v>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.418403761513029</v>
+        <v>6.12665813598971</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3362,22 +3362,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0746638537052265</v>
+        <v>0.07479590208192424</v>
       </c>
       <c r="C24">
-        <v>4555.468715615774</v>
+        <v>4475.722265014596</v>
       </c>
       <c r="D24">
-        <v>5321.532715615775</v>
+        <v>5297.298265014596</v>
       </c>
       <c r="E24">
-        <v>-622.836</v>
+        <v>-567.3239999999998</v>
       </c>
       <c r="F24">
-        <v>1221.264</v>
+        <v>1276.776</v>
       </c>
       <c r="G24">
         <v>455.2</v>
@@ -3398,45 +3398,45 @@
         <v>435.9</v>
       </c>
       <c r="M24">
-        <v>71.14808600783535</v>
+        <v>75.65886591728241</v>
       </c>
       <c r="N24">
-        <v>364.7519139921647</v>
+        <v>360.2411340827176</v>
       </c>
       <c r="O24">
-        <v>72.95038279843294</v>
+        <v>72.04822681654353</v>
       </c>
       <c r="P24">
-        <v>291.8015311937318</v>
+        <v>288.1929072661741</v>
       </c>
       <c r="Q24">
-        <v>510.9015311937317</v>
+        <v>507.292907266174</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08257755215831944</v>
+        <v>0.08297724299305637</v>
       </c>
       <c r="T24">
-        <v>0.7561851814193888</v>
+        <v>0.7644032456634728</v>
       </c>
       <c r="U24">
-        <v>0.05825774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04660619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.12665813598971</v>
+        <v>5.761386913683957</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3444,22 +3444,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07479590208192424</v>
+        <v>0.07475195045862203</v>
       </c>
       <c r="C25">
-        <v>4475.722265014596</v>
+        <v>4428.252032639068</v>
       </c>
       <c r="D25">
-        <v>5297.298265014596</v>
+        <v>5305.340032639067</v>
       </c>
       <c r="E25">
-        <v>-567.3239999999998</v>
+        <v>-511.8119999999999</v>
       </c>
       <c r="F25">
-        <v>1276.776</v>
+        <v>1332.288</v>
       </c>
       <c r="G25">
         <v>455.2</v>
@@ -3480,28 +3480,28 @@
         <v>435.9</v>
       </c>
       <c r="M25">
-        <v>75.65886591728241</v>
+        <v>78.94838182672947</v>
       </c>
       <c r="N25">
-        <v>360.2411340827176</v>
+        <v>356.9516181732706</v>
       </c>
       <c r="O25">
-        <v>72.04822681654353</v>
+        <v>71.39032363465411</v>
       </c>
       <c r="P25">
-        <v>288.1929072661741</v>
+        <v>285.5612945386164</v>
       </c>
       <c r="Q25">
-        <v>507.292907266174</v>
+        <v>504.6612945386164</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08297724299305637</v>
+        <v>0.08338745200765481</v>
       </c>
       <c r="T25">
-        <v>0.7644032456634728</v>
+        <v>0.7728375747560854</v>
       </c>
       <c r="U25">
         <v>0.05925774444168939</v>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.761386913683957</v>
+        <v>5.521329125613792</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3526,22 +3526,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07475195045862201</v>
+        <v>0.07470799883531977</v>
       </c>
       <c r="C26">
-        <v>4428.25203263907</v>
+        <v>4380.806253615941</v>
       </c>
       <c r="D26">
-        <v>5305.340032639069</v>
+        <v>5313.406253615942</v>
       </c>
       <c r="E26">
-        <v>-511.8119999999999</v>
+        <v>-456.3</v>
       </c>
       <c r="F26">
-        <v>1332.288</v>
+        <v>1387.8</v>
       </c>
       <c r="G26">
         <v>455.2</v>
@@ -3562,28 +3562,28 @@
         <v>435.9</v>
       </c>
       <c r="M26">
-        <v>78.94838182672947</v>
+        <v>82.23789773617654</v>
       </c>
       <c r="N26">
-        <v>356.9516181732706</v>
+        <v>353.6621022638235</v>
       </c>
       <c r="O26">
-        <v>71.39032363465411</v>
+        <v>70.7324204527647</v>
       </c>
       <c r="P26">
-        <v>285.5612945386164</v>
+        <v>282.9296818110588</v>
       </c>
       <c r="Q26">
-        <v>504.6612945386164</v>
+        <v>502.0296818110588</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08338745200765479</v>
+        <v>0.0838085999293092</v>
       </c>
       <c r="T26">
-        <v>0.7728375747560853</v>
+        <v>0.7814968192911674</v>
       </c>
       <c r="U26">
         <v>0.05925774444168939</v>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.521329125613792</v>
+        <v>5.300475960589241</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3608,22 +3608,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07470799883531977</v>
+        <v>0.07466404721201754</v>
       </c>
       <c r="C27">
-        <v>4380.806253615941</v>
+        <v>4333.385039651429</v>
       </c>
       <c r="D27">
-        <v>5313.406253615942</v>
+        <v>5321.497039651429</v>
       </c>
       <c r="E27">
-        <v>-456.3</v>
+        <v>-400.788</v>
       </c>
       <c r="F27">
-        <v>1387.8</v>
+        <v>1443.312</v>
       </c>
       <c r="G27">
         <v>455.2</v>
@@ -3644,28 +3644,28 @@
         <v>435.9</v>
       </c>
       <c r="M27">
-        <v>82.23789773617654</v>
+        <v>85.52741364562358</v>
       </c>
       <c r="N27">
-        <v>353.6621022638235</v>
+        <v>350.3725863543764</v>
       </c>
       <c r="O27">
-        <v>70.7324204527647</v>
+        <v>70.07451727087529</v>
       </c>
       <c r="P27">
-        <v>282.9296818110588</v>
+        <v>280.2980690835012</v>
       </c>
       <c r="Q27">
-        <v>502.0296818110588</v>
+        <v>499.3980690835011</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0838085999293092</v>
+        <v>0.08424113022722453</v>
       </c>
       <c r="T27">
-        <v>0.7814968192911674</v>
+        <v>0.790390097462333</v>
       </c>
       <c r="U27">
         <v>0.05925774444168939</v>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.300475960589241</v>
+        <v>5.096611500566578</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3690,22 +3690,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07466404721201754</v>
+        <v>0.07462009558871531</v>
       </c>
       <c r="C28">
-        <v>4333.385039651429</v>
+        <v>4285.988503133176</v>
       </c>
       <c r="D28">
-        <v>5321.497039651429</v>
+        <v>5329.612503133177</v>
       </c>
       <c r="E28">
-        <v>-400.788</v>
+        <v>-345.2759999999998</v>
       </c>
       <c r="F28">
-        <v>1443.312</v>
+        <v>1498.824</v>
       </c>
       <c r="G28">
         <v>455.2</v>
@@ -3726,28 +3726,28 @@
         <v>435.9</v>
       </c>
       <c r="M28">
-        <v>85.52741364562358</v>
+        <v>88.81692955507066</v>
       </c>
       <c r="N28">
-        <v>350.3725863543764</v>
+        <v>347.0830704449294</v>
       </c>
       <c r="O28">
-        <v>70.07451727087529</v>
+        <v>69.41661408898588</v>
       </c>
       <c r="P28">
-        <v>280.2980690835012</v>
+        <v>277.6664563559435</v>
       </c>
       <c r="Q28">
-        <v>499.3980690835011</v>
+        <v>496.7664563559435</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08424113022722453</v>
+        <v>0.08468551067028822</v>
       </c>
       <c r="T28">
-        <v>0.790390097462333</v>
+        <v>0.7995270270902428</v>
       </c>
       <c r="U28">
         <v>0.05925774444168939</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.096611500566578</v>
+        <v>4.907848111656704</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3772,22 +3772,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07462009558871531</v>
+        <v>0.07457614396541307</v>
       </c>
       <c r="C29">
-        <v>4285.988503133176</v>
+        <v>4238.616757135456</v>
       </c>
       <c r="D29">
-        <v>5329.612503133177</v>
+        <v>5337.752757135457</v>
       </c>
       <c r="E29">
-        <v>-345.2759999999998</v>
+        <v>-289.7639999999999</v>
       </c>
       <c r="F29">
-        <v>1498.824</v>
+        <v>1554.336</v>
       </c>
       <c r="G29">
         <v>455.2</v>
@@ -3808,28 +3808,28 @@
         <v>435.9</v>
       </c>
       <c r="M29">
-        <v>88.81692955507066</v>
+        <v>92.10644546451772</v>
       </c>
       <c r="N29">
-        <v>347.0830704449294</v>
+        <v>343.7935545354823</v>
       </c>
       <c r="O29">
-        <v>69.41661408898588</v>
+        <v>68.75871090709647</v>
       </c>
       <c r="P29">
-        <v>277.6664563559435</v>
+        <v>275.0348436283858</v>
       </c>
       <c r="Q29">
-        <v>496.7664563559435</v>
+        <v>494.1348436283858</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08468551067028822</v>
+        <v>0.08514223501454812</v>
       </c>
       <c r="T29">
-        <v>0.7995270270902428</v>
+        <v>0.8089177603189278</v>
       </c>
       <c r="U29">
         <v>0.05925774444168939</v>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.907848111656704</v>
+        <v>4.732567821954679</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3854,22 +3854,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07457614396541307</v>
+        <v>0.07453219234211084</v>
       </c>
       <c r="C30">
-        <v>4238.616757135456</v>
+        <v>4191.269915424412</v>
       </c>
       <c r="D30">
-        <v>5337.752757135457</v>
+        <v>5345.917915424412</v>
       </c>
       <c r="E30">
-        <v>-289.7639999999999</v>
+        <v>-234.2519999999997</v>
       </c>
       <c r="F30">
-        <v>1554.336</v>
+        <v>1609.848</v>
       </c>
       <c r="G30">
         <v>455.2</v>
@@ -3890,28 +3890,28 @@
         <v>435.9</v>
       </c>
       <c r="M30">
-        <v>92.10644546451772</v>
+        <v>95.39596137396479</v>
       </c>
       <c r="N30">
-        <v>343.7935545354823</v>
+        <v>340.5040386260353</v>
       </c>
       <c r="O30">
-        <v>68.75871090709647</v>
+        <v>68.10080772520705</v>
       </c>
       <c r="P30">
-        <v>275.0348436283858</v>
+        <v>272.4032309008282</v>
       </c>
       <c r="Q30">
-        <v>494.1348436283858</v>
+        <v>491.5032309008282</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08514223501454812</v>
+        <v>0.08561182483329421</v>
       </c>
       <c r="T30">
-        <v>0.8089177603189278</v>
+        <v>0.8185730212441955</v>
       </c>
       <c r="U30">
         <v>0.05925774444168939</v>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.732567821954679</v>
+        <v>4.569375828094172</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3936,22 +3936,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07453219234211084</v>
+        <v>0.0750882407188086</v>
       </c>
       <c r="C31">
-        <v>4191.269915424412</v>
+        <v>4034.263632877007</v>
       </c>
       <c r="D31">
-        <v>5345.917915424412</v>
+        <v>5244.423632877007</v>
       </c>
       <c r="E31">
-        <v>-234.2520000000002</v>
+        <v>-178.74</v>
       </c>
       <c r="F31">
-        <v>1609.848</v>
+        <v>1665.36</v>
       </c>
       <c r="G31">
         <v>455.2</v>
@@ -3972,45 +3972,45 @@
         <v>435.9</v>
       </c>
       <c r="M31">
-        <v>95.39596137396477</v>
+        <v>102.8488772834118</v>
       </c>
       <c r="N31">
-        <v>340.5040386260353</v>
+        <v>333.0511227165882</v>
       </c>
       <c r="O31">
-        <v>68.10080772520705</v>
+        <v>66.61022454331764</v>
       </c>
       <c r="P31">
-        <v>272.4032309008282</v>
+        <v>266.4408981732706</v>
       </c>
       <c r="Q31">
-        <v>491.5032309008282</v>
+        <v>485.5408981732705</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08561182483329421</v>
+        <v>0.08609483150400449</v>
       </c>
       <c r="T31">
-        <v>0.8185730212441955</v>
+        <v>0.828504146767328</v>
       </c>
       <c r="U31">
-        <v>0.05925774444168939</v>
+        <v>0.06175774444168938</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.04740619555335152</v>
+        <v>0.04940619555335151</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.569375828094174</v>
+        <v>4.238257251937013</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4018,22 +4018,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0750882407188086</v>
+        <v>0.07506428909550636</v>
       </c>
       <c r="C32">
-        <v>4034.263632877007</v>
+        <v>3983.043979049573</v>
       </c>
       <c r="D32">
-        <v>5244.423632877007</v>
+        <v>5248.715979049573</v>
       </c>
       <c r="E32">
-        <v>-178.74</v>
+        <v>-123.2280000000001</v>
       </c>
       <c r="F32">
-        <v>1665.36</v>
+        <v>1720.872</v>
       </c>
       <c r="G32">
         <v>455.2</v>
@@ -4054,28 +4054,28 @@
         <v>435.9</v>
       </c>
       <c r="M32">
-        <v>102.8488772834118</v>
+        <v>106.2771731928589</v>
       </c>
       <c r="N32">
-        <v>333.0511227165882</v>
+        <v>329.6228268071412</v>
       </c>
       <c r="O32">
-        <v>66.61022454331764</v>
+        <v>65.92456536142824</v>
       </c>
       <c r="P32">
-        <v>266.4408981732706</v>
+        <v>263.6982614457129</v>
       </c>
       <c r="Q32">
-        <v>485.5408981732705</v>
+        <v>482.7982614457129</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08609483150400449</v>
+        <v>0.08659183836806869</v>
       </c>
       <c r="T32">
-        <v>0.828504146767328</v>
+        <v>0.8387231310012758</v>
       </c>
       <c r="U32">
         <v>0.06175774444168938</v>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.238257251937013</v>
+        <v>4.101539276068078</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4100,22 +4100,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07506428909550636</v>
+        <v>0.07593633747220412</v>
       </c>
       <c r="C33">
-        <v>3983.043979049573</v>
+        <v>3775.651072701899</v>
       </c>
       <c r="D33">
-        <v>5248.715979049573</v>
+        <v>5096.8350727019</v>
       </c>
       <c r="E33">
-        <v>-123.2280000000001</v>
+        <v>-67.71599999999989</v>
       </c>
       <c r="F33">
-        <v>1720.872</v>
+        <v>1776.384</v>
       </c>
       <c r="G33">
         <v>455.2</v>
@@ -4136,45 +4136,45 @@
         <v>435.9</v>
       </c>
       <c r="M33">
-        <v>106.2771731928589</v>
+        <v>115.922813102306</v>
       </c>
       <c r="N33">
-        <v>329.6228268071412</v>
+        <v>319.9771868976941</v>
       </c>
       <c r="O33">
-        <v>65.92456536142824</v>
+        <v>63.99543737953882</v>
       </c>
       <c r="P33">
-        <v>263.6982614457129</v>
+        <v>255.9817495181553</v>
       </c>
       <c r="Q33">
-        <v>482.7982614457129</v>
+        <v>475.0817495181552</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08659183836806869</v>
+        <v>0.08710346308107594</v>
       </c>
       <c r="T33">
-        <v>0.8387231310012758</v>
+        <v>0.8492426735950458</v>
       </c>
       <c r="U33">
-        <v>0.06175774444168938</v>
+        <v>0.06525774444168939</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.04940619555335151</v>
+        <v>0.05220619555335151</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.101539276068078</v>
+        <v>3.760260714302222</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4182,22 +4182,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07593633747220412</v>
+        <v>0.07594038584890188</v>
       </c>
       <c r="C34">
-        <v>3775.651072701899</v>
+        <v>3719.454479331261</v>
       </c>
       <c r="D34">
-        <v>5096.8350727019</v>
+        <v>5096.150479331261</v>
       </c>
       <c r="E34">
-        <v>-67.71599999999989</v>
+        <v>-12.20399999999995</v>
       </c>
       <c r="F34">
-        <v>1776.384</v>
+        <v>1831.896</v>
       </c>
       <c r="G34">
         <v>455.2</v>
@@ -4218,28 +4218,28 @@
         <v>435.9</v>
       </c>
       <c r="M34">
-        <v>115.922813102306</v>
+        <v>119.545401011753</v>
       </c>
       <c r="N34">
-        <v>319.9771868976941</v>
+        <v>316.354598988247</v>
       </c>
       <c r="O34">
-        <v>63.99543737953882</v>
+        <v>63.27091979764941</v>
       </c>
       <c r="P34">
-        <v>255.9817495181553</v>
+        <v>253.0836791905976</v>
       </c>
       <c r="Q34">
-        <v>475.0817495181552</v>
+        <v>472.1836791905976</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08710346308107594</v>
+        <v>0.08763036017357595</v>
       </c>
       <c r="T34">
-        <v>0.8492426735950458</v>
+        <v>0.8600762323856447</v>
       </c>
       <c r="U34">
         <v>0.06525774444168939</v>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.760260714302222</v>
+        <v>3.646313419929428</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4264,22 +4264,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07594038584890188</v>
+        <v>0.07594443422559966</v>
       </c>
       <c r="C35">
-        <v>3719.454479331261</v>
+        <v>3663.258069841451</v>
       </c>
       <c r="D35">
-        <v>5096.150479331261</v>
+        <v>5095.466069841452</v>
       </c>
       <c r="E35">
-        <v>-12.20399999999995</v>
+        <v>43.30800000000022</v>
       </c>
       <c r="F35">
-        <v>1831.896</v>
+        <v>1887.408</v>
       </c>
       <c r="G35">
         <v>455.2</v>
@@ -4300,28 +4300,28 @@
         <v>435.9</v>
       </c>
       <c r="M35">
-        <v>119.545401011753</v>
+        <v>123.1679889212001</v>
       </c>
       <c r="N35">
-        <v>316.354598988247</v>
+        <v>312.7320110787999</v>
       </c>
       <c r="O35">
-        <v>63.27091979764941</v>
+        <v>62.54640221575999</v>
       </c>
       <c r="P35">
-        <v>253.0836791905976</v>
+        <v>250.1856088630399</v>
       </c>
       <c r="Q35">
-        <v>472.1836791905976</v>
+        <v>469.2856088630399</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08763036017357595</v>
+        <v>0.08817322384463658</v>
       </c>
       <c r="T35">
-        <v>0.8600762323856447</v>
+        <v>0.8712380808365647</v>
       </c>
       <c r="U35">
         <v>0.06525774444168939</v>
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.646313419929428</v>
+        <v>3.539068907578562</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4346,22 +4346,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07594443422559966</v>
+        <v>0.07673248260229741</v>
       </c>
       <c r="C36">
-        <v>3663.258069841451</v>
+        <v>3477.931925387401</v>
       </c>
       <c r="D36">
-        <v>5095.466069841452</v>
+        <v>4965.651925387401</v>
       </c>
       <c r="E36">
-        <v>43.30800000000022</v>
+        <v>98.82000000000016</v>
       </c>
       <c r="F36">
-        <v>1887.408</v>
+        <v>1942.92</v>
       </c>
       <c r="G36">
         <v>455.2</v>
@@ -4382,45 +4382,45 @@
         <v>435.9</v>
       </c>
       <c r="M36">
-        <v>123.1679889212001</v>
+        <v>132.2307528306471</v>
       </c>
       <c r="N36">
-        <v>312.7320110787999</v>
+        <v>303.6692471693529</v>
       </c>
       <c r="O36">
-        <v>62.54640221575999</v>
+        <v>60.73384943387058</v>
       </c>
       <c r="P36">
-        <v>250.1856088630399</v>
+        <v>242.9353977354823</v>
       </c>
       <c r="Q36">
-        <v>469.2856088630399</v>
+        <v>462.0353977354823</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08817322384463658</v>
+        <v>0.08873279101326828</v>
       </c>
       <c r="T36">
-        <v>0.8712380808365647</v>
+        <v>0.8827433707782824</v>
       </c>
       <c r="U36">
-        <v>0.06525774444168939</v>
+        <v>0.06805774444168938</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.05220619555335151</v>
+        <v>0.05444619555335151</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.539068907578562</v>
+        <v>3.296510007458503</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4428,22 +4428,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07673248260229741</v>
+        <v>0.07675893097899517</v>
       </c>
       <c r="C37">
-        <v>3477.931925387401</v>
+        <v>3418.177742969614</v>
       </c>
       <c r="D37">
-        <v>4965.651925387401</v>
+        <v>4961.409742969614</v>
       </c>
       <c r="E37">
-        <v>98.82000000000016</v>
+        <v>154.3320000000003</v>
       </c>
       <c r="F37">
-        <v>1942.92</v>
+        <v>1998.432</v>
       </c>
       <c r="G37">
         <v>455.2</v>
@@ -4464,28 +4464,28 @@
         <v>435.9</v>
       </c>
       <c r="M37">
-        <v>132.2307528306471</v>
+        <v>136.0087743400942</v>
       </c>
       <c r="N37">
-        <v>303.6692471693529</v>
+        <v>299.8912256599058</v>
       </c>
       <c r="O37">
-        <v>60.73384943387058</v>
+        <v>59.97824513198116</v>
       </c>
       <c r="P37">
-        <v>242.9353977354823</v>
+        <v>239.9129805279246</v>
       </c>
       <c r="Q37">
-        <v>462.0353977354823</v>
+        <v>459.0129805279246</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08873279101326828</v>
+        <v>0.08930984465591975</v>
       </c>
       <c r="T37">
-        <v>0.8827433707782824</v>
+        <v>0.8946082010306787</v>
       </c>
       <c r="U37">
         <v>0.06805774444168938</v>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.296510007458503</v>
+        <v>3.204940285029099</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4510,22 +4510,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07675893097899517</v>
+        <v>0.07678537935569293</v>
       </c>
       <c r="C38">
-        <v>3418.177742969614</v>
+        <v>3358.430802602168</v>
       </c>
       <c r="D38">
-        <v>4961.409742969614</v>
+        <v>4957.174802602168</v>
       </c>
       <c r="E38">
-        <v>154.3319999999999</v>
+        <v>209.8440000000001</v>
       </c>
       <c r="F38">
-        <v>1998.432</v>
+        <v>2053.944</v>
       </c>
       <c r="G38">
         <v>455.2</v>
@@ -4546,28 +4546,28 @@
         <v>435.9</v>
       </c>
       <c r="M38">
-        <v>136.0087743400942</v>
+        <v>139.7867958495412</v>
       </c>
       <c r="N38">
-        <v>299.8912256599058</v>
+        <v>296.1132041504588</v>
       </c>
       <c r="O38">
-        <v>59.97824513198117</v>
+        <v>59.22264083009176</v>
       </c>
       <c r="P38">
-        <v>239.9129805279247</v>
+        <v>236.890563320367</v>
       </c>
       <c r="Q38">
-        <v>459.0129805279246</v>
+        <v>455.990563320367</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08930984465591973</v>
+        <v>0.08990521746182997</v>
       </c>
       <c r="T38">
-        <v>0.8946082010306785</v>
+        <v>0.9068496925609287</v>
       </c>
       <c r="U38">
         <v>0.06805774444168938</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.2049402850291</v>
+        <v>3.118320277325611</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4592,22 +4592,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07678537935569293</v>
+        <v>0.0768118277323907</v>
       </c>
       <c r="C39">
-        <v>3358.430802602168</v>
+        <v>3298.691085755961</v>
       </c>
       <c r="D39">
-        <v>4957.174802602168</v>
+        <v>4952.947085755961</v>
       </c>
       <c r="E39">
-        <v>209.8440000000001</v>
+        <v>265.3560000000002</v>
       </c>
       <c r="F39">
-        <v>2053.944</v>
+        <v>2109.456</v>
       </c>
       <c r="G39">
         <v>455.2</v>
@@ -4628,28 +4628,28 @@
         <v>435.9</v>
       </c>
       <c r="M39">
-        <v>139.7867958495412</v>
+        <v>143.5648173589883</v>
       </c>
       <c r="N39">
-        <v>296.1132041504588</v>
+        <v>292.3351826410117</v>
       </c>
       <c r="O39">
-        <v>59.22264083009176</v>
+        <v>58.46703652820234</v>
       </c>
       <c r="P39">
-        <v>236.890563320367</v>
+        <v>233.8681461128093</v>
       </c>
       <c r="Q39">
-        <v>455.990563320367</v>
+        <v>452.9681461128093</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08990521746182997</v>
+        <v>0.09051979584212441</v>
       </c>
       <c r="T39">
-        <v>0.9068496925609287</v>
+        <v>0.9194860709147352</v>
       </c>
       <c r="U39">
         <v>0.06805774444168938</v>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.118320277325611</v>
+        <v>3.036259217395989</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4674,22 +4674,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0768118277323907</v>
+        <v>0.07927187610908847</v>
       </c>
       <c r="C40">
-        <v>3298.691085755961</v>
+        <v>2879.157379937223</v>
       </c>
       <c r="D40">
-        <v>4952.947085755961</v>
+        <v>4588.925379937223</v>
       </c>
       <c r="E40">
-        <v>265.3560000000002</v>
+        <v>320.8679999999999</v>
       </c>
       <c r="F40">
-        <v>2109.456</v>
+        <v>2164.968</v>
       </c>
       <c r="G40">
         <v>455.2</v>
@@ -4710,45 +4710,45 @@
         <v>435.9</v>
       </c>
       <c r="M40">
-        <v>143.5648173589883</v>
+        <v>164.2295892684354</v>
       </c>
       <c r="N40">
-        <v>292.3351826410117</v>
+        <v>271.6704107315646</v>
       </c>
       <c r="O40">
-        <v>58.46703652820234</v>
+        <v>54.33408214631293</v>
       </c>
       <c r="P40">
-        <v>233.8681461128093</v>
+        <v>217.3363285852517</v>
       </c>
       <c r="Q40">
-        <v>452.9681461128093</v>
+        <v>436.4363285852517</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09051979584212441</v>
+        <v>0.09115452433324817</v>
       </c>
       <c r="T40">
-        <v>0.9194860709147352</v>
+        <v>0.9325367567555519</v>
       </c>
       <c r="U40">
-        <v>0.06805774444168938</v>
+        <v>0.07585774444168938</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.05444619555335151</v>
+        <v>0.06068619555335151</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.036259217395989</v>
+        <v>2.654211107399872</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4756,22 +4756,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07927187610908847</v>
+        <v>0.07936072448578624</v>
       </c>
       <c r="C41">
-        <v>2879.157379937223</v>
+        <v>2811.496697897676</v>
       </c>
       <c r="D41">
-        <v>4588.925379937223</v>
+        <v>4576.776697897676</v>
       </c>
       <c r="E41">
-        <v>320.8679999999999</v>
+        <v>376.3800000000001</v>
       </c>
       <c r="F41">
-        <v>2164.968</v>
+        <v>2220.48</v>
       </c>
       <c r="G41">
         <v>455.2</v>
@@ -4792,28 +4792,28 @@
         <v>435.9</v>
       </c>
       <c r="M41">
-        <v>164.2295892684354</v>
+        <v>168.4406043778824</v>
       </c>
       <c r="N41">
-        <v>271.6704107315646</v>
+        <v>267.4593956221176</v>
       </c>
       <c r="O41">
-        <v>54.33408214631293</v>
+        <v>53.49187912442352</v>
       </c>
       <c r="P41">
-        <v>217.3363285852517</v>
+        <v>213.9675164976941</v>
       </c>
       <c r="Q41">
-        <v>436.4363285852517</v>
+        <v>433.067516497694</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09115452433324817</v>
+        <v>0.09181041044074273</v>
       </c>
       <c r="T41">
-        <v>0.9325367567555519</v>
+        <v>0.9460224654577292</v>
       </c>
       <c r="U41">
         <v>0.07585774444168938</v>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.654211107399872</v>
+        <v>2.587855829714876</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4838,22 +4838,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07936072448578624</v>
+        <v>0.079449572862484</v>
       </c>
       <c r="C42">
-        <v>2811.496697897676</v>
+        <v>2743.900170650387</v>
       </c>
       <c r="D42">
-        <v>4576.776697897676</v>
+        <v>4564.692170650387</v>
       </c>
       <c r="E42">
-        <v>376.3800000000001</v>
+        <v>431.8920000000003</v>
       </c>
       <c r="F42">
-        <v>2220.48</v>
+        <v>2275.992</v>
       </c>
       <c r="G42">
         <v>455.2</v>
@@ -4874,28 +4874,28 @@
         <v>435.9</v>
       </c>
       <c r="M42">
-        <v>168.4406043778824</v>
+        <v>172.6516194873295</v>
       </c>
       <c r="N42">
-        <v>267.4593956221176</v>
+        <v>263.2483805126705</v>
       </c>
       <c r="O42">
-        <v>53.49187912442352</v>
+        <v>52.6496761025341</v>
       </c>
       <c r="P42">
-        <v>213.9675164976941</v>
+        <v>210.5987044101364</v>
       </c>
       <c r="Q42">
-        <v>433.067516497694</v>
+        <v>429.6987044101364</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09181041044074273</v>
+        <v>0.09248852997560997</v>
       </c>
       <c r="T42">
-        <v>0.9460224654577292</v>
+        <v>0.9599653168277767</v>
       </c>
       <c r="U42">
         <v>0.07585774444168938</v>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.587855829714876</v>
+        <v>2.524737394843781</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4920,22 +4920,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.079449572862484</v>
+        <v>0.08084882123918177</v>
       </c>
       <c r="C43">
-        <v>2743.900170650387</v>
+        <v>2506.152709254404</v>
       </c>
       <c r="D43">
-        <v>4564.692170650387</v>
+        <v>4382.456709254405</v>
       </c>
       <c r="E43">
-        <v>431.8920000000003</v>
+        <v>487.4040000000005</v>
       </c>
       <c r="F43">
-        <v>2275.992</v>
+        <v>2331.504</v>
       </c>
       <c r="G43">
         <v>455.2</v>
@@ -4956,45 +4956,45 @@
         <v>435.9</v>
       </c>
       <c r="M43">
-        <v>172.6516194873295</v>
+        <v>185.9555001967766</v>
       </c>
       <c r="N43">
-        <v>263.2483805126705</v>
+        <v>249.9444998032234</v>
       </c>
       <c r="O43">
-        <v>52.6496761025341</v>
+        <v>49.98889996064469</v>
       </c>
       <c r="P43">
-        <v>210.5987044101364</v>
+        <v>199.9555998425787</v>
       </c>
       <c r="Q43">
-        <v>429.6987044101364</v>
+        <v>419.0555998425787</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09248852997560997</v>
+        <v>0.09319003294271402</v>
       </c>
       <c r="T43">
-        <v>0.9599653168277767</v>
+        <v>0.9743889561761019</v>
       </c>
       <c r="U43">
-        <v>0.07585774444168938</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.06068619555335151</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.524737394843781</v>
+        <v>2.344109206443123</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5002,22 +5002,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08084882123918176</v>
+        <v>0.08096886961587953</v>
       </c>
       <c r="C44">
-        <v>2506.152709254407</v>
+        <v>2435.681263027089</v>
       </c>
       <c r="D44">
-        <v>4382.456709254407</v>
+        <v>4367.49726302709</v>
       </c>
       <c r="E44">
-        <v>487.404</v>
+        <v>542.9160000000002</v>
       </c>
       <c r="F44">
-        <v>2331.504</v>
+        <v>2387.016</v>
       </c>
       <c r="G44">
         <v>455.2</v>
@@ -5038,28 +5038,28 @@
         <v>435.9</v>
       </c>
       <c r="M44">
-        <v>185.9555001967766</v>
+        <v>190.3830121062236</v>
       </c>
       <c r="N44">
-        <v>249.9444998032235</v>
+        <v>245.5169878937764</v>
       </c>
       <c r="O44">
-        <v>49.98889996064469</v>
+        <v>49.10339757875528</v>
       </c>
       <c r="P44">
-        <v>199.9555998425788</v>
+        <v>196.4135903150211</v>
       </c>
       <c r="Q44">
-        <v>419.0555998425788</v>
+        <v>415.5135903150211</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.093190032942714</v>
+        <v>0.09391615004901468</v>
       </c>
       <c r="T44">
-        <v>0.9743889561761017</v>
+        <v>0.9893186881331401</v>
       </c>
       <c r="U44">
         <v>0.07975774444168938</v>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.344109206443123</v>
+        <v>2.289595038851423</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5084,22 +5084,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08096886961587953</v>
+        <v>0.08108891799257729</v>
       </c>
       <c r="C45">
-        <v>2435.681263027089</v>
+        <v>2365.311597037767</v>
       </c>
       <c r="D45">
-        <v>4367.49726302709</v>
+        <v>4352.639597037767</v>
       </c>
       <c r="E45">
-        <v>542.9160000000002</v>
+        <v>598.4279999999999</v>
       </c>
       <c r="F45">
-        <v>2387.016</v>
+        <v>2442.528</v>
       </c>
       <c r="G45">
         <v>455.2</v>
@@ -5120,28 +5120,28 @@
         <v>435.9</v>
       </c>
       <c r="M45">
-        <v>190.3830121062236</v>
+        <v>194.8105240156707</v>
       </c>
       <c r="N45">
-        <v>245.5169878937764</v>
+        <v>241.0894759843294</v>
       </c>
       <c r="O45">
-        <v>49.10339757875528</v>
+        <v>48.21789519686588</v>
       </c>
       <c r="P45">
-        <v>196.4135903150211</v>
+        <v>192.8715807874635</v>
       </c>
       <c r="Q45">
-        <v>415.5135903150211</v>
+        <v>411.9715807874635</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09391615004901468</v>
+        <v>0.09466819990911182</v>
       </c>
       <c r="T45">
-        <v>0.9893186881331401</v>
+        <v>1.00478162480293</v>
       </c>
       <c r="U45">
         <v>0.07975774444168938</v>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.289595038851423</v>
+        <v>2.237558787968436</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5166,22 +5166,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08108891799257729</v>
+        <v>0.08120896636927505</v>
       </c>
       <c r="C46">
-        <v>2365.311597037767</v>
+        <v>2295.042676078104</v>
       </c>
       <c r="D46">
-        <v>4352.639597037767</v>
+        <v>4337.882676078104</v>
       </c>
       <c r="E46">
-        <v>598.4279999999999</v>
+        <v>653.9400000000001</v>
       </c>
       <c r="F46">
-        <v>2442.528</v>
+        <v>2498.04</v>
       </c>
       <c r="G46">
         <v>455.2</v>
@@ -5202,28 +5202,28 @@
         <v>435.9</v>
       </c>
       <c r="M46">
-        <v>194.8105240156707</v>
+        <v>199.2380359251177</v>
       </c>
       <c r="N46">
-        <v>241.0894759843294</v>
+        <v>236.6619640748823</v>
       </c>
       <c r="O46">
-        <v>48.21789519686588</v>
+        <v>47.33239281497646</v>
       </c>
       <c r="P46">
-        <v>192.8715807874635</v>
+        <v>189.3295712599058</v>
       </c>
       <c r="Q46">
-        <v>411.9715807874635</v>
+        <v>408.4295712599058</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09466819990911182</v>
+        <v>0.09544759703684885</v>
       </c>
       <c r="T46">
-        <v>1.00478162480293</v>
+        <v>1.020806850078893</v>
       </c>
       <c r="U46">
         <v>0.07975774444168938</v>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.237558787968436</v>
+        <v>2.187835259346915</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5248,22 +5248,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08120896636927505</v>
+        <v>0.08132901474597282</v>
       </c>
       <c r="C47">
-        <v>2295.042676078104</v>
+        <v>2224.873478931155</v>
       </c>
       <c r="D47">
-        <v>4337.882676078104</v>
+        <v>4323.225478931156</v>
       </c>
       <c r="E47">
-        <v>653.9400000000001</v>
+        <v>709.4520000000002</v>
       </c>
       <c r="F47">
-        <v>2498.04</v>
+        <v>2553.552</v>
       </c>
       <c r="G47">
         <v>455.2</v>
@@ -5284,28 +5284,28 @@
         <v>435.9</v>
       </c>
       <c r="M47">
-        <v>199.2380359251177</v>
+        <v>203.6655478345648</v>
       </c>
       <c r="N47">
-        <v>236.6619640748823</v>
+        <v>232.2344521654352</v>
       </c>
       <c r="O47">
-        <v>47.33239281497646</v>
+        <v>46.44689043308705</v>
       </c>
       <c r="P47">
-        <v>189.3295712599058</v>
+        <v>185.7875617323482</v>
       </c>
       <c r="Q47">
-        <v>408.4295712599058</v>
+        <v>404.8875617323481</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09544759703684885</v>
+        <v>0.09625586072487244</v>
       </c>
       <c r="T47">
-        <v>1.020806850078893</v>
+        <v>1.03742560221693</v>
       </c>
       <c r="U47">
         <v>0.07975774444168938</v>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.187835259346915</v>
+        <v>2.140273623274156</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5330,22 +5330,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08132901474597282</v>
+        <v>0.08144906312267058</v>
       </c>
       <c r="C48">
-        <v>2224.873478931155</v>
+        <v>2154.802998135792</v>
       </c>
       <c r="D48">
-        <v>4323.225478931156</v>
+        <v>4308.666998135792</v>
       </c>
       <c r="E48">
-        <v>709.4520000000002</v>
+        <v>764.9639999999999</v>
       </c>
       <c r="F48">
-        <v>2553.552</v>
+        <v>2609.064</v>
       </c>
       <c r="G48">
         <v>455.2</v>
@@ -5366,28 +5366,28 @@
         <v>435.9</v>
       </c>
       <c r="M48">
-        <v>203.6655478345648</v>
+        <v>208.0930597440119</v>
       </c>
       <c r="N48">
-        <v>232.2344521654352</v>
+        <v>227.8069402559882</v>
       </c>
       <c r="O48">
-        <v>46.44689043308705</v>
+        <v>45.56138805119764</v>
       </c>
       <c r="P48">
-        <v>185.7875617323482</v>
+        <v>182.2455522047905</v>
       </c>
       <c r="Q48">
-        <v>404.8875617323481</v>
+        <v>401.3455522047905</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09625586072487244</v>
+        <v>0.09709462492942522</v>
       </c>
       <c r="T48">
-        <v>1.03742560221693</v>
+        <v>1.054671477077157</v>
       </c>
       <c r="U48">
         <v>0.07975774444168938</v>
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.140273623274156</v>
+        <v>2.094735886608749</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5412,22 +5412,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08144906312267058</v>
+        <v>0.08156911149936835</v>
       </c>
       <c r="C49">
-        <v>2154.802998135792</v>
+        <v>2084.830239755854</v>
       </c>
       <c r="D49">
-        <v>4308.666998135792</v>
+        <v>4294.206239755854</v>
       </c>
       <c r="E49">
-        <v>764.9639999999999</v>
+        <v>820.4760000000001</v>
       </c>
       <c r="F49">
-        <v>2609.064</v>
+        <v>2664.576</v>
       </c>
       <c r="G49">
         <v>455.2</v>
@@ -5448,28 +5448,28 @@
         <v>435.9</v>
       </c>
       <c r="M49">
-        <v>208.0930597440119</v>
+        <v>212.5205716534589</v>
       </c>
       <c r="N49">
-        <v>227.8069402559882</v>
+        <v>223.3794283465411</v>
       </c>
       <c r="O49">
-        <v>45.56138805119764</v>
+        <v>44.67588566930822</v>
       </c>
       <c r="P49">
-        <v>182.2455522047905</v>
+        <v>178.7035426772329</v>
       </c>
       <c r="Q49">
-        <v>401.3455522047905</v>
+        <v>397.8035426772328</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09709462492942522</v>
+        <v>0.09796564929569157</v>
       </c>
       <c r="T49">
-        <v>1.054671477077157</v>
+        <v>1.072580654816623</v>
       </c>
       <c r="U49">
         <v>0.07975774444168938</v>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.094735886608749</v>
+        <v>2.051095555637733</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5494,22 +5494,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08156911149936835</v>
+        <v>0.08168915987606611</v>
       </c>
       <c r="C50">
-        <v>2084.830239755854</v>
+        <v>2014.954223153954</v>
       </c>
       <c r="D50">
-        <v>4294.206239755854</v>
+        <v>4279.842223153953</v>
       </c>
       <c r="E50">
-        <v>820.4760000000001</v>
+        <v>875.9879999999998</v>
       </c>
       <c r="F50">
-        <v>2664.576</v>
+        <v>2720.088</v>
       </c>
       <c r="G50">
         <v>455.2</v>
@@ -5530,28 +5530,28 @@
         <v>435.9</v>
       </c>
       <c r="M50">
-        <v>212.5205716534589</v>
+        <v>216.948083562906</v>
       </c>
       <c r="N50">
-        <v>223.3794283465411</v>
+        <v>218.9519164370941</v>
       </c>
       <c r="O50">
-        <v>44.67588566930822</v>
+        <v>43.79038328741882</v>
       </c>
       <c r="P50">
-        <v>178.7035426772329</v>
+        <v>175.1615331496753</v>
       </c>
       <c r="Q50">
-        <v>397.8035426772328</v>
+        <v>394.2615331496752</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09796564929569157</v>
+        <v>0.09887083148024287</v>
       </c>
       <c r="T50">
-        <v>1.072580654816623</v>
+        <v>1.091192153251754</v>
       </c>
       <c r="U50">
         <v>0.07975774444168938</v>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.051095555637733</v>
+        <v>2.009236462665535</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5576,22 +5576,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08168915987606611</v>
+        <v>0.08748920825276388</v>
       </c>
       <c r="C51">
-        <v>2014.954223153954</v>
+        <v>1364.005346818435</v>
       </c>
       <c r="D51">
-        <v>4279.842223153953</v>
+        <v>3684.405346818434</v>
       </c>
       <c r="E51">
-        <v>875.9879999999998</v>
+        <v>931.5</v>
       </c>
       <c r="F51">
-        <v>2720.088</v>
+        <v>2775.6</v>
       </c>
       <c r="G51">
         <v>455.2</v>
@@ -5612,45 +5612,45 @@
         <v>435.9</v>
       </c>
       <c r="M51">
-        <v>216.948083562906</v>
+        <v>260.789115472353</v>
       </c>
       <c r="N51">
-        <v>218.9519164370941</v>
+        <v>175.110884527647</v>
       </c>
       <c r="O51">
-        <v>43.79038328741882</v>
+        <v>35.0221769055294</v>
       </c>
       <c r="P51">
-        <v>175.1615331496753</v>
+        <v>140.0887076221176</v>
       </c>
       <c r="Q51">
-        <v>394.2615331496752</v>
+        <v>359.1887076221176</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09887083148024287</v>
+        <v>0.09981222095217623</v>
       </c>
       <c r="T51">
-        <v>1.091192153251754</v>
+        <v>1.110548111624291</v>
       </c>
       <c r="U51">
-        <v>0.07975774444168938</v>
+        <v>0.09395774444168939</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.06380619555335151</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.009236462665535</v>
+        <v>1.671465464386726</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5658,22 +5658,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08748920825276388</v>
+        <v>0.08772285662946164</v>
       </c>
       <c r="C52">
-        <v>1364.005346818435</v>
+        <v>1287.959075120553</v>
       </c>
       <c r="D52">
-        <v>3684.405346818434</v>
+        <v>3663.871075120554</v>
       </c>
       <c r="E52">
-        <v>931.5</v>
+        <v>987.0120000000002</v>
       </c>
       <c r="F52">
-        <v>2775.6</v>
+        <v>2831.112</v>
       </c>
       <c r="G52">
         <v>455.2</v>
@@ -5694,28 +5694,28 @@
         <v>435.9</v>
       </c>
       <c r="M52">
-        <v>260.789115472353</v>
+        <v>266.0048977818001</v>
       </c>
       <c r="N52">
-        <v>175.110884527647</v>
+        <v>169.8951022181999</v>
       </c>
       <c r="O52">
-        <v>35.0221769055294</v>
+        <v>33.97902044363998</v>
       </c>
       <c r="P52">
-        <v>140.0887076221176</v>
+        <v>135.9160817745599</v>
       </c>
       <c r="Q52">
-        <v>359.1887076221176</v>
+        <v>355.0160817745599</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09981222095217623</v>
+        <v>0.1007920344841885</v>
       </c>
       <c r="T52">
-        <v>1.110548111624291</v>
+        <v>1.130694109114074</v>
       </c>
       <c r="U52">
         <v>0.09395774444168939</v>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.671465464386726</v>
+        <v>1.638691631751692</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5740,22 +5740,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08772285662946164</v>
+        <v>0.08795650500615941</v>
       </c>
       <c r="C53">
-        <v>1287.959075120553</v>
+        <v>1212.140421876724</v>
       </c>
       <c r="D53">
-        <v>3663.871075120554</v>
+        <v>3643.564421876724</v>
       </c>
       <c r="E53">
-        <v>987.0120000000002</v>
+        <v>1042.524</v>
       </c>
       <c r="F53">
-        <v>2831.112</v>
+        <v>2886.624</v>
       </c>
       <c r="G53">
         <v>455.2</v>
@@ -5776,28 +5776,28 @@
         <v>435.9</v>
       </c>
       <c r="M53">
-        <v>266.0048977818001</v>
+        <v>271.2206800912472</v>
       </c>
       <c r="N53">
-        <v>169.8951022181999</v>
+        <v>164.6793199087529</v>
       </c>
       <c r="O53">
-        <v>33.97902044363998</v>
+        <v>32.93586398175057</v>
       </c>
       <c r="P53">
-        <v>135.9160817745599</v>
+        <v>131.7434559270023</v>
       </c>
       <c r="Q53">
-        <v>355.0160817745599</v>
+        <v>350.8434559270023</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1007920344841885</v>
+        <v>0.1018126735800346</v>
       </c>
       <c r="T53">
-        <v>1.130694109114074</v>
+        <v>1.151679523165931</v>
       </c>
       <c r="U53">
         <v>0.09395774444168939</v>
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.638691631751692</v>
+        <v>1.607178331141082</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5822,22 +5822,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08795650500615941</v>
+        <v>0.08819015338285717</v>
       </c>
       <c r="C54">
-        <v>1212.140421876724</v>
+        <v>1136.545623287241</v>
       </c>
       <c r="D54">
-        <v>3643.564421876724</v>
+        <v>3623.481623287241</v>
       </c>
       <c r="E54">
-        <v>1042.524</v>
+        <v>1098.036</v>
       </c>
       <c r="F54">
-        <v>2886.624</v>
+        <v>2942.136</v>
       </c>
       <c r="G54">
         <v>455.2</v>
@@ -5858,28 +5858,28 @@
         <v>435.9</v>
       </c>
       <c r="M54">
-        <v>271.2206800912472</v>
+        <v>276.4364624006943</v>
       </c>
       <c r="N54">
-        <v>164.6793199087529</v>
+        <v>159.4635375993058</v>
       </c>
       <c r="O54">
-        <v>32.93586398175057</v>
+        <v>31.89270751986115</v>
       </c>
       <c r="P54">
-        <v>131.7434559270023</v>
+        <v>127.5708300794446</v>
       </c>
       <c r="Q54">
-        <v>350.8434559270023</v>
+        <v>346.6708300794446</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1018126735800346</v>
+        <v>0.1028767441267678</v>
       </c>
       <c r="T54">
-        <v>1.151679523165931</v>
+        <v>1.173557933560421</v>
       </c>
       <c r="U54">
         <v>0.09395774444168939</v>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.607178331141082</v>
+        <v>1.57685421168559</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5904,22 +5904,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08819015338285717</v>
+        <v>0.08842380175955494</v>
       </c>
       <c r="C55">
-        <v>1136.545623287241</v>
+        <v>1061.170998079589</v>
       </c>
       <c r="D55">
-        <v>3623.481623287241</v>
+        <v>3603.61899807959</v>
       </c>
       <c r="E55">
-        <v>1098.036</v>
+        <v>1153.548</v>
       </c>
       <c r="F55">
-        <v>2942.136</v>
+        <v>2997.648</v>
       </c>
       <c r="G55">
         <v>455.2</v>
@@ -5940,28 +5940,28 @@
         <v>435.9</v>
       </c>
       <c r="M55">
-        <v>276.4364624006943</v>
+        <v>281.6522447101413</v>
       </c>
       <c r="N55">
-        <v>159.4635375993058</v>
+        <v>154.2477552898587</v>
       </c>
       <c r="O55">
-        <v>31.89270751986115</v>
+        <v>30.84955105797175</v>
       </c>
       <c r="P55">
-        <v>127.5708300794446</v>
+        <v>123.398204231887</v>
       </c>
       <c r="Q55">
-        <v>346.6708300794446</v>
+        <v>342.4982042318869</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1028767441267678</v>
+        <v>0.1039870786103155</v>
       </c>
       <c r="T55">
-        <v>1.173557933560421</v>
+        <v>1.196387579189453</v>
       </c>
       <c r="U55">
         <v>0.09395774444168939</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.57685421168559</v>
+        <v>1.547653207765487</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5986,22 +5986,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08842380175955494</v>
+        <v>0.0886574501362527</v>
       </c>
       <c r="C56">
-        <v>1061.170998079589</v>
+        <v>986.0129452588617</v>
       </c>
       <c r="D56">
-        <v>3603.61899807959</v>
+        <v>3583.972945258862</v>
       </c>
       <c r="E56">
-        <v>1153.548</v>
+        <v>1209.06</v>
       </c>
       <c r="F56">
-        <v>2997.648</v>
+        <v>3053.16</v>
       </c>
       <c r="G56">
         <v>455.2</v>
@@ -6022,28 +6022,28 @@
         <v>435.9</v>
       </c>
       <c r="M56">
-        <v>281.6522447101413</v>
+        <v>286.8680270195884</v>
       </c>
       <c r="N56">
-        <v>154.2477552898587</v>
+        <v>149.0319729804116</v>
       </c>
       <c r="O56">
-        <v>30.84955105797175</v>
+        <v>29.80639459608233</v>
       </c>
       <c r="P56">
-        <v>123.398204231887</v>
+        <v>119.2255783843293</v>
       </c>
       <c r="Q56">
-        <v>342.4982042318869</v>
+        <v>338.3255783843293</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1039870786103155</v>
+        <v>0.1051467612931319</v>
       </c>
       <c r="T56">
-        <v>1.196387579189453</v>
+        <v>1.220231875735332</v>
       </c>
       <c r="U56">
         <v>0.09395774444168939</v>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.547653207765487</v>
+        <v>1.519514058533387</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6068,22 +6068,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0886574501362527</v>
+        <v>0.1157525511729299</v>
       </c>
       <c r="C57">
-        <v>986.0129452588617</v>
+        <v>-457.6987334697255</v>
       </c>
       <c r="D57">
-        <v>3583.972945258862</v>
+        <v>2195.773266530275</v>
       </c>
       <c r="E57">
-        <v>1209.06</v>
+        <v>1264.572</v>
       </c>
       <c r="F57">
-        <v>3053.16</v>
+        <v>3108.672</v>
       </c>
       <c r="G57">
         <v>455.2</v>
@@ -6104,45 +6104,45 @@
         <v>435.9</v>
       </c>
       <c r="M57">
-        <v>286.8680270195884</v>
+        <v>468.6563789290355</v>
       </c>
       <c r="N57">
-        <v>149.0319729804116</v>
+        <v>-32.75637892903546</v>
       </c>
       <c r="O57">
-        <v>29.80639459608233</v>
+        <v>-6.551275785807093</v>
       </c>
       <c r="P57">
-        <v>119.2255783843293</v>
+        <v>-26.20510314322837</v>
       </c>
       <c r="Q57">
-        <v>338.3255783843293</v>
+        <v>192.8948968567716</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1051467612931319</v>
+        <v>0.106893015409499</v>
       </c>
       <c r="T57">
-        <v>1.220231875735332</v>
+        <v>1.256136698332143</v>
       </c>
       <c r="U57">
-        <v>0.09395774444168939</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V57">
-        <v>0.2</v>
+        <v>0.1860211530657538</v>
       </c>
       <c r="W57">
-        <v>0.07516619555335152</v>
+        <v>0.1227136149870541</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.519514058533387</v>
+        <v>0.9301057653287688</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6150,22 +6150,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1157525511729299</v>
+        <v>0.1168021286173468</v>
       </c>
       <c r="C58">
-        <v>-457.6987334697255</v>
+        <v>-545.6693954631455</v>
       </c>
       <c r="D58">
-        <v>2195.773266530275</v>
+        <v>2163.314604536855</v>
       </c>
       <c r="E58">
-        <v>1264.572</v>
+        <v>1320.084</v>
       </c>
       <c r="F58">
-        <v>3108.672</v>
+        <v>3164.184</v>
       </c>
       <c r="G58">
         <v>455.2</v>
@@ -6186,37 +6186,37 @@
         <v>435.9</v>
       </c>
       <c r="M58">
-        <v>468.6563789290355</v>
+        <v>477.0252428384826</v>
       </c>
       <c r="N58">
-        <v>-32.75637892903546</v>
+        <v>-41.12524283848256</v>
       </c>
       <c r="O58">
-        <v>-6.551275785807093</v>
+        <v>-8.225048567696513</v>
       </c>
       <c r="P58">
-        <v>-26.20510314322837</v>
+        <v>-32.90019427078605</v>
       </c>
       <c r="Q58">
-        <v>192.8948968567716</v>
+        <v>186.1998057292139</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.106893015409499</v>
+        <v>0.1083137832097199</v>
       </c>
       <c r="T58">
-        <v>1.256136698332143</v>
+        <v>1.285349179688704</v>
       </c>
       <c r="U58">
         <v>0.1507577444416894</v>
       </c>
       <c r="V58">
-        <v>0.1860211530657538</v>
+        <v>0.1827576240646002</v>
       </c>
       <c r="W58">
-        <v>0.1227136149870541</v>
+        <v>0.1232056172581881</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9301057653287688</v>
+        <v>0.9137881203230008</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6232,22 +6232,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1168021286173468</v>
+        <v>0.1178517060617637</v>
       </c>
       <c r="C59">
-        <v>-545.6693954631455</v>
+        <v>-632.6944065798184</v>
       </c>
       <c r="D59">
-        <v>2163.314604536855</v>
+        <v>2131.801593420182</v>
       </c>
       <c r="E59">
-        <v>1320.084</v>
+        <v>1375.596</v>
       </c>
       <c r="F59">
-        <v>3164.184</v>
+        <v>3219.696</v>
       </c>
       <c r="G59">
         <v>455.2</v>
@@ -6268,37 +6268,37 @@
         <v>435.9</v>
       </c>
       <c r="M59">
-        <v>477.0252428384826</v>
+        <v>485.3941067479297</v>
       </c>
       <c r="N59">
-        <v>-41.12524283848256</v>
+        <v>-49.49410674792966</v>
       </c>
       <c r="O59">
-        <v>-8.225048567696513</v>
+        <v>-9.898821349585933</v>
       </c>
       <c r="P59">
-        <v>-32.90019427078605</v>
+        <v>-39.59528539834373</v>
       </c>
       <c r="Q59">
-        <v>186.1998057292139</v>
+        <v>179.5047146016562</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1083137832097199</v>
+        <v>0.1098022066194752</v>
       </c>
       <c r="T59">
-        <v>1.285349179688704</v>
+        <v>1.315952731586054</v>
       </c>
       <c r="U59">
         <v>0.1507577444416894</v>
       </c>
       <c r="V59">
-        <v>0.1827576240646002</v>
+        <v>0.179606630546245</v>
       </c>
       <c r="W59">
-        <v>0.1232056172581881</v>
+        <v>0.1236806539337657</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9137881203230008</v>
+        <v>0.8980331527312249</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6314,22 +6314,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1178517060617637</v>
+        <v>0.1189012835061806</v>
       </c>
       <c r="C60">
-        <v>-632.6944065798166</v>
+        <v>-718.814499367088</v>
       </c>
       <c r="D60">
-        <v>2131.801593420183</v>
+        <v>2101.193500632912</v>
       </c>
       <c r="E60">
-        <v>1375.596</v>
+        <v>1431.108</v>
       </c>
       <c r="F60">
-        <v>3219.695999999999</v>
+        <v>3275.208</v>
       </c>
       <c r="G60">
         <v>455.2</v>
@@ -6350,37 +6350,37 @@
         <v>435.9</v>
       </c>
       <c r="M60">
-        <v>485.3941067479295</v>
+        <v>493.7629706573766</v>
       </c>
       <c r="N60">
-        <v>-49.49410674792949</v>
+        <v>-57.86297065737659</v>
       </c>
       <c r="O60">
-        <v>-9.8988213495859</v>
+        <v>-11.57259413147532</v>
       </c>
       <c r="P60">
-        <v>-39.59528539834359</v>
+        <v>-46.29037652590127</v>
       </c>
       <c r="Q60">
-        <v>179.5047146016564</v>
+        <v>172.8096234740987</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1098022066194752</v>
+        <v>0.1113632360492185</v>
       </c>
       <c r="T60">
-        <v>1.315952731586054</v>
+        <v>1.348049139673519</v>
       </c>
       <c r="U60">
         <v>0.1507577444416894</v>
       </c>
       <c r="V60">
-        <v>0.179606630546245</v>
+        <v>0.1765624503674951</v>
       </c>
       <c r="W60">
-        <v>0.1236806539337657</v>
+        <v>0.1241395876711881</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8980331527312252</v>
+        <v>0.8828122518374756</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6396,22 +6396,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1189012835061806</v>
+        <v>0.1199508609505974</v>
       </c>
       <c r="C61">
-        <v>-718.814499367088</v>
+        <v>-804.0681001569833</v>
       </c>
       <c r="D61">
-        <v>2101.193500632912</v>
+        <v>2071.451899843017</v>
       </c>
       <c r="E61">
-        <v>1431.108</v>
+        <v>1486.62</v>
       </c>
       <c r="F61">
-        <v>3275.208</v>
+        <v>3330.72</v>
       </c>
       <c r="G61">
         <v>455.2</v>
@@ -6432,37 +6432,37 @@
         <v>435.9</v>
       </c>
       <c r="M61">
-        <v>493.7629706573766</v>
+        <v>502.1318345668237</v>
       </c>
       <c r="N61">
-        <v>-57.86297065737659</v>
+        <v>-66.23183456682369</v>
       </c>
       <c r="O61">
-        <v>-11.57259413147532</v>
+        <v>-13.24636691336474</v>
       </c>
       <c r="P61">
-        <v>-46.29037652590127</v>
+        <v>-52.98546765345895</v>
       </c>
       <c r="Q61">
-        <v>172.8096234740987</v>
+        <v>166.114532346541</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1113632360492185</v>
+        <v>0.1130023169504489</v>
       </c>
       <c r="T61">
-        <v>1.348049139673519</v>
+        <v>1.381750368165356</v>
       </c>
       <c r="U61">
         <v>0.1507577444416894</v>
       </c>
       <c r="V61">
-        <v>0.1765624503674951</v>
+        <v>0.1736197428613702</v>
       </c>
       <c r="W61">
-        <v>0.1241395876711881</v>
+        <v>0.1245832236173631</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8828122518374756</v>
+        <v>0.8680987143068509</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6478,22 +6478,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1199508609505974</v>
+        <v>0.1210004383950143</v>
       </c>
       <c r="C62">
-        <v>-804.0681001569833</v>
+        <v>-888.491490006194</v>
       </c>
       <c r="D62">
-        <v>2071.451899843017</v>
+        <v>2042.540509993806</v>
       </c>
       <c r="E62">
-        <v>1486.62</v>
+        <v>1542.132</v>
       </c>
       <c r="F62">
-        <v>3330.72</v>
+        <v>3386.232</v>
       </c>
       <c r="G62">
         <v>455.2</v>
@@ -6514,37 +6514,37 @@
         <v>435.9</v>
       </c>
       <c r="M62">
-        <v>502.1318345668237</v>
+        <v>510.5006984762708</v>
       </c>
       <c r="N62">
-        <v>-66.23183456682369</v>
+        <v>-74.60069847627074</v>
       </c>
       <c r="O62">
-        <v>-13.24636691336474</v>
+        <v>-14.92013969525415</v>
       </c>
       <c r="P62">
-        <v>-52.98546765345895</v>
+        <v>-59.68055878101659</v>
       </c>
       <c r="Q62">
-        <v>166.114532346541</v>
+        <v>159.4194412189834</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1130023169504489</v>
+        <v>0.1147254532825117</v>
       </c>
       <c r="T62">
-        <v>1.381750368165356</v>
+        <v>1.417179864784981</v>
       </c>
       <c r="U62">
         <v>0.1507577444416894</v>
       </c>
       <c r="V62">
-        <v>0.1736197428613702</v>
+        <v>0.1707735175685609</v>
       </c>
       <c r="W62">
-        <v>0.1245832236173631</v>
+        <v>0.12501231412268</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8680987143068509</v>
+        <v>0.8538675878428041</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6560,22 +6560,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1210004383950143</v>
+        <v>0.1220500158394312</v>
       </c>
       <c r="C63">
-        <v>-888.491490006194</v>
+        <v>-972.1189523440867</v>
       </c>
       <c r="D63">
-        <v>2042.540509993806</v>
+        <v>2014.425047655913</v>
       </c>
       <c r="E63">
-        <v>1542.132</v>
+        <v>1597.644</v>
       </c>
       <c r="F63">
-        <v>3386.232</v>
+        <v>3441.744</v>
       </c>
       <c r="G63">
         <v>455.2</v>
@@ -6596,37 +6596,37 @@
         <v>435.9</v>
       </c>
       <c r="M63">
-        <v>510.5006984762708</v>
+        <v>518.8695623857178</v>
       </c>
       <c r="N63">
-        <v>-74.60069847627074</v>
+        <v>-82.96956238571778</v>
       </c>
       <c r="O63">
-        <v>-14.92013969525415</v>
+        <v>-16.59391247714356</v>
       </c>
       <c r="P63">
-        <v>-59.68055878101659</v>
+        <v>-66.37564990857422</v>
       </c>
       <c r="Q63">
-        <v>159.4194412189834</v>
+        <v>152.7243500914257</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1147254532825117</v>
+        <v>0.1165392810004726</v>
       </c>
       <c r="T63">
-        <v>1.417179864784981</v>
+        <v>1.454474071753007</v>
       </c>
       <c r="U63">
         <v>0.1507577444416894</v>
       </c>
       <c r="V63">
-        <v>0.1707735175685609</v>
+        <v>0.1680191059948744</v>
       </c>
       <c r="W63">
-        <v>0.12501231412268</v>
+        <v>0.125427562998793</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8538675878428041</v>
+        <v>0.8400955299743719</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6642,22 +6642,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1220500158394312</v>
+        <v>0.1230995932838481</v>
       </c>
       <c r="C64">
-        <v>-972.1189523440867</v>
+        <v>-1054.982908592087</v>
       </c>
       <c r="D64">
-        <v>2014.425047655913</v>
+        <v>1987.073091407913</v>
       </c>
       <c r="E64">
-        <v>1597.644</v>
+        <v>1653.156</v>
       </c>
       <c r="F64">
-        <v>3441.744</v>
+        <v>3497.256</v>
       </c>
       <c r="G64">
         <v>455.2</v>
@@ -6678,37 +6678,37 @@
         <v>435.9</v>
       </c>
       <c r="M64">
-        <v>518.8695623857178</v>
+        <v>527.2384262951649</v>
       </c>
       <c r="N64">
-        <v>-82.96956238571778</v>
+        <v>-91.33842629516488</v>
       </c>
       <c r="O64">
-        <v>-16.59391247714356</v>
+        <v>-18.26768525903298</v>
       </c>
       <c r="P64">
-        <v>-66.37564990857422</v>
+        <v>-73.07074103613191</v>
       </c>
       <c r="Q64">
-        <v>152.7243500914257</v>
+        <v>146.0292589638681</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1165392810004726</v>
+        <v>0.1184511534599448</v>
       </c>
       <c r="T64">
-        <v>1.454474071753007</v>
+        <v>1.493784181800386</v>
       </c>
       <c r="U64">
         <v>0.1507577444416894</v>
       </c>
       <c r="V64">
-        <v>0.1680191059948744</v>
+        <v>0.1653521360584478</v>
       </c>
       <c r="W64">
-        <v>0.125427562998793</v>
+        <v>0.1258296293709025</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8400955299743719</v>
+        <v>0.8267606802922389</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6724,22 +6724,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1230995932838481</v>
+        <v>0.124149170728265</v>
       </c>
       <c r="C65">
-        <v>-1054.982908592087</v>
+        <v>-1137.11404288239</v>
       </c>
       <c r="D65">
-        <v>1987.073091407913</v>
+        <v>1960.45395711761</v>
       </c>
       <c r="E65">
-        <v>1653.156</v>
+        <v>1708.668</v>
       </c>
       <c r="F65">
-        <v>3497.256</v>
+        <v>3552.768</v>
       </c>
       <c r="G65">
         <v>455.2</v>
@@ -6760,37 +6760,37 @@
         <v>435.9</v>
       </c>
       <c r="M65">
-        <v>527.2384262951649</v>
+        <v>535.607290204612</v>
       </c>
       <c r="N65">
-        <v>-91.33842629516488</v>
+        <v>-99.70729020461198</v>
       </c>
       <c r="O65">
-        <v>-18.26768525903298</v>
+        <v>-19.9414580409224</v>
       </c>
       <c r="P65">
-        <v>-73.07074103613191</v>
+        <v>-79.76583216368958</v>
       </c>
       <c r="Q65">
-        <v>146.0292589638681</v>
+        <v>139.3341678363104</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1184511534599448</v>
+        <v>0.1204692410560544</v>
       </c>
       <c r="T65">
-        <v>1.493784181800386</v>
+        <v>1.535278186850396</v>
       </c>
       <c r="U65">
         <v>0.1507577444416894</v>
       </c>
       <c r="V65">
-        <v>0.1653521360584478</v>
+        <v>0.1627685089325346</v>
       </c>
       <c r="W65">
-        <v>0.1258296293709025</v>
+        <v>0.1262191311688835</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8267606802922389</v>
+        <v>0.8138425446626727</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6806,22 +6806,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.124149170728265</v>
+        <v>0.1251987481726819</v>
       </c>
       <c r="C66">
-        <v>-1137.11404288239</v>
+        <v>-1218.541416884677</v>
       </c>
       <c r="D66">
-        <v>1960.45395711761</v>
+        <v>1934.538583115323</v>
       </c>
       <c r="E66">
-        <v>1708.668</v>
+        <v>1764.18</v>
       </c>
       <c r="F66">
-        <v>3552.768</v>
+        <v>3608.28</v>
       </c>
       <c r="G66">
         <v>455.2</v>
@@ -6842,37 +6842,37 @@
         <v>435.9</v>
       </c>
       <c r="M66">
-        <v>535.607290204612</v>
+        <v>543.9761541140591</v>
       </c>
       <c r="N66">
-        <v>-99.70729020461198</v>
+        <v>-108.0761541140591</v>
       </c>
       <c r="O66">
-        <v>-19.9414580409224</v>
+        <v>-21.61523082281182</v>
       </c>
       <c r="P66">
-        <v>-79.76583216368958</v>
+        <v>-86.46092329124727</v>
       </c>
       <c r="Q66">
-        <v>139.3341678363104</v>
+        <v>132.6390767087527</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1204692410560544</v>
+        <v>0.1226026479433702</v>
       </c>
       <c r="T66">
-        <v>1.535278186850396</v>
+        <v>1.579143277903265</v>
       </c>
       <c r="U66">
         <v>0.1507577444416894</v>
       </c>
       <c r="V66">
-        <v>0.1627685089325346</v>
+        <v>0.1602643780258801</v>
       </c>
       <c r="W66">
-        <v>0.1262191311688835</v>
+        <v>0.1265966482961575</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8138425446626727</v>
+        <v>0.8013218901294007</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6888,22 +6888,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1251987481726819</v>
+        <v>0.1627126977691551</v>
       </c>
       <c r="C67">
-        <v>-1218.541416884677</v>
+        <v>-1894.791662466138</v>
       </c>
       <c r="D67">
-        <v>1934.538583115323</v>
+        <v>1313.800337533862</v>
       </c>
       <c r="E67">
-        <v>1764.18</v>
+        <v>1819.692</v>
       </c>
       <c r="F67">
-        <v>3608.28</v>
+        <v>3663.792</v>
       </c>
       <c r="G67">
         <v>455.2</v>
@@ -6924,45 +6924,45 @@
         <v>435.9</v>
       </c>
       <c r="M67">
-        <v>543.9761541140591</v>
+        <v>750.189786023506</v>
       </c>
       <c r="N67">
-        <v>-108.0761541140591</v>
+        <v>-314.289786023506</v>
       </c>
       <c r="O67">
-        <v>-21.61523082281182</v>
+        <v>-62.8579572047012</v>
       </c>
       <c r="P67">
-        <v>-86.46092329124727</v>
+        <v>-251.4318288188048</v>
       </c>
       <c r="Q67">
-        <v>132.6390767087527</v>
+        <v>-32.33182881880484</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1226026479433702</v>
+        <v>0.1272861733301055</v>
       </c>
       <c r="T67">
-        <v>1.579143277903265</v>
+        <v>1.675441489350424</v>
       </c>
       <c r="U67">
-        <v>0.1507577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V67">
-        <v>0.1602643780258801</v>
+        <v>0.1162105931381854</v>
       </c>
       <c r="W67">
-        <v>0.1265966482961575</v>
+        <v>0.1809627255104837</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.8013218901294007</v>
+        <v>0.5810529656909269</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6970,22 +6970,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1627126977691551</v>
+        <v>0.164302275213572</v>
       </c>
       <c r="C68">
-        <v>-1894.791662466138</v>
+        <v>-1967.926846318493</v>
       </c>
       <c r="D68">
-        <v>1313.800337533862</v>
+        <v>1296.177153681507</v>
       </c>
       <c r="E68">
-        <v>1819.692</v>
+        <v>1875.204</v>
       </c>
       <c r="F68">
-        <v>3663.792</v>
+        <v>3719.304</v>
       </c>
       <c r="G68">
         <v>455.2</v>
@@ -7006,37 +7006,37 @@
         <v>435.9</v>
       </c>
       <c r="M68">
-        <v>750.189786023506</v>
+        <v>761.5562979329532</v>
       </c>
       <c r="N68">
-        <v>-314.289786023506</v>
+        <v>-325.6562979329531</v>
       </c>
       <c r="O68">
-        <v>-62.8579572047012</v>
+        <v>-65.13125958659063</v>
       </c>
       <c r="P68">
-        <v>-251.4318288188048</v>
+        <v>-260.5250383463625</v>
       </c>
       <c r="Q68">
-        <v>-32.33182881880484</v>
+        <v>-41.42503834636256</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1272861733301055</v>
+        <v>0.1297554513098057</v>
       </c>
       <c r="T68">
-        <v>1.675441489350424</v>
+        <v>1.726212443573164</v>
       </c>
       <c r="U68">
         <v>0.2047577444416894</v>
       </c>
       <c r="V68">
-        <v>0.1162105931381854</v>
+        <v>0.1144761066734363</v>
       </c>
       <c r="W68">
-        <v>0.1809627255104837</v>
+        <v>0.1813178750467704</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5810529656909269</v>
+        <v>0.5723805333671816</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7052,22 +7052,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.164302275213572</v>
+        <v>0.1658918526579889</v>
       </c>
       <c r="C69">
-        <v>-1967.926846318493</v>
+        <v>-2040.59549701426</v>
       </c>
       <c r="D69">
-        <v>1296.177153681507</v>
+        <v>1279.02050298574</v>
       </c>
       <c r="E69">
-        <v>1875.204</v>
+        <v>1930.716</v>
       </c>
       <c r="F69">
-        <v>3719.304</v>
+        <v>3774.816</v>
       </c>
       <c r="G69">
         <v>455.2</v>
@@ -7088,37 +7088,37 @@
         <v>435.9</v>
       </c>
       <c r="M69">
-        <v>761.5562979329532</v>
+        <v>772.9228098424003</v>
       </c>
       <c r="N69">
-        <v>-325.6562979329531</v>
+        <v>-337.0228098424002</v>
       </c>
       <c r="O69">
-        <v>-65.13125958659063</v>
+        <v>-67.40456196848005</v>
       </c>
       <c r="P69">
-        <v>-260.5250383463625</v>
+        <v>-269.6182478739202</v>
       </c>
       <c r="Q69">
-        <v>-41.42503834636256</v>
+        <v>-50.51824787392025</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1297554513098057</v>
+        <v>0.1323790591632371</v>
       </c>
       <c r="T69">
-        <v>1.726212443573164</v>
+        <v>1.780156582434826</v>
       </c>
       <c r="U69">
         <v>0.2047577444416894</v>
       </c>
       <c r="V69">
-        <v>0.1144761066734363</v>
+        <v>0.112792634516474</v>
       </c>
       <c r="W69">
-        <v>0.1813178750467704</v>
+        <v>0.1816625790084603</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5723805333671816</v>
+        <v>0.5639631725823702</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7134,22 +7134,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1658918526579889</v>
+        <v>0.1674814301024058</v>
       </c>
       <c r="C70">
-        <v>-2040.59549701426</v>
+        <v>-2112.815898130041</v>
       </c>
       <c r="D70">
-        <v>1279.02050298574</v>
+        <v>1262.312101869959</v>
       </c>
       <c r="E70">
-        <v>1930.716</v>
+        <v>1986.228</v>
       </c>
       <c r="F70">
-        <v>3774.816</v>
+        <v>3830.328</v>
       </c>
       <c r="G70">
         <v>455.2</v>
@@ -7170,37 +7170,37 @@
         <v>435.9</v>
       </c>
       <c r="M70">
-        <v>772.9228098424003</v>
+        <v>784.2893217518473</v>
       </c>
       <c r="N70">
-        <v>-337.0228098424002</v>
+        <v>-348.3893217518473</v>
       </c>
       <c r="O70">
-        <v>-67.40456196848005</v>
+        <v>-69.67786435036946</v>
       </c>
       <c r="P70">
-        <v>-269.6182478739202</v>
+        <v>-278.7114574014778</v>
       </c>
       <c r="Q70">
-        <v>-50.51824787392025</v>
+        <v>-59.61145740147782</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1323790591632371</v>
+        <v>0.1351719320394706</v>
       </c>
       <c r="T70">
-        <v>1.780156582434826</v>
+        <v>1.83758098831982</v>
       </c>
       <c r="U70">
         <v>0.2047577444416894</v>
       </c>
       <c r="V70">
-        <v>0.112792634516474</v>
+        <v>0.1111579586539164</v>
       </c>
       <c r="W70">
-        <v>0.1816625790084603</v>
+        <v>0.1819972915509709</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5639631725823702</v>
+        <v>0.5557897932695821</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7216,22 +7216,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1674814301024058</v>
+        <v>0.1690710075468227</v>
       </c>
       <c r="C71">
-        <v>-2112.815898130041</v>
+        <v>-2184.605390176862</v>
       </c>
       <c r="D71">
-        <v>1262.312101869959</v>
+        <v>1246.034609823138</v>
       </c>
       <c r="E71">
-        <v>1986.228</v>
+        <v>2041.74</v>
       </c>
       <c r="F71">
-        <v>3830.328</v>
+        <v>3885.84</v>
       </c>
       <c r="G71">
         <v>455.2</v>
@@ -7252,37 +7252,37 @@
         <v>435.9</v>
       </c>
       <c r="M71">
-        <v>784.2893217518473</v>
+        <v>795.6558336612943</v>
       </c>
       <c r="N71">
-        <v>-348.3893217518473</v>
+        <v>-359.7558336612943</v>
       </c>
       <c r="O71">
-        <v>-69.67786435036946</v>
+        <v>-71.95116673225886</v>
       </c>
       <c r="P71">
-        <v>-278.7114574014778</v>
+        <v>-287.8046669290354</v>
       </c>
       <c r="Q71">
-        <v>-59.61145740147782</v>
+        <v>-68.70466692903545</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1351719320394706</v>
+        <v>0.1381509964407862</v>
       </c>
       <c r="T71">
-        <v>1.83758098831982</v>
+        <v>1.89883368793048</v>
       </c>
       <c r="U71">
         <v>0.2047577444416894</v>
       </c>
       <c r="V71">
-        <v>0.1111579586539164</v>
+        <v>0.1095699878160034</v>
       </c>
       <c r="W71">
-        <v>0.1819972915509709</v>
+        <v>0.1823224408779812</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5557897932695821</v>
+        <v>0.5478499390800168</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7298,22 +7298,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1690710075468227</v>
+        <v>0.1706605849912396</v>
       </c>
       <c r="C72">
-        <v>-2184.605390176862</v>
+        <v>-2255.980430630153</v>
       </c>
       <c r="D72">
-        <v>1246.034609823138</v>
+        <v>1230.171569369847</v>
       </c>
       <c r="E72">
-        <v>2041.74</v>
+        <v>2097.252</v>
       </c>
       <c r="F72">
-        <v>3885.84</v>
+        <v>3941.352</v>
       </c>
       <c r="G72">
         <v>455.2</v>
@@ -7334,37 +7334,37 @@
         <v>435.9</v>
       </c>
       <c r="M72">
-        <v>795.6558336612943</v>
+        <v>807.0223455707414</v>
       </c>
       <c r="N72">
-        <v>-359.7558336612943</v>
+        <v>-371.1223455707414</v>
       </c>
       <c r="O72">
-        <v>-71.95116673225886</v>
+        <v>-74.22446911414828</v>
       </c>
       <c r="P72">
-        <v>-287.8046669290354</v>
+        <v>-296.8978764565931</v>
       </c>
       <c r="Q72">
-        <v>-68.70466692903545</v>
+        <v>-77.79787645659314</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1381509964407862</v>
+        <v>0.1413355135594341</v>
       </c>
       <c r="T72">
-        <v>1.89883368793048</v>
+        <v>1.964310711652222</v>
       </c>
       <c r="U72">
         <v>0.2047577444416894</v>
       </c>
       <c r="V72">
-        <v>0.1095699878160034</v>
+        <v>0.1080267485509892</v>
       </c>
       <c r="W72">
-        <v>0.1823224408779812</v>
+        <v>0.1826384310690193</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5478499390800168</v>
+        <v>0.5401337427549461</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7380,22 +7380,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1706605849912396</v>
+        <v>0.1722501624356564</v>
       </c>
       <c r="C73">
-        <v>-2255.980430630152</v>
+        <v>-2326.956649431992</v>
       </c>
       <c r="D73">
-        <v>1230.171569369848</v>
+        <v>1214.707350568008</v>
       </c>
       <c r="E73">
-        <v>2097.252</v>
+        <v>2152.764</v>
       </c>
       <c r="F73">
-        <v>3941.352</v>
+        <v>3996.864</v>
       </c>
       <c r="G73">
         <v>455.2</v>
@@ -7416,37 +7416,37 @@
         <v>435.9</v>
       </c>
       <c r="M73">
-        <v>807.0223455707413</v>
+        <v>818.3888574801883</v>
       </c>
       <c r="N73">
-        <v>-371.1223455707413</v>
+        <v>-382.4888574801883</v>
       </c>
       <c r="O73">
-        <v>-74.22446911414826</v>
+        <v>-76.49777149603766</v>
       </c>
       <c r="P73">
-        <v>-296.8978764565931</v>
+        <v>-305.9910859841506</v>
       </c>
       <c r="Q73">
-        <v>-77.79787645659309</v>
+        <v>-86.89108598415066</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.141335513559434</v>
+        <v>0.1447474961865567</v>
       </c>
       <c r="T73">
-        <v>1.964310711652221</v>
+        <v>2.0344646656398</v>
       </c>
       <c r="U73">
         <v>0.2047577444416894</v>
       </c>
       <c r="V73">
-        <v>0.1080267485509892</v>
+        <v>0.1065263770433366</v>
       </c>
       <c r="W73">
-        <v>0.1826384310690193</v>
+        <v>0.1829456437547508</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5401337427549462</v>
+        <v>0.532631885216683</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7462,22 +7462,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1722501624356564</v>
+        <v>0.1738397398800734</v>
       </c>
       <c r="C74">
-        <v>-2326.956649431992</v>
+        <v>-2397.548900359079</v>
       </c>
       <c r="D74">
-        <v>1214.707350568008</v>
+        <v>1199.627099640921</v>
       </c>
       <c r="E74">
-        <v>2152.764</v>
+        <v>2208.276</v>
       </c>
       <c r="F74">
-        <v>3996.864</v>
+        <v>4052.376</v>
       </c>
       <c r="G74">
         <v>455.2</v>
@@ -7498,37 +7498,37 @@
         <v>435.9</v>
       </c>
       <c r="M74">
-        <v>818.3888574801883</v>
+        <v>829.7553693896355</v>
       </c>
       <c r="N74">
-        <v>-382.4888574801883</v>
+        <v>-393.8553693896354</v>
       </c>
       <c r="O74">
-        <v>-76.49777149603766</v>
+        <v>-78.77107387792709</v>
       </c>
       <c r="P74">
-        <v>-305.9910859841506</v>
+        <v>-315.0842955117083</v>
       </c>
       <c r="Q74">
-        <v>-86.89108598415066</v>
+        <v>-95.98429551170835</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1447474961865567</v>
+        <v>0.1484122182675403</v>
       </c>
       <c r="T74">
-        <v>2.0344646656398</v>
+        <v>2.109815208811644</v>
       </c>
       <c r="U74">
         <v>0.2047577444416894</v>
       </c>
       <c r="V74">
-        <v>0.1065263770433366</v>
+        <v>0.1050671116043868</v>
       </c>
       <c r="W74">
-        <v>0.1829456437547508</v>
+        <v>0.1832444396545719</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.532631885216683</v>
+        <v>0.5253355580219339</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7544,22 +7544,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1738397398800734</v>
+        <v>0.1754293173244902</v>
       </c>
       <c r="C75">
-        <v>-2397.548900359079</v>
+        <v>-2467.771308611304</v>
       </c>
       <c r="D75">
-        <v>1199.627099640921</v>
+        <v>1184.916691388697</v>
       </c>
       <c r="E75">
-        <v>2208.276</v>
+        <v>2263.788</v>
       </c>
       <c r="F75">
-        <v>4052.376</v>
+        <v>4107.888</v>
       </c>
       <c r="G75">
         <v>455.2</v>
@@ -7580,37 +7580,37 @@
         <v>435.9</v>
       </c>
       <c r="M75">
-        <v>829.7553693896355</v>
+        <v>841.1218812990826</v>
       </c>
       <c r="N75">
-        <v>-393.8553693896354</v>
+        <v>-405.2218812990826</v>
       </c>
       <c r="O75">
-        <v>-78.77107387792709</v>
+        <v>-81.04437625981652</v>
       </c>
       <c r="P75">
-        <v>-315.0842955117083</v>
+        <v>-324.1775050392661</v>
       </c>
       <c r="Q75">
-        <v>-95.98429551170835</v>
+        <v>-105.0775050392661</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1484122182675403</v>
+        <v>0.152358842047061</v>
       </c>
       <c r="T75">
-        <v>2.109815208811644</v>
+        <v>2.190961947612093</v>
       </c>
       <c r="U75">
         <v>0.2047577444416894</v>
       </c>
       <c r="V75">
-        <v>0.1050671116043868</v>
+        <v>0.1036472857718951</v>
       </c>
       <c r="W75">
-        <v>0.1832444396545719</v>
+        <v>0.183535159989533</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5253355580219339</v>
+        <v>0.5182364288594753</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7626,22 +7626,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1754293173244902</v>
+        <v>0.1770188947689071</v>
       </c>
       <c r="C76">
-        <v>-2467.771308611304</v>
+        <v>-2537.637314941426</v>
       </c>
       <c r="D76">
-        <v>1184.916691388697</v>
+        <v>1170.562685058574</v>
       </c>
       <c r="E76">
-        <v>2263.788</v>
+        <v>2319.3</v>
       </c>
       <c r="F76">
-        <v>4107.888</v>
+        <v>4163.4</v>
       </c>
       <c r="G76">
         <v>455.2</v>
@@ -7662,37 +7662,37 @@
         <v>435.9</v>
       </c>
       <c r="M76">
-        <v>841.1218812990826</v>
+        <v>852.4883932085296</v>
       </c>
       <c r="N76">
-        <v>-405.2218812990826</v>
+        <v>-416.5883932085296</v>
       </c>
       <c r="O76">
-        <v>-81.04437625981652</v>
+        <v>-83.31767864170592</v>
       </c>
       <c r="P76">
-        <v>-324.1775050392661</v>
+        <v>-333.2707145668236</v>
       </c>
       <c r="Q76">
-        <v>-105.0775050392661</v>
+        <v>-114.1707145668237</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.152358842047061</v>
+        <v>0.1566211957289435</v>
       </c>
       <c r="T76">
-        <v>2.190961947612093</v>
+        <v>2.278600425516576</v>
       </c>
       <c r="U76">
         <v>0.2047577444416894</v>
       </c>
       <c r="V76">
-        <v>0.1036472857718951</v>
+        <v>0.1022653219616032</v>
       </c>
       <c r="W76">
-        <v>0.183535159989533</v>
+        <v>0.1838181277822284</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5182364288594753</v>
+        <v>0.5113266098080156</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7708,22 +7708,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1770188947689071</v>
+        <v>0.178608472213324</v>
       </c>
       <c r="C77">
-        <v>-2537.637314941426</v>
+        <v>-2607.159716615624</v>
       </c>
       <c r="D77">
-        <v>1170.562685058574</v>
+        <v>1156.552283384376</v>
       </c>
       <c r="E77">
-        <v>2319.3</v>
+        <v>2374.812</v>
       </c>
       <c r="F77">
-        <v>4163.4</v>
+        <v>4218.912</v>
       </c>
       <c r="G77">
         <v>455.2</v>
@@ -7744,37 +7744,37 @@
         <v>435.9</v>
       </c>
       <c r="M77">
-        <v>852.4883932085296</v>
+        <v>863.8549051179767</v>
       </c>
       <c r="N77">
-        <v>-416.5883932085296</v>
+        <v>-427.9549051179767</v>
       </c>
       <c r="O77">
-        <v>-83.31767864170592</v>
+        <v>-85.59098102359535</v>
       </c>
       <c r="P77">
-        <v>-333.2707145668236</v>
+        <v>-342.3639240943813</v>
       </c>
       <c r="Q77">
-        <v>-114.1707145668237</v>
+        <v>-123.2639240943814</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1566211957289435</v>
+        <v>0.1612387455509828</v>
       </c>
       <c r="T77">
-        <v>2.278600425516576</v>
+        <v>2.3735421099131</v>
       </c>
       <c r="U77">
         <v>0.2047577444416894</v>
       </c>
       <c r="V77">
-        <v>0.1022653219616032</v>
+        <v>0.1009197256200031</v>
       </c>
       <c r="W77">
-        <v>0.1838181277822284</v>
+        <v>0.1840936490540634</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5113266098080156</v>
+        <v>0.5045986281000154</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7790,22 +7790,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.178608472213324</v>
+        <v>0.207484022817586</v>
       </c>
       <c r="C78">
-        <v>-2607.159716615624</v>
+        <v>-2869.223257104062</v>
       </c>
       <c r="D78">
-        <v>1156.552283384376</v>
+        <v>950.0007428959376</v>
       </c>
       <c r="E78">
-        <v>2374.812</v>
+        <v>2430.324</v>
       </c>
       <c r="F78">
-        <v>4218.912</v>
+        <v>4274.424</v>
       </c>
       <c r="G78">
         <v>455.2</v>
@@ -7826,45 +7826,45 @@
         <v>435.9</v>
       </c>
       <c r="M78">
-        <v>863.8549051179767</v>
+        <v>1024.826257027424</v>
       </c>
       <c r="N78">
-        <v>-427.9549051179767</v>
+        <v>-588.9262570274236</v>
       </c>
       <c r="O78">
-        <v>-85.59098102359535</v>
+        <v>-117.7852514054847</v>
       </c>
       <c r="P78">
-        <v>-342.3639240943813</v>
+        <v>-471.1410056219389</v>
       </c>
       <c r="Q78">
-        <v>-123.2639240943814</v>
+        <v>-252.041005621939</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1612387455509828</v>
+        <v>0.1677185743133953</v>
       </c>
       <c r="T78">
-        <v>2.3735421099131</v>
+        <v>2.506774209406243</v>
       </c>
       <c r="U78">
-        <v>0.2047577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V78">
-        <v>0.1009197256200031</v>
+        <v>0.08506807802999833</v>
       </c>
       <c r="W78">
-        <v>0.1840936490540634</v>
+        <v>0.2193620139292274</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.5045986281000154</v>
+        <v>0.4253403901499917</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7872,22 +7872,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.207484022817586</v>
+        <v>0.2094236002620029</v>
       </c>
       <c r="C79">
-        <v>-2869.223257104062</v>
+        <v>-2935.99646887394</v>
       </c>
       <c r="D79">
-        <v>950.0007428959376</v>
+        <v>938.7395311260598</v>
       </c>
       <c r="E79">
-        <v>2430.324</v>
+        <v>2485.836</v>
       </c>
       <c r="F79">
-        <v>4274.424</v>
+        <v>4329.936</v>
       </c>
       <c r="G79">
         <v>455.2</v>
@@ -7908,37 +7908,37 @@
         <v>435.9</v>
       </c>
       <c r="M79">
-        <v>1024.826257027424</v>
+        <v>1038.135688936871</v>
       </c>
       <c r="N79">
-        <v>-588.9262570274236</v>
+        <v>-602.2356889368707</v>
       </c>
       <c r="O79">
-        <v>-117.7852514054847</v>
+        <v>-120.4471377873741</v>
       </c>
       <c r="P79">
-        <v>-471.1410056219389</v>
+        <v>-481.7885511494966</v>
       </c>
       <c r="Q79">
-        <v>-252.041005621939</v>
+        <v>-262.6885511494966</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1677185743133953</v>
+        <v>0.1732603276912769</v>
       </c>
       <c r="T79">
-        <v>2.506774209406243</v>
+        <v>2.620718491651981</v>
       </c>
       <c r="U79">
         <v>0.2397577444416894</v>
       </c>
       <c r="V79">
-        <v>0.08506807802999833</v>
+        <v>0.08397746164499836</v>
       </c>
       <c r="W79">
-        <v>0.2193620139292274</v>
+        <v>0.2196234976537461</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4253403901499917</v>
+        <v>0.4198873082249918</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7954,22 +7954,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2094236002620029</v>
+        <v>0.2113631777064198</v>
       </c>
       <c r="C80">
-        <v>-2935.99646887394</v>
+        <v>-3002.505829796689</v>
       </c>
       <c r="D80">
-        <v>938.7395311260598</v>
+        <v>927.7421702033113</v>
       </c>
       <c r="E80">
-        <v>2485.836</v>
+        <v>2541.348</v>
       </c>
       <c r="F80">
-        <v>4329.936</v>
+        <v>4385.448</v>
       </c>
       <c r="G80">
         <v>455.2</v>
@@ -7990,37 +7990,37 @@
         <v>435.9</v>
       </c>
       <c r="M80">
-        <v>1038.135688936871</v>
+        <v>1051.445120846318</v>
       </c>
       <c r="N80">
-        <v>-602.2356889368707</v>
+        <v>-615.5451208463178</v>
       </c>
       <c r="O80">
-        <v>-120.4471377873741</v>
+        <v>-123.1090241692636</v>
       </c>
       <c r="P80">
-        <v>-481.7885511494966</v>
+        <v>-492.4360966770543</v>
       </c>
       <c r="Q80">
-        <v>-262.6885511494966</v>
+        <v>-273.3360966770543</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1732603276912769</v>
+        <v>0.1793298671051472</v>
       </c>
       <c r="T80">
-        <v>2.620718491651981</v>
+        <v>2.745514610302075</v>
       </c>
       <c r="U80">
         <v>0.2397577444416894</v>
       </c>
       <c r="V80">
-        <v>0.08397746164499836</v>
+        <v>0.08291445580139079</v>
       </c>
       <c r="W80">
-        <v>0.2196234976537461</v>
+        <v>0.2198783615371378</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4198873082249918</v>
+        <v>0.4145722790069539</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8036,22 +8036,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2113631777064198</v>
+        <v>0.2133027551508367</v>
       </c>
       <c r="C81">
-        <v>-3002.505829796689</v>
+        <v>-3068.760505557098</v>
       </c>
       <c r="D81">
-        <v>927.7421702033113</v>
+        <v>916.9994944429021</v>
       </c>
       <c r="E81">
-        <v>2541.348</v>
+        <v>2596.86</v>
       </c>
       <c r="F81">
-        <v>4385.448</v>
+        <v>4440.96</v>
       </c>
       <c r="G81">
         <v>455.2</v>
@@ -8072,37 +8072,37 @@
         <v>435.9</v>
       </c>
       <c r="M81">
-        <v>1051.445120846318</v>
+        <v>1064.754552755765</v>
       </c>
       <c r="N81">
-        <v>-615.5451208463178</v>
+        <v>-628.8545527557649</v>
       </c>
       <c r="O81">
-        <v>-123.1090241692636</v>
+        <v>-125.770910551153</v>
       </c>
       <c r="P81">
-        <v>-492.4360966770543</v>
+        <v>-503.0836422046119</v>
       </c>
       <c r="Q81">
-        <v>-273.3360966770543</v>
+        <v>-283.983642204612</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1793298671051472</v>
+        <v>0.1860063604604046</v>
       </c>
       <c r="T81">
-        <v>2.745514610302075</v>
+        <v>2.882790340817179</v>
       </c>
       <c r="U81">
         <v>0.2397577444416894</v>
       </c>
       <c r="V81">
-        <v>0.08291445580139079</v>
+        <v>0.08187802510387339</v>
       </c>
       <c r="W81">
-        <v>0.2198783615371378</v>
+        <v>0.2201268538234447</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4145722790069539</v>
+        <v>0.409390125519367</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8118,22 +8118,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2133027551508367</v>
+        <v>0.2152423325952535</v>
       </c>
       <c r="C82">
-        <v>-3068.760505557098</v>
+        <v>-3134.769242167846</v>
       </c>
       <c r="D82">
-        <v>916.9994944429021</v>
+        <v>906.502757832154</v>
       </c>
       <c r="E82">
-        <v>2596.86</v>
+        <v>2652.372</v>
       </c>
       <c r="F82">
-        <v>4440.96</v>
+        <v>4496.472</v>
       </c>
       <c r="G82">
         <v>455.2</v>
@@ -8154,37 +8154,37 @@
         <v>435.9</v>
       </c>
       <c r="M82">
-        <v>1064.754552755765</v>
+        <v>1078.063984665212</v>
       </c>
       <c r="N82">
-        <v>-628.8545527557649</v>
+        <v>-642.163984665212</v>
       </c>
       <c r="O82">
-        <v>-125.770910551153</v>
+        <v>-128.4327969330424</v>
       </c>
       <c r="P82">
-        <v>-503.0836422046119</v>
+        <v>-513.7311877321696</v>
       </c>
       <c r="Q82">
-        <v>-283.983642204612</v>
+        <v>-294.6311877321696</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1860063604604046</v>
+        <v>0.1933856425898996</v>
       </c>
       <c r="T82">
-        <v>2.882790340817179</v>
+        <v>3.03451614822861</v>
       </c>
       <c r="U82">
         <v>0.2397577444416894</v>
       </c>
       <c r="V82">
-        <v>0.08187802510387339</v>
+        <v>0.0808671852877762</v>
       </c>
       <c r="W82">
-        <v>0.2201268538234447</v>
+        <v>0.220369210497744</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.409390125519367</v>
+        <v>0.4043359264388809</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8200,22 +8200,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2152423325952535</v>
+        <v>0.2171819100396705</v>
       </c>
       <c r="C83">
-        <v>-3134.769242167846</v>
+        <v>-3200.540389717235</v>
       </c>
       <c r="D83">
-        <v>906.502757832154</v>
+        <v>896.2436102827653</v>
       </c>
       <c r="E83">
-        <v>2652.372</v>
+        <v>2707.884</v>
       </c>
       <c r="F83">
-        <v>4496.472</v>
+        <v>4551.984</v>
       </c>
       <c r="G83">
         <v>455.2</v>
@@ -8236,37 +8236,37 @@
         <v>435.9</v>
       </c>
       <c r="M83">
-        <v>1078.063984665212</v>
+        <v>1091.373416574659</v>
       </c>
       <c r="N83">
-        <v>-642.163984665212</v>
+        <v>-655.473416574659</v>
       </c>
       <c r="O83">
-        <v>-128.4327969330424</v>
+        <v>-131.0946833149318</v>
       </c>
       <c r="P83">
-        <v>-513.7311877321696</v>
+        <v>-524.3787332597273</v>
       </c>
       <c r="Q83">
-        <v>-294.6311877321696</v>
+        <v>-305.2787332597273</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1933856425898996</v>
+        <v>0.2015848449560051</v>
       </c>
       <c r="T83">
-        <v>3.03451614822861</v>
+        <v>3.203100378685755</v>
       </c>
       <c r="U83">
         <v>0.2397577444416894</v>
       </c>
       <c r="V83">
-        <v>0.0808671852877762</v>
+        <v>0.0798810001013399</v>
       </c>
       <c r="W83">
-        <v>0.220369210497744</v>
+        <v>0.2206056560336458</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4043359264388809</v>
+        <v>0.3994050005066995</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8282,22 +8282,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2171819100396705</v>
+        <v>0.2191214874840874</v>
       </c>
       <c r="C84">
-        <v>-3200.540389717235</v>
+        <v>-3266.081924522415</v>
       </c>
       <c r="D84">
-        <v>896.2436102827653</v>
+        <v>886.2140754775857</v>
       </c>
       <c r="E84">
-        <v>2707.884</v>
+        <v>2763.396</v>
       </c>
       <c r="F84">
-        <v>4551.984</v>
+        <v>4607.496</v>
       </c>
       <c r="G84">
         <v>455.2</v>
@@ -8318,37 +8318,37 @@
         <v>435.9</v>
       </c>
       <c r="M84">
-        <v>1091.373416574659</v>
+        <v>1104.682848484106</v>
       </c>
       <c r="N84">
-        <v>-655.473416574659</v>
+        <v>-668.7828484841061</v>
       </c>
       <c r="O84">
-        <v>-131.0946833149318</v>
+        <v>-133.7565696968212</v>
       </c>
       <c r="P84">
-        <v>-524.3787332597273</v>
+        <v>-535.0262787872849</v>
       </c>
       <c r="Q84">
-        <v>-305.2787332597273</v>
+        <v>-315.926278787285</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2015848449560051</v>
+        <v>0.2107486593651819</v>
       </c>
       <c r="T84">
-        <v>3.203100378685755</v>
+        <v>3.391518048020212</v>
       </c>
       <c r="U84">
         <v>0.2397577444416894</v>
       </c>
       <c r="V84">
-        <v>0.0798810001013399</v>
+        <v>0.07891857841337194</v>
       </c>
       <c r="W84">
-        <v>0.2206056560336458</v>
+        <v>0.2208364040867548</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3994050005066995</v>
+        <v>0.3945928920668598</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8364,22 +8364,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2191214874840874</v>
+        <v>0.2210610649285042</v>
       </c>
       <c r="C85">
-        <v>-3266.081924522415</v>
+        <v>-3331.401469811623</v>
       </c>
       <c r="D85">
-        <v>886.2140754775857</v>
+        <v>876.4065301883778</v>
       </c>
       <c r="E85">
-        <v>2763.396</v>
+        <v>2818.908000000001</v>
       </c>
       <c r="F85">
-        <v>4607.496</v>
+        <v>4663.008000000001</v>
       </c>
       <c r="G85">
         <v>455.2</v>
@@ -8400,37 +8400,37 @@
         <v>435.9</v>
       </c>
       <c r="M85">
-        <v>1104.682848484106</v>
+        <v>1117.992280393553</v>
       </c>
       <c r="N85">
-        <v>-668.7828484841061</v>
+        <v>-682.0922803935532</v>
       </c>
       <c r="O85">
-        <v>-133.7565696968212</v>
+        <v>-136.4184560787106</v>
       </c>
       <c r="P85">
-        <v>-535.0262787872849</v>
+        <v>-545.6738243148426</v>
       </c>
       <c r="Q85">
-        <v>-315.926278787285</v>
+        <v>-326.5738243148426</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2107486593651819</v>
+        <v>0.2210579505755058</v>
       </c>
       <c r="T85">
-        <v>3.391518048020212</v>
+        <v>3.603487926021475</v>
       </c>
       <c r="U85">
         <v>0.2397577444416894</v>
       </c>
       <c r="V85">
-        <v>0.07891857841337194</v>
+        <v>0.07797907152749846</v>
       </c>
       <c r="W85">
-        <v>0.2208364040867548</v>
+        <v>0.2210616581385992</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3945928920668598</v>
+        <v>0.3898953576374924</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8446,22 +8446,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2210610649285042</v>
+        <v>0.2230006423729211</v>
       </c>
       <c r="C86">
-        <v>-3331.401469811622</v>
+        <v>-3396.506315048129</v>
       </c>
       <c r="D86">
-        <v>876.4065301883778</v>
+        <v>866.8136849518709</v>
       </c>
       <c r="E86">
-        <v>2818.908</v>
+        <v>2874.42</v>
       </c>
       <c r="F86">
-        <v>4663.008</v>
+        <v>4718.52</v>
       </c>
       <c r="G86">
         <v>455.2</v>
@@ -8482,37 +8482,37 @@
         <v>435.9</v>
       </c>
       <c r="M86">
-        <v>1117.992280393553</v>
+        <v>1131.301712303</v>
       </c>
       <c r="N86">
-        <v>-682.092280393553</v>
+        <v>-695.4017123030001</v>
       </c>
       <c r="O86">
-        <v>-136.4184560787106</v>
+        <v>-139.0803424606</v>
       </c>
       <c r="P86">
-        <v>-545.6738243148424</v>
+        <v>-556.3213698424</v>
       </c>
       <c r="Q86">
-        <v>-326.5738243148424</v>
+        <v>-337.2213698424001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2210579505755056</v>
+        <v>0.232741813947206</v>
       </c>
       <c r="T86">
-        <v>3.603487926021473</v>
+        <v>3.843720454422904</v>
       </c>
       <c r="U86">
         <v>0.2397577444416894</v>
       </c>
       <c r="V86">
-        <v>0.07797907152749849</v>
+        <v>0.07706167068599851</v>
       </c>
       <c r="W86">
-        <v>0.2210616581385992</v>
+        <v>0.2212816120951061</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3898953576374924</v>
+        <v>0.3853083534299925</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8528,22 +8528,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2230006423729211</v>
+        <v>0.224940219817338</v>
       </c>
       <c r="C87">
-        <v>-3396.506315048129</v>
+        <v>-3461.403433998853</v>
       </c>
       <c r="D87">
-        <v>866.8136849518709</v>
+        <v>857.4285660011468</v>
       </c>
       <c r="E87">
-        <v>2874.42</v>
+        <v>2929.932</v>
       </c>
       <c r="F87">
-        <v>4718.52</v>
+        <v>4774.032</v>
       </c>
       <c r="G87">
         <v>455.2</v>
@@ -8564,37 +8564,37 @@
         <v>435.9</v>
       </c>
       <c r="M87">
-        <v>1131.301712303</v>
+        <v>1144.611144212447</v>
       </c>
       <c r="N87">
-        <v>-695.4017123030001</v>
+        <v>-708.7111442124474</v>
       </c>
       <c r="O87">
-        <v>-139.0803424606</v>
+        <v>-141.7422288424895</v>
       </c>
       <c r="P87">
-        <v>-556.3213698424</v>
+        <v>-566.9689153699579</v>
       </c>
       <c r="Q87">
-        <v>-337.2213698424001</v>
+        <v>-347.868915369958</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.232741813947206</v>
+        <v>0.2460948006577208</v>
       </c>
       <c r="T87">
-        <v>3.843720454422904</v>
+        <v>4.118271915453112</v>
       </c>
       <c r="U87">
         <v>0.2397577444416894</v>
       </c>
       <c r="V87">
-        <v>0.07706167068599851</v>
+        <v>0.0761656047477892</v>
       </c>
       <c r="W87">
-        <v>0.2212816120951061</v>
+        <v>0.2214964508433222</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3853083534299925</v>
+        <v>0.380828023738946</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8610,22 +8610,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.224940219817338</v>
+        <v>0.2268797972617549</v>
       </c>
       <c r="C88">
-        <v>-3461.403433998853</v>
+        <v>-3526.099501641752</v>
       </c>
       <c r="D88">
-        <v>857.4285660011468</v>
+        <v>848.2444983582475</v>
       </c>
       <c r="E88">
-        <v>2929.932</v>
+        <v>2985.444</v>
       </c>
       <c r="F88">
-        <v>4774.032</v>
+        <v>4829.544</v>
       </c>
       <c r="G88">
         <v>455.2</v>
@@ -8646,37 +8646,37 @@
         <v>435.9</v>
       </c>
       <c r="M88">
-        <v>1144.611144212447</v>
+        <v>1157.920576121894</v>
       </c>
       <c r="N88">
-        <v>-708.7111442124474</v>
+        <v>-722.0205761218942</v>
       </c>
       <c r="O88">
-        <v>-141.7422288424895</v>
+        <v>-144.4041152243788</v>
       </c>
       <c r="P88">
-        <v>-566.9689153699579</v>
+        <v>-577.6164608975154</v>
       </c>
       <c r="Q88">
-        <v>-347.868915369958</v>
+        <v>-358.5164608975154</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2460948006577208</v>
+        <v>0.261502093016007</v>
       </c>
       <c r="T88">
-        <v>4.118271915453112</v>
+        <v>4.43506206279566</v>
       </c>
       <c r="U88">
         <v>0.2397577444416894</v>
       </c>
       <c r="V88">
-        <v>0.0761656047477892</v>
+        <v>0.07529013802655025</v>
       </c>
       <c r="W88">
-        <v>0.2214964508433222</v>
+        <v>0.2217063507697402</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.380828023738946</v>
+        <v>0.3764506901327513</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8692,22 +8692,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2268797972617549</v>
+        <v>0.2288193747061718</v>
       </c>
       <c r="C89">
-        <v>-3526.099501641752</v>
+        <v>-3590.60090999815</v>
       </c>
       <c r="D89">
-        <v>848.2444983582475</v>
+        <v>839.2550900018493</v>
       </c>
       <c r="E89">
-        <v>2985.444</v>
+        <v>3040.956</v>
       </c>
       <c r="F89">
-        <v>4829.544</v>
+        <v>4885.056</v>
       </c>
       <c r="G89">
         <v>455.2</v>
@@ -8728,37 +8728,37 @@
         <v>435.9</v>
       </c>
       <c r="M89">
-        <v>1157.920576121894</v>
+        <v>1171.230008031341</v>
       </c>
       <c r="N89">
-        <v>-722.0205761218942</v>
+        <v>-735.3300080313413</v>
       </c>
       <c r="O89">
-        <v>-144.4041152243788</v>
+        <v>-147.0660016062683</v>
       </c>
       <c r="P89">
-        <v>-577.6164608975154</v>
+        <v>-588.264006425073</v>
       </c>
       <c r="Q89">
-        <v>-358.5164608975154</v>
+        <v>-369.1640064250731</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.261502093016007</v>
+        <v>0.2794772674340076</v>
       </c>
       <c r="T89">
-        <v>4.43506206279566</v>
+        <v>4.804650568028632</v>
       </c>
       <c r="U89">
         <v>0.2397577444416894</v>
       </c>
       <c r="V89">
-        <v>0.07529013802655025</v>
+        <v>0.07443456827624854</v>
       </c>
       <c r="W89">
-        <v>0.2217063507697402</v>
+        <v>0.2219114802432851</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3764506901327513</v>
+        <v>0.3721728413812427</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8774,22 +8774,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2288193747061718</v>
+        <v>0.2307589521505887</v>
       </c>
       <c r="C90">
-        <v>-3590.60090999815</v>
+        <v>-3654.913782968897</v>
       </c>
       <c r="D90">
-        <v>839.2550900018493</v>
+        <v>830.454217031103</v>
       </c>
       <c r="E90">
-        <v>3040.956</v>
+        <v>3096.468</v>
       </c>
       <c r="F90">
-        <v>4885.056</v>
+        <v>4940.568</v>
       </c>
       <c r="G90">
         <v>455.2</v>
@@ -8810,37 +8810,37 @@
         <v>435.9</v>
       </c>
       <c r="M90">
-        <v>1171.230008031341</v>
+        <v>1184.539439940788</v>
       </c>
       <c r="N90">
-        <v>-735.3300080313413</v>
+        <v>-748.6394399407884</v>
       </c>
       <c r="O90">
-        <v>-147.0660016062683</v>
+        <v>-149.7278879881577</v>
       </c>
       <c r="P90">
-        <v>-588.264006425073</v>
+        <v>-598.9115519526307</v>
       </c>
       <c r="Q90">
-        <v>-369.1640064250731</v>
+        <v>-379.8115519526307</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2794772674340076</v>
+        <v>0.3007206553825538</v>
       </c>
       <c r="T90">
-        <v>4.804650568028632</v>
+        <v>5.241436983303962</v>
       </c>
       <c r="U90">
         <v>0.2397577444416894</v>
       </c>
       <c r="V90">
-        <v>0.07443456827624854</v>
+        <v>0.07359822481247046</v>
       </c>
       <c r="W90">
-        <v>0.2219114802432851</v>
+        <v>0.2221120000657391</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3721728413812427</v>
+        <v>0.3679911240623523</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8856,22 +8856,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2307589521505887</v>
+        <v>0.2326985295950056</v>
       </c>
       <c r="C91">
-        <v>-3654.913782968897</v>
+        <v>-3719.043990246743</v>
       </c>
       <c r="D91">
-        <v>830.454217031103</v>
+        <v>821.8360097532568</v>
       </c>
       <c r="E91">
-        <v>3096.468</v>
+        <v>3151.98</v>
       </c>
       <c r="F91">
-        <v>4940.568</v>
+        <v>4996.08</v>
       </c>
       <c r="G91">
         <v>455.2</v>
@@ -8892,37 +8892,37 @@
         <v>435.9</v>
       </c>
       <c r="M91">
-        <v>1184.539439940788</v>
+        <v>1197.848871850236</v>
       </c>
       <c r="N91">
-        <v>-748.6394399407884</v>
+        <v>-761.9488718502355</v>
       </c>
       <c r="O91">
-        <v>-149.7278879881577</v>
+        <v>-152.3897743700471</v>
       </c>
       <c r="P91">
-        <v>-598.9115519526307</v>
+        <v>-609.5590974801884</v>
       </c>
       <c r="Q91">
-        <v>-379.8115519526307</v>
+        <v>-390.4590974801884</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3007206553825538</v>
+        <v>0.3262127209208092</v>
       </c>
       <c r="T91">
-        <v>5.241436983303962</v>
+        <v>5.765580681634359</v>
       </c>
       <c r="U91">
         <v>0.2397577444416894</v>
       </c>
       <c r="V91">
-        <v>0.07359822481247046</v>
+        <v>0.07278046675899856</v>
       </c>
       <c r="W91">
-        <v>0.2221120000657391</v>
+        <v>0.2223080638921386</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3679911240623523</v>
+        <v>0.3639023337949929</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8938,22 +8938,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2326985295950056</v>
+        <v>0.2346381070394225</v>
       </c>
       <c r="C92">
-        <v>-3719.043990246743</v>
+        <v>-3782.997160371342</v>
       </c>
       <c r="D92">
-        <v>821.8360097532568</v>
+        <v>813.3948396286579</v>
       </c>
       <c r="E92">
-        <v>3151.98</v>
+        <v>3207.492</v>
       </c>
       <c r="F92">
-        <v>4996.08</v>
+        <v>5051.592</v>
       </c>
       <c r="G92">
         <v>455.2</v>
@@ -8974,37 +8974,37 @@
         <v>435.9</v>
       </c>
       <c r="M92">
-        <v>1197.848871850236</v>
+        <v>1211.158303759683</v>
       </c>
       <c r="N92">
-        <v>-761.9488718502355</v>
+        <v>-775.2583037596826</v>
       </c>
       <c r="O92">
-        <v>-152.3897743700471</v>
+        <v>-155.0516607519365</v>
       </c>
       <c r="P92">
-        <v>-609.5590974801884</v>
+        <v>-620.206643007746</v>
       </c>
       <c r="Q92">
-        <v>-390.4590974801884</v>
+        <v>-401.1066430077461</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3262127209208092</v>
+        <v>0.3573696899120102</v>
       </c>
       <c r="T92">
-        <v>5.765580681634359</v>
+        <v>6.406200757371511</v>
       </c>
       <c r="U92">
         <v>0.2397577444416894</v>
       </c>
       <c r="V92">
-        <v>0.07278046675899856</v>
+        <v>0.07198068140999858</v>
       </c>
       <c r="W92">
-        <v>0.2223080638921386</v>
+        <v>0.2224998186234523</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3639023337949929</v>
+        <v>0.3599034070499929</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9020,22 +9020,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2346381070394225</v>
+        <v>0.2365776844838394</v>
       </c>
       <c r="C93">
-        <v>-3782.997160371342</v>
+        <v>-3846.778692987891</v>
       </c>
       <c r="D93">
-        <v>813.3948396286579</v>
+        <v>805.1253070121089</v>
       </c>
       <c r="E93">
-        <v>3207.492</v>
+        <v>3263.004</v>
       </c>
       <c r="F93">
-        <v>5051.592</v>
+        <v>5107.104</v>
       </c>
       <c r="G93">
         <v>455.2</v>
@@ -9056,37 +9056,37 @@
         <v>435.9</v>
       </c>
       <c r="M93">
-        <v>1211.158303759683</v>
+        <v>1224.46773566913</v>
       </c>
       <c r="N93">
-        <v>-775.2583037596826</v>
+        <v>-788.5677356691297</v>
       </c>
       <c r="O93">
-        <v>-155.0516607519365</v>
+        <v>-157.713547133826</v>
       </c>
       <c r="P93">
-        <v>-620.206643007746</v>
+        <v>-630.8541885353037</v>
       </c>
       <c r="Q93">
-        <v>-401.1066430077461</v>
+        <v>-411.7541885353037</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3573696899120102</v>
+        <v>0.3963159011510116</v>
       </c>
       <c r="T93">
-        <v>6.406200757371511</v>
+        <v>7.206975852042952</v>
       </c>
       <c r="U93">
         <v>0.2397577444416894</v>
       </c>
       <c r="V93">
-        <v>0.07198068140999858</v>
+        <v>0.07119828269902033</v>
       </c>
       <c r="W93">
-        <v>0.2224998186234523</v>
+        <v>0.2226874047736505</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3599034070499929</v>
+        <v>0.3559914134951018</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9102,22 +9102,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2365776844838394</v>
+        <v>0.2385172619282563</v>
       </c>
       <c r="C94">
-        <v>-3846.778692987891</v>
+        <v>-3910.393770365523</v>
       </c>
       <c r="D94">
-        <v>805.1253070121089</v>
+        <v>797.0222296344772</v>
       </c>
       <c r="E94">
-        <v>3263.004</v>
+        <v>3318.516</v>
       </c>
       <c r="F94">
-        <v>5107.104</v>
+        <v>5162.616</v>
       </c>
       <c r="G94">
         <v>455.2</v>
@@ -9138,37 +9138,37 @@
         <v>435.9</v>
       </c>
       <c r="M94">
-        <v>1224.46773566913</v>
+        <v>1237.777167578577</v>
       </c>
       <c r="N94">
-        <v>-788.5677356691297</v>
+        <v>-801.8771675785767</v>
       </c>
       <c r="O94">
-        <v>-157.713547133826</v>
+        <v>-160.3754335157154</v>
       </c>
       <c r="P94">
-        <v>-630.8541885353037</v>
+        <v>-641.5017340628614</v>
       </c>
       <c r="Q94">
-        <v>-411.7541885353037</v>
+        <v>-422.4017340628614</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3963159011510116</v>
+        <v>0.4463896013154418</v>
       </c>
       <c r="T94">
-        <v>7.206975852042952</v>
+        <v>8.23654383090623</v>
       </c>
       <c r="U94">
         <v>0.2397577444416894</v>
       </c>
       <c r="V94">
-        <v>0.07119828269902033</v>
+        <v>0.07043270976677281</v>
       </c>
       <c r="W94">
-        <v>0.2226874047736505</v>
+        <v>0.2228709568130918</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3559914134951018</v>
+        <v>0.352163548833864</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9184,22 +9184,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2385172619282563</v>
+        <v>0.2404568393726732</v>
       </c>
       <c r="C95">
-        <v>-3910.393770365523</v>
+        <v>-3973.847368227071</v>
       </c>
       <c r="D95">
-        <v>797.0222296344772</v>
+        <v>789.0806317729281</v>
       </c>
       <c r="E95">
-        <v>3318.516</v>
+        <v>3374.028</v>
       </c>
       <c r="F95">
-        <v>5162.616</v>
+        <v>5218.128</v>
       </c>
       <c r="G95">
         <v>455.2</v>
@@ -9220,37 +9220,37 @@
         <v>435.9</v>
       </c>
       <c r="M95">
-        <v>1237.777167578577</v>
+        <v>1251.086599488024</v>
       </c>
       <c r="N95">
-        <v>-801.8771675785767</v>
+        <v>-815.1865994880236</v>
       </c>
       <c r="O95">
-        <v>-160.3754335157154</v>
+        <v>-163.0373198976047</v>
       </c>
       <c r="P95">
-        <v>-641.5017340628614</v>
+        <v>-652.1492795904189</v>
       </c>
       <c r="Q95">
-        <v>-422.4017340628614</v>
+        <v>-433.049279590419</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4463896013154418</v>
+        <v>0.5131545348680155</v>
       </c>
       <c r="T95">
-        <v>8.23654383090623</v>
+        <v>9.609301136057271</v>
       </c>
       <c r="U95">
         <v>0.2397577444416894</v>
       </c>
       <c r="V95">
-        <v>0.07043270976677281</v>
+        <v>0.06968342562031779</v>
       </c>
       <c r="W95">
-        <v>0.2228709568130918</v>
+        <v>0.2230506034899918</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.352163548833864</v>
+        <v>0.348417128101589</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9266,22 +9266,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2404568393726732</v>
+        <v>0.2423964168170901</v>
       </c>
       <c r="C96">
-        <v>-3973.847368227071</v>
+        <v>-4037.144265937781</v>
       </c>
       <c r="D96">
-        <v>789.0806317729281</v>
+        <v>781.2957340622191</v>
       </c>
       <c r="E96">
-        <v>3374.028</v>
+        <v>3429.54</v>
       </c>
       <c r="F96">
-        <v>5218.128</v>
+        <v>5273.64</v>
       </c>
       <c r="G96">
         <v>455.2</v>
@@ -9302,37 +9302,37 @@
         <v>435.9</v>
       </c>
       <c r="M96">
-        <v>1251.086599488024</v>
+        <v>1264.396031397471</v>
       </c>
       <c r="N96">
-        <v>-815.1865994880236</v>
+        <v>-828.4960313974709</v>
       </c>
       <c r="O96">
-        <v>-163.0373198976047</v>
+        <v>-165.6992062794942</v>
       </c>
       <c r="P96">
-        <v>-652.1492795904189</v>
+        <v>-662.7968251179767</v>
       </c>
       <c r="Q96">
-        <v>-433.049279590419</v>
+        <v>-443.6968251179767</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5131545348680155</v>
+        <v>0.6066254418416189</v>
       </c>
       <c r="T96">
-        <v>9.609301136057271</v>
+        <v>11.53116136326873</v>
       </c>
       <c r="U96">
         <v>0.2397577444416894</v>
       </c>
       <c r="V96">
-        <v>0.06968342562031779</v>
+        <v>0.06894991587694602</v>
       </c>
       <c r="W96">
-        <v>0.2230506034899918</v>
+        <v>0.2232264681315886</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.348417128101589</v>
+        <v>0.3447495793847301</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9348,22 +9348,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2423964168170901</v>
+        <v>0.244335994261507</v>
       </c>
       <c r="C97">
-        <v>-4037.144265937781</v>
+        <v>-4100.289056096779</v>
       </c>
       <c r="D97">
-        <v>781.2957340622191</v>
+        <v>773.6629439032206</v>
       </c>
       <c r="E97">
-        <v>3429.54</v>
+        <v>3485.052</v>
       </c>
       <c r="F97">
-        <v>5273.64</v>
+        <v>5329.152</v>
       </c>
       <c r="G97">
         <v>455.2</v>
@@ -9384,37 +9384,37 @@
         <v>435.9</v>
       </c>
       <c r="M97">
-        <v>1264.396031397471</v>
+        <v>1277.705463306918</v>
       </c>
       <c r="N97">
-        <v>-828.4960313974709</v>
+        <v>-841.8054633069178</v>
       </c>
       <c r="O97">
-        <v>-165.6992062794942</v>
+        <v>-168.3610926613836</v>
       </c>
       <c r="P97">
-        <v>-662.7968251179767</v>
+        <v>-673.4443706455343</v>
       </c>
       <c r="Q97">
-        <v>-443.6968251179767</v>
+        <v>-454.3443706455343</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6066254418416189</v>
+        <v>0.7468318023020241</v>
       </c>
       <c r="T97">
-        <v>11.53116136326873</v>
+        <v>14.41395170408592</v>
       </c>
       <c r="U97">
         <v>0.2397577444416894</v>
       </c>
       <c r="V97">
-        <v>0.06894991587694602</v>
+        <v>0.06823168758656116</v>
       </c>
       <c r="W97">
-        <v>0.2232264681315886</v>
+        <v>0.2233986689264855</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3447495793847301</v>
+        <v>0.3411584379328059</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9430,22 +9430,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.244335994261507</v>
+        <v>0.2462755717059238</v>
       </c>
       <c r="C98">
-        <v>-4100.289056096779</v>
+        <v>-4163.286153571782</v>
       </c>
       <c r="D98">
-        <v>773.6629439032206</v>
+        <v>766.1778464282173</v>
       </c>
       <c r="E98">
-        <v>3485.052</v>
+        <v>3540.564</v>
       </c>
       <c r="F98">
-        <v>5329.152</v>
+        <v>5384.664</v>
       </c>
       <c r="G98">
         <v>455.2</v>
@@ -9466,37 +9466,37 @@
         <v>435.9</v>
       </c>
       <c r="M98">
-        <v>1277.705463306918</v>
+        <v>1291.014895216365</v>
       </c>
       <c r="N98">
-        <v>-841.8054633069178</v>
+        <v>-855.1148952163649</v>
       </c>
       <c r="O98">
-        <v>-168.3610926613836</v>
+        <v>-171.022979043273</v>
       </c>
       <c r="P98">
-        <v>-673.4443706455343</v>
+        <v>-684.0919161730919</v>
       </c>
       <c r="Q98">
-        <v>-454.3443706455343</v>
+        <v>-464.991916173092</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7468318023020221</v>
+        <v>0.9805090697360295</v>
       </c>
       <c r="T98">
-        <v>14.41395170408588</v>
+        <v>19.21860227211451</v>
       </c>
       <c r="U98">
         <v>0.2397577444416894</v>
       </c>
       <c r="V98">
-        <v>0.06823168758656116</v>
+        <v>0.06752826812690589</v>
       </c>
       <c r="W98">
-        <v>0.2233986689264855</v>
+        <v>0.2235673191895288</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3411584379328059</v>
+        <v>0.3376413406345296</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9512,22 +9512,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2462755717059238</v>
+        <v>0.2482151491503407</v>
       </c>
       <c r="C99">
-        <v>-4163.286153571782</v>
+        <v>-4226.13980401436</v>
       </c>
       <c r="D99">
-        <v>766.1778464282173</v>
+        <v>758.8361959856392</v>
       </c>
       <c r="E99">
-        <v>3540.564</v>
+        <v>3596.076</v>
       </c>
       <c r="F99">
-        <v>5384.664</v>
+        <v>5440.175999999999</v>
       </c>
       <c r="G99">
         <v>455.2</v>
@@ -9548,37 +9548,37 @@
         <v>435.9</v>
       </c>
       <c r="M99">
-        <v>1291.014895216365</v>
+        <v>1304.324327125812</v>
       </c>
       <c r="N99">
-        <v>-855.1148952163649</v>
+        <v>-868.4243271258119</v>
       </c>
       <c r="O99">
-        <v>-171.022979043273</v>
+        <v>-173.6848654251624</v>
       </c>
       <c r="P99">
-        <v>-684.0919161730919</v>
+        <v>-694.7394617006496</v>
       </c>
       <c r="Q99">
-        <v>-464.991916173092</v>
+        <v>-475.6394617006496</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9805090697360295</v>
+        <v>1.447863604604044</v>
       </c>
       <c r="T99">
-        <v>19.21860227211451</v>
+        <v>28.82790340817176</v>
       </c>
       <c r="U99">
         <v>0.2397577444416894</v>
       </c>
       <c r="V99">
-        <v>0.06752826812690589</v>
+        <v>0.06683920416642726</v>
       </c>
       <c r="W99">
-        <v>0.2235673191895288</v>
+        <v>0.2237325276104692</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3376413406345296</v>
+        <v>0.3341960208321363</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9594,22 +9594,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2482151491503407</v>
+        <v>0.2501547265947576</v>
       </c>
       <c r="C100">
-        <v>-4226.13980401436</v>
+        <v>-4288.854091890284</v>
       </c>
       <c r="D100">
-        <v>758.8361959856392</v>
+        <v>751.6339081097168</v>
       </c>
       <c r="E100">
-        <v>3596.076</v>
+        <v>3651.588</v>
       </c>
       <c r="F100">
-        <v>5440.175999999999</v>
+        <v>5495.688</v>
       </c>
       <c r="G100">
         <v>455.2</v>
@@ -9630,37 +9630,37 @@
         <v>435.9</v>
       </c>
       <c r="M100">
-        <v>1304.324327125812</v>
+        <v>1317.633759035259</v>
       </c>
       <c r="N100">
-        <v>-868.4243271258119</v>
+        <v>-881.733759035259</v>
       </c>
       <c r="O100">
-        <v>-173.6848654251624</v>
+        <v>-176.3467518070518</v>
       </c>
       <c r="P100">
-        <v>-694.7394617006496</v>
+        <v>-705.3870072282073</v>
       </c>
       <c r="Q100">
-        <v>-475.6394617006496</v>
+        <v>-486.2870072282073</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.447863604604044</v>
+        <v>2.849927209208088</v>
       </c>
       <c r="T100">
-        <v>28.82790340817176</v>
+        <v>57.65580681634353</v>
       </c>
       <c r="U100">
         <v>0.2397577444416894</v>
       </c>
       <c r="V100">
-        <v>0.06683920416642726</v>
+        <v>0.06616406068999871</v>
       </c>
       <c r="W100">
-        <v>0.2237325276104692</v>
+        <v>0.2238943984875523</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9668,91 +9668,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3341960208321363</v>
+        <v>0.3308203034499936</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2501547265947576</v>
-      </c>
-      <c r="C101">
-        <v>-4288.854091890284</v>
-      </c>
-      <c r="D101">
-        <v>751.6339081097168</v>
-      </c>
-      <c r="E101">
-        <v>3651.588</v>
-      </c>
-      <c r="F101">
-        <v>5495.688</v>
-      </c>
-      <c r="G101">
-        <v>455.2</v>
-      </c>
-      <c r="H101">
-        <v>3707.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>655</v>
-      </c>
-      <c r="K101">
-        <v>219.1</v>
-      </c>
-      <c r="L101">
-        <v>435.9</v>
-      </c>
-      <c r="M101">
-        <v>1317.633759035259</v>
-      </c>
-      <c r="N101">
-        <v>-881.733759035259</v>
-      </c>
-      <c r="O101">
-        <v>-176.3467518070518</v>
-      </c>
-      <c r="P101">
-        <v>-705.3870072282073</v>
-      </c>
-      <c r="Q101">
-        <v>-486.2870072282073</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.849927209208088</v>
-      </c>
-      <c r="T101">
-        <v>57.65580681634353</v>
-      </c>
-      <c r="U101">
-        <v>0.2397577444416894</v>
-      </c>
-      <c r="V101">
-        <v>0.06616406068999871</v>
-      </c>
-      <c r="W101">
-        <v>0.2238943984875523</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3308203034499936</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
